--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE948764-831C-42C6-9B37-0D27F9130A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D33FBA3-7C81-4B49-98D9-61B203FB456B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -942,18 +942,180 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_FRA_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_FRA_030</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_FRA_018</t>
   </si>
   <si>
@@ -966,174 +1128,90 @@
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_FRA_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w98890904-400_FRA,e_w110086345-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w90842395-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA,e_w79866837-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA,e_w99722046-400_FRA,e_w85047359-400_FRA,e_w79866837-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w235370803-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w79866837-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w99722046-400_FRA,e_w85995894-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA,e_w85203486-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w179260933-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w179260933-400_FRA,e_w81641090-400_FRA,e_w159167277-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w82825438-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w81641090-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w24020601-400_FRA,e_w159167277-400_FRA,e_w147132694-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w79866837-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w112342683-400_FRA,e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w79866837-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w49510896-400_FRA,e_w98890904-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
     <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w99722046-400_FRA</t>
   </si>
   <si>
@@ -1143,82 +1221,10 @@
     <t>e_w147132694-400_FRA,e_w159167277-400_FRA</t>
   </si>
   <si>
-    <t>e_w79866837-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w79866837-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w82825438-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w81641090-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w24020601-400_FRA,e_w159167277-400_FRA,e_w147132694-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w99722046-400_FRA,e_w85995894-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w85710783-400_FRA,e_w85203486-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w179260933-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w179260933-400_FRA,e_w81641090-400_FRA,e_w159167277-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w49510896-400_FRA,e_w98890904-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w112342683-400_FRA,e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w98890904-400_FRA,e_w110086345-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w90842395-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA,e_w79866837-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w85710783-400_FRA,e_w99722046-400_FRA,e_w85047359-400_FRA,e_w79866837-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w235370803-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w79866837-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA</t>
+    <t>distr_wonelc_won_FRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wonelc_won_FRA_012</t>
@@ -1239,6 +1245,96 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wonelc_won_FRA_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_FRA_027</t>
   </si>
   <si>
@@ -1251,16 +1347,28 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>distr_wonelc_won_FRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_FRA_028</t>
@@ -1275,118 +1383,16 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_FRA_008</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
+    <t>elc_won_FRA_004</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA,e_w147132694-400_FRA</t>
   </si>
   <si>
     <t>elc_won_FRA_012</t>
@@ -1404,6 +1410,87 @@
     <t>e_w27259817-400_FRA,e_w90842395-400_FRA</t>
   </si>
   <si>
+    <t>elc_won_FRA_018</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_013</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w98890904-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_024</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w79866837-400_FRA,e_w179260933-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_017</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_007</t>
+  </si>
+  <si>
+    <t>e_w98890904-400_FRA,e_w110086345-400_FRA,e_w27259817-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_010</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_025</t>
+  </si>
+  <si>
+    <t>e_w99722046-400_FRA,e_w79866837-400_FRA,e_w85047359-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA,e_w82825438-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_009</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_022</t>
+  </si>
+  <si>
+    <t>e_w159167277-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_023</t>
+  </si>
+  <si>
+    <t>e_w179260933-400_FRA,e_w24020601-400_FRA,e_w159167277-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_021</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_014</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_016</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA,e_w85047359-400_FRA,e_w85203486-400_FRA,e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
+  </si>
+  <si>
     <t>elc_won_FRA_027</t>
   </si>
   <si>
@@ -1416,124 +1503,103 @@
     <t>e_w27259817-400_FRA</t>
   </si>
   <si>
-    <t>elc_won_FRA_017</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w85710783-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_007</t>
-  </si>
-  <si>
-    <t>e_w98890904-400_FRA,e_w110086345-400_FRA,e_w27259817-400_FRA</t>
+    <t>elc_won_FRA_002</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_026</t>
+  </si>
+  <si>
+    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_011</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_006</t>
+  </si>
+  <si>
+    <t>e_w110086345-400_FRA,e_w24020601-400_FRA</t>
   </si>
   <si>
     <t>elc_won_FRA_028</t>
   </si>
   <si>
-    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
     <t>elc_won_FRA_019</t>
   </si>
   <si>
     <t>e_w118086309-400_FRA</t>
   </si>
   <si>
-    <t>elc_won_FRA_026</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_025</t>
-  </si>
-  <si>
-    <t>e_w99722046-400_FRA,e_w79866837-400_FRA,e_w85047359-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA,e_w82825438-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_009</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_002</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_010</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_004</t>
-  </si>
-  <si>
-    <t>e_w27259817-400_FRA,e_w147132694-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_018</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_013</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w98890904-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_024</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w79866837-400_FRA,e_w179260933-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_015</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_014</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_016</t>
-  </si>
-  <si>
-    <t>e_w85710783-400_FRA,e_w85047359-400_FRA,e_w85203486-400_FRA,e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_011</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_006</t>
-  </si>
-  <si>
-    <t>e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_023</t>
-  </si>
-  <si>
-    <t>e_w179260933-400_FRA,e_w24020601-400_FRA,e_w159167277-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_021</t>
-  </si>
-  <si>
-    <t>e_w159167277-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_003</t>
-  </si>
-  <si>
     <t>elc_won_FRA_008</t>
   </si>
   <si>
     <t>e_w24020601-400_FRA</t>
   </si>
   <si>
-    <t>elc_won_FRA_022</t>
+    <t>distr_wofelc_wof_FRA_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_FRA_012</t>
@@ -1542,10 +1608,22 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
+    <t>distr_wofelc_wof_FRA_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wofelc_wof_FRA_013</t>
@@ -1554,88 +1632,46 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_FRA_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>elc_wof_FRA_014</t>
+  </si>
+  <si>
+    <t>e_w85995894-400_FRA,e_w85710783-400_FRA,e_w85203486-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_006</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_010</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_001</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_017</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_002</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_007</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_008</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_005</t>
   </si>
   <si>
     <t>elc_wof_FRA_012</t>
@@ -1644,7 +1680,16 @@
     <t>e_w146695955-400_FRA,e_w112342683-400_FRA</t>
   </si>
   <si>
-    <t>elc_wof_FRA_010</t>
+    <t>elc_wof_FRA_016</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_011</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w146695955-400_FRA,e_w235370803-400_FRA,e_w112342683-400_FRA,e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_004</t>
   </si>
   <si>
     <t>elc_wof_FRA_013</t>
@@ -1653,52 +1698,7 @@
     <t>e_w146695955-400_FRA,e_w85995894-400_FRA</t>
   </si>
   <si>
-    <t>elc_wof_FRA_016</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_011</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w146695955-400_FRA,e_w235370803-400_FRA,e_w112342683-400_FRA,e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_004</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_008</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_005</t>
-  </si>
-  <si>
     <t>elc_wof_FRA_009</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_017</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_003</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_002</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_014</t>
-  </si>
-  <si>
-    <t>e_w85995894-400_FRA,e_w85710783-400_FRA,e_w85203486-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_006</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_001</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_015</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_007</t>
   </si>
   <si>
     <t>e_won_FRA_001</t>
@@ -6796,7 +6796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{009C16A6-1C9B-4E7D-82B9-6D5C8DB770C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88318C55-1C2B-4A73-90F3-DC4911C27D53}">
   <dimension ref="B9:BD40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7034,16 +7034,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.9980700000086743</v>
+        <v>0.99811888657672254</v>
       </c>
       <c r="AB11">
-        <v>35.38333317430456</v>
+        <v>34.487079426754121</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7073,13 +7073,13 @@
         <v>420</v>
       </c>
       <c r="AN11" t="s">
-        <v>347</v>
+        <v>421</v>
       </c>
       <c r="AO11">
-        <v>0.99724350262056138</v>
+        <v>0.99739565808689357</v>
       </c>
       <c r="AP11">
-        <v>50.535785289707377</v>
+        <v>47.746268406951614</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7112,10 +7112,10 @@
         <v>504</v>
       </c>
       <c r="BC11">
-        <v>0.9911086854453236</v>
+        <v>0.99579717949467605</v>
       </c>
       <c r="BD11">
-        <v>163.0074335024004</v>
+        <v>77.051709264272191</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7180,16 +7180,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99767867140691957</v>
+        <v>0.99796668524605581</v>
       </c>
       <c r="AB12">
-        <v>42.55769087314146</v>
+        <v>37.277437155643319</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7216,16 +7216,16 @@
         <v>366</v>
       </c>
       <c r="AM12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN12" t="s">
-        <v>422</v>
+        <v>343</v>
       </c>
       <c r="AO12">
-        <v>0.99816665404006633</v>
+        <v>0.99724350262056138</v>
       </c>
       <c r="AP12">
-        <v>33.611342598783573</v>
+        <v>50.535785289707377</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7255,13 +7255,13 @@
         <v>505</v>
       </c>
       <c r="BB12" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="BC12">
-        <v>0.99863344496525219</v>
+        <v>0.98772606347662006</v>
       </c>
       <c r="BD12">
-        <v>25.053508970375976</v>
+        <v>225.02216959529935</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7326,16 +7326,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.9987681422400152</v>
+        <v>0.98282786238014608</v>
       </c>
       <c r="AB13">
-        <v>22.584058933054997</v>
+        <v>314.82252303065502</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7368,10 +7368,10 @@
         <v>424</v>
       </c>
       <c r="AO13">
-        <v>0.98918214360614543</v>
+        <v>0.99816665404006633</v>
       </c>
       <c r="AP13">
-        <v>198.32736722066633</v>
+        <v>33.611342598783573</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -7401,13 +7401,13 @@
         <v>506</v>
       </c>
       <c r="BB13" t="s">
-        <v>507</v>
+        <v>343</v>
       </c>
       <c r="BC13">
-        <v>0.99419387483019273</v>
+        <v>0.99863344496525219</v>
       </c>
       <c r="BD13">
-        <v>106.44562811313425</v>
+        <v>25.053508970375976</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7472,16 +7472,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="Z14" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AA14">
-        <v>0.99754382386829921</v>
+        <v>0.99778628553476412</v>
       </c>
       <c r="AB14">
-        <v>45.029895747848158</v>
+        <v>40.584765195991288</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -7514,10 +7514,10 @@
         <v>426</v>
       </c>
       <c r="AO14">
-        <v>0.99586599256158292</v>
+        <v>0.98918214360614543</v>
       </c>
       <c r="AP14">
-        <v>75.790136370979724</v>
+        <v>198.32736722066633</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -7544,16 +7544,16 @@
         <v>475</v>
       </c>
       <c r="BA14" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="BB14" t="s">
-        <v>342</v>
+        <v>437</v>
       </c>
       <c r="BC14">
-        <v>0.98973273644055293</v>
+        <v>0.99536965776860997</v>
       </c>
       <c r="BD14">
-        <v>188.23316525652893</v>
+        <v>84.889607575482927</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7618,16 +7618,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="Z15" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AA15">
-        <v>0.99783160220227129</v>
+        <v>0.99760073307445152</v>
       </c>
       <c r="AB15">
-        <v>39.753959625025857</v>
+        <v>43.986560301722875</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -7660,10 +7660,10 @@
         <v>428</v>
       </c>
       <c r="AO15">
-        <v>0.99742293468348531</v>
+        <v>0.99765345145842399</v>
       </c>
       <c r="AP15">
-        <v>47.246197469436119</v>
+        <v>43.020056595559488</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -7690,16 +7690,16 @@
         <v>477</v>
       </c>
       <c r="BA15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BB15" t="s">
-        <v>510</v>
+        <v>349</v>
       </c>
       <c r="BC15">
-        <v>0.98905121950258512</v>
+        <v>0.98065397607653604</v>
       </c>
       <c r="BD15">
-        <v>200.72764245260552</v>
+        <v>354.67710526350635</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7764,16 +7764,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="Z16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AA16">
-        <v>0.99738643688349482</v>
+        <v>0.99771094718615749</v>
       </c>
       <c r="AB16">
-        <v>47.915323802595424</v>
+        <v>41.965968253779806</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -7806,10 +7806,10 @@
         <v>430</v>
       </c>
       <c r="AO16">
-        <v>0.99784198809622926</v>
+        <v>0.99756226071513543</v>
       </c>
       <c r="AP16">
-        <v>39.563551569129636</v>
+        <v>44.691886889183898</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -7836,16 +7836,16 @@
         <v>479</v>
       </c>
       <c r="BA16" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="BB16" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="BC16">
-        <v>0.99441277928791383</v>
+        <v>0.98299346510038665</v>
       </c>
       <c r="BD16">
-        <v>102.43237972158009</v>
+        <v>311.78647315957892</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7910,16 +7910,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="Z17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AA17">
-        <v>0.99757113701984168</v>
+        <v>0.99789185737427777</v>
       </c>
       <c r="AB17">
-        <v>44.529154636235894</v>
+        <v>38.649281471573786</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -7952,10 +7952,10 @@
         <v>432</v>
       </c>
       <c r="AO17">
-        <v>0.99746485747937264</v>
+        <v>0.99719673945277698</v>
       </c>
       <c r="AP17">
-        <v>46.477612878168472</v>
+        <v>51.393110032423003</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -7982,16 +7982,16 @@
         <v>481</v>
       </c>
       <c r="BA17" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="BB17" t="s">
-        <v>428</v>
+        <v>337</v>
       </c>
       <c r="BC17">
-        <v>0.99850355933568513</v>
+        <v>0.98380382000267219</v>
       </c>
       <c r="BD17">
-        <v>27.434745512439168</v>
+        <v>296.92996661767575</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8056,16 +8056,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="Z18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AA18">
-        <v>0.99775269613274897</v>
+        <v>0.99603217268588318</v>
       </c>
       <c r="AB18">
-        <v>41.200570899602418</v>
+        <v>72.743500758808537</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8095,13 +8095,13 @@
         <v>433</v>
       </c>
       <c r="AN18" t="s">
-        <v>434</v>
+        <v>351</v>
       </c>
       <c r="AO18">
-        <v>0.99712165362217109</v>
+        <v>0.99778204559874861</v>
       </c>
       <c r="AP18">
-        <v>52.769683593529635</v>
+        <v>40.662497356275288</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8128,16 +8128,16 @@
         <v>483</v>
       </c>
       <c r="BA18" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="BB18" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="BC18">
-        <v>0.97849331544243145</v>
+        <v>0.99093284602677045</v>
       </c>
       <c r="BD18">
-        <v>394.28921688875596</v>
+        <v>166.23115617587521</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8202,16 +8202,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="Z19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AA19">
-        <v>0.99737794036187466</v>
+        <v>0.99851075781809495</v>
       </c>
       <c r="AB19">
-        <v>48.07109336563137</v>
+        <v>27.30277333492506</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8238,16 +8238,16 @@
         <v>380</v>
       </c>
       <c r="AM19" t="s">
+        <v>434</v>
+      </c>
+      <c r="AN19" t="s">
         <v>435</v>
       </c>
-      <c r="AN19" t="s">
-        <v>436</v>
-      </c>
       <c r="AO19">
-        <v>0.99650877616217826</v>
+        <v>0.99784198809622926</v>
       </c>
       <c r="AP19">
-        <v>64.005770360066109</v>
+        <v>39.563551569129636</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8274,16 +8274,16 @@
         <v>485</v>
       </c>
       <c r="BA19" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="BB19" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="BC19">
-        <v>0.99440716597809709</v>
+        <v>0.99703425039877824</v>
       </c>
       <c r="BD19">
-        <v>102.53529040155342</v>
+        <v>54.372076022398424</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8348,16 +8348,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="Z20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AA20">
-        <v>0.99790569401710338</v>
+        <v>0.99807548905811494</v>
       </c>
       <c r="AB20">
-        <v>38.395609686438895</v>
+        <v>35.282700601226196</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -8384,16 +8384,16 @@
         <v>382</v>
       </c>
       <c r="AM20" t="s">
+        <v>436</v>
+      </c>
+      <c r="AN20" t="s">
         <v>437</v>
       </c>
-      <c r="AN20" t="s">
-        <v>434</v>
-      </c>
       <c r="AO20">
-        <v>0.99789185043252149</v>
+        <v>0.99746485747937264</v>
       </c>
       <c r="AP20">
-        <v>38.649408737106661</v>
+        <v>46.477612878168472</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -8420,16 +8420,16 @@
         <v>487</v>
       </c>
       <c r="BA20" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="BB20" t="s">
-        <v>342</v>
+        <v>457</v>
       </c>
       <c r="BC20">
-        <v>0.98065397607653604</v>
+        <v>0.99850355933568513</v>
       </c>
       <c r="BD20">
-        <v>354.67710526350635</v>
+        <v>27.434745512439168</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8494,16 +8494,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="Z21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AA21">
-        <v>0.99777826206332976</v>
+        <v>0.99812782016534596</v>
       </c>
       <c r="AB21">
-        <v>40.731862172288039</v>
+        <v>34.323296968657118</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -8536,10 +8536,10 @@
         <v>439</v>
       </c>
       <c r="AO21">
-        <v>0.99804245386379287</v>
+        <v>0.99808767667924114</v>
       </c>
       <c r="AP21">
-        <v>35.888345830464296</v>
+        <v>35.059260880579068</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -8566,16 +8566,16 @@
         <v>489</v>
       </c>
       <c r="BA21" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="BB21" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="BC21">
-        <v>0.98299346510038665</v>
+        <v>0.97849331544243145</v>
       </c>
       <c r="BD21">
-        <v>311.78647315957892</v>
+        <v>394.28921688875596</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8640,16 +8640,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="Z22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AA22">
-        <v>0.99764504969214185</v>
+        <v>0.99873749004157653</v>
       </c>
       <c r="AB22">
-        <v>43.174088977399613</v>
+        <v>23.146015904430175</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -8682,10 +8682,10 @@
         <v>441</v>
       </c>
       <c r="AO22">
-        <v>0.9970097215210143</v>
+        <v>0.99804245386379287</v>
       </c>
       <c r="AP22">
-        <v>54.82177211473752</v>
+        <v>35.888345830464296</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -8712,16 +8712,16 @@
         <v>491</v>
       </c>
       <c r="BA22" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="BB22" t="s">
-        <v>357</v>
+        <v>516</v>
       </c>
       <c r="BC22">
-        <v>0.98380382000267219</v>
+        <v>0.9911086854453236</v>
       </c>
       <c r="BD22">
-        <v>296.92996661767575</v>
+        <v>163.0074335024004</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8786,16 +8786,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Z23" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA23">
-        <v>0.99807548905811494</v>
+        <v>0.99820251673680249</v>
       </c>
       <c r="AB23">
-        <v>35.282700601226196</v>
+        <v>32.953859825288589</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -8825,13 +8825,13 @@
         <v>442</v>
       </c>
       <c r="AN23" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="AO23">
-        <v>0.99857814187768335</v>
+        <v>0.9970097215210143</v>
       </c>
       <c r="AP23">
-        <v>26.067398909139413</v>
+        <v>54.82177211473752</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -8858,16 +8858,16 @@
         <v>493</v>
       </c>
       <c r="BA23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="BB23" t="s">
-        <v>519</v>
+        <v>349</v>
       </c>
       <c r="BC23">
-        <v>0.99579717949467605</v>
+        <v>0.98973273644055293</v>
       </c>
       <c r="BD23">
-        <v>77.051709264272191</v>
+        <v>188.23316525652893</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8932,16 +8932,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Z24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AA24">
-        <v>0.99812782016534596</v>
+        <v>0.99719319688440999</v>
       </c>
       <c r="AB24">
-        <v>34.323296968657118</v>
+        <v>51.458057119150247</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -8968,16 +8968,16 @@
         <v>390</v>
       </c>
       <c r="AM24" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN24" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO24">
-        <v>0.99808767667924114</v>
+        <v>0.9979962856207204</v>
       </c>
       <c r="AP24">
-        <v>35.059260880579068</v>
+        <v>36.734763620126827</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9004,16 +9004,16 @@
         <v>495</v>
       </c>
       <c r="BA24" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="BB24" t="s">
-        <v>357</v>
+        <v>519</v>
       </c>
       <c r="BC24">
-        <v>0.98772606347662006</v>
+        <v>0.98905121950258512</v>
       </c>
       <c r="BD24">
-        <v>225.02216959529935</v>
+        <v>200.72764245260552</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9078,16 +9078,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="Z25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AA25">
-        <v>0.99873749004157653</v>
+        <v>0.99700804792465858</v>
       </c>
       <c r="AB25">
-        <v>23.146015904430175</v>
+        <v>54.85245471459325</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9114,16 +9114,16 @@
         <v>392</v>
       </c>
       <c r="AM25" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO25">
-        <v>0.99739565808689357</v>
+        <v>0.99648757714768388</v>
       </c>
       <c r="AP25">
-        <v>47.746268406951614</v>
+        <v>64.394418959127933</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9150,16 +9150,16 @@
         <v>497</v>
       </c>
       <c r="BA25" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BB25" t="s">
-        <v>432</v>
+        <v>337</v>
       </c>
       <c r="BC25">
-        <v>0.99536965776860997</v>
+        <v>0.99441277928791383</v>
       </c>
       <c r="BD25">
-        <v>84.889607575482927</v>
+        <v>102.43237972158009</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9224,16 +9224,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="Z26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AA26">
-        <v>0.99820251673680249</v>
+        <v>0.99775269613274897</v>
       </c>
       <c r="AB26">
-        <v>32.953859825288589</v>
+        <v>41.200570899602418</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9260,16 +9260,16 @@
         <v>394</v>
       </c>
       <c r="AM26" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN26" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AO26">
-        <v>0.99765345145842399</v>
+        <v>0.9988955767418648</v>
       </c>
       <c r="AP26">
-        <v>43.020056595559488</v>
+        <v>20.247759732477729</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9296,16 +9296,16 @@
         <v>499</v>
       </c>
       <c r="BA26" t="s">
+        <v>521</v>
+      </c>
+      <c r="BB26" t="s">
         <v>522</v>
       </c>
-      <c r="BB26" t="s">
-        <v>342</v>
-      </c>
       <c r="BC26">
-        <v>0.99093284602677045</v>
+        <v>0.99419387483019273</v>
       </c>
       <c r="BD26">
-        <v>166.23115617587521</v>
+        <v>106.44562811313425</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9370,16 +9370,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AA27">
-        <v>0.99719319688440999</v>
+        <v>0.99737794036187466</v>
       </c>
       <c r="AB27">
-        <v>51.458057119150247</v>
+        <v>48.07109336563137</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -9409,13 +9409,13 @@
         <v>449</v>
       </c>
       <c r="AN27" t="s">
-        <v>450</v>
+        <v>337</v>
       </c>
       <c r="AO27">
-        <v>0.99756226071513543</v>
+        <v>0.99512455257015542</v>
       </c>
       <c r="AP27">
-        <v>44.691886889183898</v>
+        <v>89.383202880483722</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -9445,13 +9445,13 @@
         <v>523</v>
       </c>
       <c r="BB27" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="BC27">
-        <v>0.99703425039877824</v>
+        <v>0.99440716597809709</v>
       </c>
       <c r="BD27">
-        <v>54.372076022398424</v>
+        <v>102.53529040155342</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9516,16 +9516,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="Z28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AA28">
-        <v>0.99768389076925323</v>
+        <v>0.99790569401710338</v>
       </c>
       <c r="AB28">
-        <v>42.462002563689758</v>
+        <v>38.395609686438895</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -9552,16 +9552,16 @@
         <v>398</v>
       </c>
       <c r="AM28" t="s">
+        <v>450</v>
+      </c>
+      <c r="AN28" t="s">
         <v>451</v>
       </c>
-      <c r="AN28" t="s">
-        <v>452</v>
-      </c>
       <c r="AO28">
-        <v>0.99719673945277698</v>
+        <v>0.99518717763850095</v>
       </c>
       <c r="AP28">
-        <v>51.393110032423003</v>
+        <v>88.235076627481902</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9626,16 +9626,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="Z29" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AA29">
-        <v>0.99678800794697264</v>
+        <v>0.99777826206332976</v>
       </c>
       <c r="AB29">
-        <v>58.88652097216788</v>
+        <v>40.731862172288039</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -9662,16 +9662,16 @@
         <v>400</v>
       </c>
       <c r="AM29" t="s">
+        <v>452</v>
+      </c>
+      <c r="AN29" t="s">
         <v>453</v>
       </c>
-      <c r="AN29" t="s">
-        <v>344</v>
-      </c>
       <c r="AO29">
-        <v>0.99778204559874861</v>
+        <v>0.99810940368916978</v>
       </c>
       <c r="AP29">
-        <v>40.662497356275288</v>
+        <v>34.660932365220965</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9736,16 +9736,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="Z30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA30">
-        <v>0.9967781407005234</v>
+        <v>0.99764504969214185</v>
       </c>
       <c r="AB30">
-        <v>59.06742049040524</v>
+        <v>43.174088977399613</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -9778,10 +9778,10 @@
         <v>455</v>
       </c>
       <c r="AO30">
-        <v>0.99518717763850095</v>
+        <v>0.99586599256158292</v>
       </c>
       <c r="AP30">
-        <v>88.235076627481902</v>
+        <v>75.790136370979724</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9846,16 +9846,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="Z31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AA31">
-        <v>0.99778628553476412</v>
+        <v>0.99738643688349482</v>
       </c>
       <c r="AB31">
-        <v>40.584765195991288</v>
+        <v>47.915323802595424</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -9888,10 +9888,10 @@
         <v>457</v>
       </c>
       <c r="AO31">
-        <v>0.99810940368916978</v>
+        <v>0.99742293468348531</v>
       </c>
       <c r="AP31">
-        <v>34.660932365220965</v>
+        <v>47.246197469436119</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9956,16 +9956,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="Z32" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AA32">
-        <v>0.99811888657672254</v>
+        <v>0.99757113701984168</v>
       </c>
       <c r="AB32">
-        <v>34.487079426754121</v>
+        <v>44.529154636235894</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -9995,13 +9995,13 @@
         <v>458</v>
       </c>
       <c r="AN32" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="AO32">
-        <v>0.99742029995821757</v>
+        <v>0.99857814187768335</v>
       </c>
       <c r="AP32">
-        <v>47.294500766011943</v>
+        <v>26.067398909139413</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10066,16 +10066,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="Z33" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA33">
-        <v>0.99796668524605581</v>
+        <v>0.9967781407005234</v>
       </c>
       <c r="AB33">
-        <v>37.277437155643319</v>
+        <v>59.06742049040524</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10108,10 +10108,10 @@
         <v>460</v>
       </c>
       <c r="AO33">
-        <v>0.99817633840500364</v>
+        <v>0.99789185043252149</v>
       </c>
       <c r="AP33">
-        <v>33.433795908267413</v>
+        <v>38.649408737106661</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10176,16 +10176,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Z34" t="s">
         <v>357</v>
       </c>
       <c r="AA34">
-        <v>0.98282786238014608</v>
+        <v>0.99754382386829921</v>
       </c>
       <c r="AB34">
-        <v>314.82252303065502</v>
+        <v>45.029895747848158</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -10215,13 +10215,13 @@
         <v>461</v>
       </c>
       <c r="AN34" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="AO34">
-        <v>0.99648757714768388</v>
+        <v>0.99742029995821757</v>
       </c>
       <c r="AP34">
-        <v>64.394418959127933</v>
+        <v>47.294500766011943</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10286,16 +10286,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="Z35" t="s">
         <v>358</v>
       </c>
       <c r="AA35">
-        <v>0.99760073307445152</v>
+        <v>0.99783160220227129</v>
       </c>
       <c r="AB35">
-        <v>43.986560301722875</v>
+        <v>39.753959625025857</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -10322,16 +10322,16 @@
         <v>412</v>
       </c>
       <c r="AM35" t="s">
+        <v>462</v>
+      </c>
+      <c r="AN35" t="s">
         <v>463</v>
       </c>
-      <c r="AN35" t="s">
-        <v>464</v>
-      </c>
       <c r="AO35">
-        <v>0.9988955767418648</v>
+        <v>0.99817633840500364</v>
       </c>
       <c r="AP35">
-        <v>20.247759732477729</v>
+        <v>33.433795908267413</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10396,16 +10396,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Z36" t="s">
         <v>359</v>
       </c>
       <c r="AA36">
-        <v>0.99771094718615749</v>
+        <v>0.99768389076925323</v>
       </c>
       <c r="AB36">
-        <v>41.965968253779806</v>
+        <v>42.462002563689758</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -10432,16 +10432,16 @@
         <v>414</v>
       </c>
       <c r="AM36" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AN36" t="s">
-        <v>357</v>
+        <v>460</v>
       </c>
       <c r="AO36">
-        <v>0.99512455257015542</v>
+        <v>0.99712165362217109</v>
       </c>
       <c r="AP36">
-        <v>89.383202880483722</v>
+        <v>52.769683593529635</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10506,16 +10506,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="Z37" t="s">
         <v>360</v>
       </c>
       <c r="AA37">
-        <v>0.99789185737427777</v>
+        <v>0.99678800794697264</v>
       </c>
       <c r="AB37">
-        <v>38.649281471573786</v>
+        <v>58.88652097216788</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -10542,16 +10542,16 @@
         <v>416</v>
       </c>
       <c r="AM37" t="s">
+        <v>465</v>
+      </c>
+      <c r="AN37" t="s">
         <v>466</v>
       </c>
-      <c r="AN37" t="s">
-        <v>467</v>
-      </c>
       <c r="AO37">
-        <v>0.99854067090268706</v>
+        <v>0.99650877616217826</v>
       </c>
       <c r="AP37">
-        <v>26.754366784069809</v>
+        <v>64.005770360066109</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10616,16 +10616,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Z38" t="s">
         <v>361</v>
       </c>
       <c r="AA38">
-        <v>0.99603217268588318</v>
+        <v>0.9980700000086743</v>
       </c>
       <c r="AB38">
-        <v>72.743500758808537</v>
+        <v>35.38333317430456</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -10652,16 +10652,16 @@
         <v>418</v>
       </c>
       <c r="AM38" t="s">
+        <v>467</v>
+      </c>
+      <c r="AN38" t="s">
         <v>468</v>
       </c>
-      <c r="AN38" t="s">
-        <v>464</v>
-      </c>
       <c r="AO38">
-        <v>0.9979962856207204</v>
+        <v>0.99854067090268706</v>
       </c>
       <c r="AP38">
-        <v>36.734763620126827</v>
+        <v>26.754366784069809</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10726,16 +10726,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="Z39" t="s">
         <v>362</v>
       </c>
       <c r="AA39">
-        <v>0.99851075781809495</v>
+        <v>0.99767867140691957</v>
       </c>
       <c r="AB39">
-        <v>27.30277333492506</v>
+        <v>42.55769087314146</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10800,16 +10800,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z40" t="s">
         <v>363</v>
       </c>
       <c r="AA40">
-        <v>0.99700804792465858</v>
+        <v>0.9987681422400152</v>
       </c>
       <c r="AB40">
-        <v>54.85245471459325</v>
+        <v>22.584058933054997</v>
       </c>
     </row>
   </sheetData>
@@ -10818,7 +10818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E498EF8C-BC78-45B4-AA8E-93CA1D00763F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752F1278-533E-4A35-BCAD-71005CB9BB87}">
   <dimension ref="B9:Z38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10930,7 +10930,7 @@
         <v>524</v>
       </c>
       <c r="K11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L11">
         <v>7.5214385218371174</v>
@@ -10963,7 +10963,7 @@
         <v>580</v>
       </c>
       <c r="X11" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="Y11">
         <v>38.3018</v>
@@ -10998,7 +10998,7 @@
         <v>526</v>
       </c>
       <c r="K12" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="L12">
         <v>8.5464211426904182</v>
@@ -11031,7 +11031,7 @@
         <v>582</v>
       </c>
       <c r="X12" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="Y12">
         <v>9.3112499999999994</v>
@@ -11066,7 +11066,7 @@
         <v>528</v>
       </c>
       <c r="K13" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="L13">
         <v>1.5340845206129941</v>
@@ -11099,7 +11099,7 @@
         <v>584</v>
       </c>
       <c r="X13" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="Y13">
         <v>9.5287500000000005</v>
@@ -11134,7 +11134,7 @@
         <v>530</v>
       </c>
       <c r="K14" t="s">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="L14">
         <v>17.642367792804524</v>
@@ -11167,7 +11167,7 @@
         <v>586</v>
       </c>
       <c r="X14" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="Y14">
         <v>2.1749999999999999E-2</v>
@@ -11202,7 +11202,7 @@
         <v>532</v>
       </c>
       <c r="K15" t="s">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="L15">
         <v>3.7020770759557711</v>
@@ -11235,7 +11235,7 @@
         <v>588</v>
       </c>
       <c r="X15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Y15">
         <v>8.2590000000000003</v>
@@ -11270,7 +11270,7 @@
         <v>534</v>
       </c>
       <c r="K16" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L16">
         <v>28.142418601835601</v>
@@ -11303,7 +11303,7 @@
         <v>590</v>
       </c>
       <c r="X16" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="Y16">
         <v>0.40575</v>
@@ -11338,7 +11338,7 @@
         <v>536</v>
       </c>
       <c r="K17" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="L17">
         <v>52.588193451360631</v>
@@ -11371,7 +11371,7 @@
         <v>592</v>
       </c>
       <c r="X17" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="Y17">
         <v>6.4290000000000003</v>
@@ -11406,7 +11406,7 @@
         <v>538</v>
       </c>
       <c r="K18" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L18">
         <v>21.66872817402496</v>
@@ -11439,7 +11439,7 @@
         <v>594</v>
       </c>
       <c r="X18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Y18">
         <v>0.10199999999999999</v>
@@ -11474,7 +11474,7 @@
         <v>540</v>
       </c>
       <c r="K19" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L19">
         <v>75.448981284454376</v>
@@ -11507,7 +11507,7 @@
         <v>596</v>
       </c>
       <c r="X19" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="Y19">
         <v>27.910499999999999</v>
@@ -11542,7 +11542,7 @@
         <v>542</v>
       </c>
       <c r="K20" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="L20">
         <v>15.373849239963436</v>
@@ -11575,7 +11575,7 @@
         <v>598</v>
       </c>
       <c r="X20" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Y20">
         <v>2.7322500000000001</v>
@@ -11610,7 +11610,7 @@
         <v>544</v>
       </c>
       <c r="K21" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L21">
         <v>20.923088433115996</v>
@@ -11643,7 +11643,7 @@
         <v>600</v>
       </c>
       <c r="X21" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="Y21">
         <v>69.386250000000004</v>
@@ -11678,7 +11678,7 @@
         <v>546</v>
       </c>
       <c r="K22" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L22">
         <v>10.348692721070078</v>
@@ -11711,7 +11711,7 @@
         <v>602</v>
       </c>
       <c r="X22" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="Y22">
         <v>79.72475</v>
@@ -11746,7 +11746,7 @@
         <v>548</v>
       </c>
       <c r="K23" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="L23">
         <v>30.731418987588004</v>
@@ -11779,7 +11779,7 @@
         <v>604</v>
       </c>
       <c r="X23" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="Y23">
         <v>19.849499999999999</v>
@@ -11814,7 +11814,7 @@
         <v>550</v>
       </c>
       <c r="K24" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L24">
         <v>6.8734480919946561</v>
@@ -11847,7 +11847,7 @@
         <v>606</v>
       </c>
       <c r="X24" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="Y24">
         <v>34.275750000000002</v>
@@ -11882,7 +11882,7 @@
         <v>552</v>
       </c>
       <c r="K25" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="L25">
         <v>44.470842554915507</v>
@@ -11915,7 +11915,7 @@
         <v>608</v>
       </c>
       <c r="X25" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="Y25">
         <v>88.0535</v>
@@ -11950,7 +11950,7 @@
         <v>554</v>
       </c>
       <c r="K26" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="L26">
         <v>94.751954680638562</v>
@@ -11983,7 +11983,7 @@
         <v>610</v>
       </c>
       <c r="X26" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="Y26">
         <v>42.073500000000003</v>
@@ -12018,7 +12018,7 @@
         <v>556</v>
       </c>
       <c r="K27" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="L27">
         <v>32.871207794729088</v>
@@ -12051,7 +12051,7 @@
         <v>612</v>
       </c>
       <c r="X27" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="Y27">
         <v>65.507249999999999</v>
@@ -12086,7 +12086,7 @@
         <v>558</v>
       </c>
       <c r="K28" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="L28">
         <v>113.99847062392492</v>
@@ -12121,7 +12121,7 @@
         <v>560</v>
       </c>
       <c r="K29" t="s">
-        <v>435</v>
+        <v>465</v>
       </c>
       <c r="L29">
         <v>18.2196769426582</v>
@@ -12156,7 +12156,7 @@
         <v>562</v>
       </c>
       <c r="K30" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L30">
         <v>53.979644051935594</v>
@@ -12191,7 +12191,7 @@
         <v>564</v>
       </c>
       <c r="K31" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="L31">
         <v>17.215449395412726</v>
@@ -12226,7 +12226,7 @@
         <v>566</v>
       </c>
       <c r="K32" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="L32">
         <v>29.852997664126345</v>
@@ -12261,7 +12261,7 @@
         <v>568</v>
       </c>
       <c r="K33" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="L33">
         <v>33.097235865274165</v>
@@ -12296,7 +12296,7 @@
         <v>570</v>
       </c>
       <c r="K34" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="L34">
         <v>50.818330360170975</v>
@@ -12331,7 +12331,7 @@
         <v>572</v>
       </c>
       <c r="K35" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L35">
         <v>93.018246457332225</v>
@@ -12366,7 +12366,7 @@
         <v>574</v>
       </c>
       <c r="K36" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L36">
         <v>48.982209359452717</v>
@@ -12401,7 +12401,7 @@
         <v>576</v>
       </c>
       <c r="K37" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="L37">
         <v>22.316533209679985</v>
@@ -12436,7 +12436,7 @@
         <v>578</v>
       </c>
       <c r="K38" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="L38">
         <v>43.496233223332773</v>
@@ -12451,7 +12451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D5A9F4-6928-4A7A-890F-7BE9954F2E7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25756439-EB5F-4164-9BA8-9A25FEA023D4}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D33FBA3-7C81-4B49-98D9-61B203FB456B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCB76F6B-22CA-4D8A-9D2F-2B0695154B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="648">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -942,18 +942,168 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_FRA_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_FRA_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_FRA_015</t>
   </si>
   <si>
@@ -966,108 +1116,6 @@
     <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_solelc_spv_FRA_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_FRA_009</t>
   </si>
   <si>
@@ -1080,145 +1128,151 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA,e_w79866837-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA,e_w99722046-400_FRA,e_w85047359-400_FRA,e_w79866837-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w235370803-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w79866837-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w98890904-400_FRA,e_w110086345-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w49510896-400_FRA,e_w98890904-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w112342683-400_FRA,e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA,e_w147132694-400_FRA,e_w90842395-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w147132694-400_FRA,e_w159167277-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w99722046-400_FRA,e_w85995894-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA,e_w85203486-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w179260933-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w179260933-400_FRA,e_w81641090-400_FRA,e_w159167277-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w79866837-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w24020601-400_FRA,e_w159167277-400_FRA,e_w147132694-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w82825438-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w81641090-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
     <t>e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
   </si>
   <si>
-    <t>e_w98890904-400_FRA,e_w110086345-400_FRA</t>
-  </si>
-  <si>
     <t>e_w90842395-400_FRA</t>
   </si>
   <si>
-    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA,e_w79866837-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w85710783-400_FRA,e_w99722046-400_FRA,e_w85047359-400_FRA,e_w79866837-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w235370803-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w79866837-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w99722046-400_FRA,e_w85995894-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w85710783-400_FRA,e_w85203486-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w179260933-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w179260933-400_FRA,e_w81641090-400_FRA,e_w159167277-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w82825438-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w81641090-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w24020601-400_FRA,e_w159167277-400_FRA,e_w147132694-400_FRA</t>
-  </si>
-  <si>
     <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA</t>
   </si>
   <si>
     <t>e_w79866837-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA</t>
   </si>
   <si>
-    <t>e_w112342683-400_FRA,e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w79866837-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w49510896-400_FRA,e_w98890904-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w27259817-400_FRA,e_w147132694-400_FRA,e_w90842395-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w147132694-400_FRA,e_w159167277-400_FRA</t>
+    <t>distr_wonelc_won_FRA_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
     <t>distr_wonelc_won_FRA_004</t>
@@ -1227,6 +1281,42 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wonelc_won_FRA_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_FRA_012</t>
   </si>
   <si>
@@ -1245,22 +1335,40 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
+    <t>distr_wonelc_won_FRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wonelc_won_FRA_015</t>
@@ -1281,112 +1389,55 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>elc_won_FRA_025</t>
+  </si>
+  <si>
+    <t>e_w99722046-400_FRA,e_w79866837-400_FRA,e_w85047359-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA,e_w82825438-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_009</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_028</t>
+  </si>
+  <si>
+    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_019</t>
+  </si>
+  <si>
+    <t>e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_018</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_013</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w98890904-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_024</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w79866837-400_FRA,e_w179260933-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_010</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_026</t>
   </si>
   <si>
     <t>elc_won_FRA_004</t>
@@ -1395,6 +1446,39 @@
     <t>e_w27259817-400_FRA,e_w147132694-400_FRA</t>
   </si>
   <si>
+    <t>elc_won_FRA_023</t>
+  </si>
+  <si>
+    <t>e_w179260933-400_FRA,e_w24020601-400_FRA,e_w159167277-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_021</t>
+  </si>
+  <si>
+    <t>e_w159167277-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_008</t>
+  </si>
+  <si>
+    <t>e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_011</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_006</t>
+  </si>
+  <si>
+    <t>e_w110086345-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
     <t>elc_won_FRA_012</t>
   </si>
   <si>
@@ -1410,22 +1494,31 @@
     <t>e_w27259817-400_FRA,e_w90842395-400_FRA</t>
   </si>
   <si>
-    <t>elc_won_FRA_018</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_013</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w98890904-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_024</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w79866837-400_FRA,e_w179260933-400_FRA</t>
+    <t>elc_won_FRA_002</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_027</t>
+  </si>
+  <si>
+    <t>e_w235370803-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_005</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_014</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_016</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA,e_w85047359-400_FRA,e_w85203486-400_FRA,e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_022</t>
   </si>
   <si>
     <t>elc_won_FRA_015</t>
@@ -1443,97 +1536,28 @@
     <t>e_w98890904-400_FRA,e_w110086345-400_FRA,e_w27259817-400_FRA</t>
   </si>
   <si>
-    <t>elc_won_FRA_010</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_025</t>
-  </si>
-  <si>
-    <t>e_w99722046-400_FRA,e_w79866837-400_FRA,e_w85047359-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA,e_w82825438-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_009</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_022</t>
-  </si>
-  <si>
-    <t>e_w159167277-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_023</t>
-  </si>
-  <si>
-    <t>e_w179260933-400_FRA,e_w24020601-400_FRA,e_w159167277-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_021</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_003</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_014</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_016</t>
-  </si>
-  <si>
-    <t>e_w85710783-400_FRA,e_w85047359-400_FRA,e_w85203486-400_FRA,e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_027</t>
-  </si>
-  <si>
-    <t>e_w235370803-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_005</t>
-  </si>
-  <si>
-    <t>e_w27259817-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_002</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_026</t>
-  </si>
-  <si>
-    <t>e_w235370803-400_FRA,e_w99722046-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_011</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_006</t>
-  </si>
-  <si>
-    <t>e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_028</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_019</t>
-  </si>
-  <si>
-    <t>e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_008</t>
-  </si>
-  <si>
-    <t>e_w24020601-400_FRA</t>
+    <t>distr_wofelc_wof_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wofelc_wof_FRA_014</t>
@@ -1542,10 +1566,46 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>distr_wofelc_wof_FRA_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_FRA_010</t>
@@ -1560,54 +1620,6 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_FRA_016</t>
   </si>
   <si>
@@ -1626,16 +1638,16 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>elc_wof_FRA_006</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_017</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_002</t>
   </si>
   <si>
     <t>elc_wof_FRA_014</t>
@@ -1644,7 +1656,31 @@
     <t>e_w85995894-400_FRA,e_w85710783-400_FRA,e_w85203486-400_FRA</t>
   </si>
   <si>
-    <t>elc_wof_FRA_006</t>
+    <t>elc_wof_FRA_012</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w112342683-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_008</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_005</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_007</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_009</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_013</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w85995894-400_FRA</t>
   </si>
   <si>
     <t>elc_wof_FRA_010</t>
@@ -1653,33 +1689,6 @@
     <t>elc_wof_FRA_001</t>
   </si>
   <si>
-    <t>elc_wof_FRA_017</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_003</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_002</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_015</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_007</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_008</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_005</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_012</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w112342683-400_FRA</t>
-  </si>
-  <si>
     <t>elc_wof_FRA_016</t>
   </si>
   <si>
@@ -1692,15 +1701,6 @@
     <t>elc_wof_FRA_004</t>
   </si>
   <si>
-    <t>elc_wof_FRA_013</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w85995894-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_009</t>
-  </si>
-  <si>
     <t>e_won_FRA_001</t>
   </si>
   <si>
@@ -1971,6 +1971,9 @@
     <t>wind offshore resource in cluster 17</t>
   </si>
   <si>
+    <t>~fi_t: UP</t>
+  </si>
+  <si>
     <t>en_gas_ccgt</t>
   </si>
   <si>
@@ -1992,7 +1995,7 @@
     <t>en_gas_turbine</t>
   </si>
   <si>
-    <t>en_gas_chp</t>
+    <t>en_chp_gas_cc_ext</t>
   </si>
   <si>
     <t>HET</t>
@@ -2001,7 +2004,7 @@
     <t>ncap_chpr</t>
   </si>
   <si>
-    <t>en_gas_fuelcell</t>
+    <t>ncap_ceh</t>
   </si>
   <si>
     <t>en_gas_ccs</t>
@@ -2022,15 +2025,6 @@
     <t>en_coal_igcc</t>
   </si>
   <si>
-    <t>en_coal_ccs</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_ccs</t>
-  </si>
-  <si>
-    <t>en_coal_oxyfuel_ccs</t>
-  </si>
-  <si>
     <t>en_nuclear</t>
   </si>
   <si>
@@ -2043,22 +2037,37 @@
     <t>ncap_af</t>
   </si>
   <si>
-    <t>en_biomass_cofiring</t>
-  </si>
-  <si>
-    <t>en_biomass_chp</t>
-  </si>
-  <si>
-    <t>en_biomass_ccs</t>
-  </si>
-  <si>
-    <t>en_geothermal</t>
+    <t>en_chp_biomass_chips_ext</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs</t>
+  </si>
+  <si>
+    <t>HET,CO2Cap</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
     <t>CHP</t>
+  </si>
+  <si>
+    <t>HPL</t>
+  </si>
+  <si>
+    <t>season</t>
   </si>
   <si>
     <t>e_FR109-400_FRA,e_FR128-380_FRA,e_FR128-400_FRA,e_FR143-400_FRA,e_FR183-400_FRA,e_FR40-400_FRA,e_FR5-400_FRA,e_w118655802-400_FRA,e_w129378915-400_FRA,e_w133299582-400_FRA,e_w146449309-400_FRA,e_w225210595-400_FRA,e_w32196554-400_FRA,e_w49049745-380_FRA,e_w49049745-400_FRA,e_w761507281-400_FRA,e_w82949228-400_FRA,e_w82949240-400_FRA,e_w85605959-400_FRA</t>
@@ -3995,7 +4004,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -6796,7 +6805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88318C55-1C2B-4A73-90F3-DC4911C27D53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189A85CE-BCCC-4BB0-8E42-A19D57C50955}">
   <dimension ref="B9:BD40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7034,16 +7043,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99811888657672254</v>
+        <v>0.99760073307445152</v>
       </c>
       <c r="AB11">
-        <v>34.487079426754121</v>
+        <v>43.986560301722875</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7076,10 +7085,10 @@
         <v>421</v>
       </c>
       <c r="AO11">
-        <v>0.99739565808689357</v>
+        <v>0.99804245386379287</v>
       </c>
       <c r="AP11">
-        <v>47.746268406951614</v>
+        <v>35.888345830464296</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7109,13 +7118,13 @@
         <v>503</v>
       </c>
       <c r="BB11" t="s">
-        <v>504</v>
+        <v>361</v>
       </c>
       <c r="BC11">
-        <v>0.99579717949467605</v>
+        <v>0.98772606347662006</v>
       </c>
       <c r="BD11">
-        <v>77.051709264272191</v>
+        <v>225.02216959529935</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7180,16 +7189,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99796668524605581</v>
+        <v>0.99771094718615749</v>
       </c>
       <c r="AB12">
-        <v>37.277437155643319</v>
+        <v>41.965968253779806</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7219,13 +7228,13 @@
         <v>422</v>
       </c>
       <c r="AN12" t="s">
-        <v>343</v>
+        <v>423</v>
       </c>
       <c r="AO12">
-        <v>0.99724350262056138</v>
+        <v>0.9970097215210143</v>
       </c>
       <c r="AP12">
-        <v>50.535785289707377</v>
+        <v>54.82177211473752</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7252,16 +7261,16 @@
         <v>471</v>
       </c>
       <c r="BA12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BB12" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="BC12">
-        <v>0.98772606347662006</v>
+        <v>0.98065397607653604</v>
       </c>
       <c r="BD12">
-        <v>225.02216959529935</v>
+        <v>354.67710526350635</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7326,16 +7335,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.98282786238014608</v>
+        <v>0.99789185737427777</v>
       </c>
       <c r="AB13">
-        <v>314.82252303065502</v>
+        <v>38.649281471573786</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7362,16 +7371,16 @@
         <v>368</v>
       </c>
       <c r="AM13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO13">
-        <v>0.99816665404006633</v>
+        <v>0.99712165362217109</v>
       </c>
       <c r="AP13">
-        <v>33.611342598783573</v>
+        <v>52.769683593529635</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -7398,16 +7407,16 @@
         <v>473</v>
       </c>
       <c r="BA13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BB13" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="BC13">
-        <v>0.99863344496525219</v>
+        <v>0.98299346510038665</v>
       </c>
       <c r="BD13">
-        <v>25.053508970375976</v>
+        <v>311.78647315957892</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7472,16 +7481,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="Z14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99778628553476412</v>
+        <v>0.99603217268588318</v>
       </c>
       <c r="AB14">
-        <v>40.584765195991288</v>
+        <v>72.743500758808537</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -7508,16 +7517,16 @@
         <v>370</v>
       </c>
       <c r="AM14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO14">
-        <v>0.98918214360614543</v>
+        <v>0.99650877616217826</v>
       </c>
       <c r="AP14">
-        <v>198.32736722066633</v>
+        <v>64.005770360066109</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -7544,16 +7553,16 @@
         <v>475</v>
       </c>
       <c r="BA14" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BB14" t="s">
-        <v>437</v>
+        <v>361</v>
       </c>
       <c r="BC14">
-        <v>0.99536965776860997</v>
+        <v>0.98380382000267219</v>
       </c>
       <c r="BD14">
-        <v>84.889607575482927</v>
+        <v>296.92996661767575</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7618,16 +7627,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="Z15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.99760073307445152</v>
+        <v>0.99851075781809495</v>
       </c>
       <c r="AB15">
-        <v>43.986560301722875</v>
+        <v>27.30277333492506</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -7654,10 +7663,10 @@
         <v>372</v>
       </c>
       <c r="AM15" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN15" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO15">
         <v>0.99765345145842399</v>
@@ -7690,16 +7699,16 @@
         <v>477</v>
       </c>
       <c r="BA15" t="s">
+        <v>507</v>
+      </c>
+      <c r="BB15" t="s">
         <v>508</v>
       </c>
-      <c r="BB15" t="s">
-        <v>349</v>
-      </c>
       <c r="BC15">
-        <v>0.98065397607653604</v>
+        <v>0.99579717949467605</v>
       </c>
       <c r="BD15">
-        <v>354.67710526350635</v>
+        <v>77.051709264272191</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7764,16 +7773,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="Z16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.99771094718615749</v>
+        <v>0.99778628553476412</v>
       </c>
       <c r="AB16">
-        <v>41.965968253779806</v>
+        <v>40.584765195991288</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -7800,10 +7809,10 @@
         <v>374</v>
       </c>
       <c r="AM16" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AO16">
         <v>0.99756226071513543</v>
@@ -7839,13 +7848,13 @@
         <v>509</v>
       </c>
       <c r="BB16" t="s">
-        <v>337</v>
+        <v>510</v>
       </c>
       <c r="BC16">
-        <v>0.98299346510038665</v>
+        <v>0.9911086854453236</v>
       </c>
       <c r="BD16">
-        <v>311.78647315957892</v>
+        <v>163.0074335024004</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7910,16 +7919,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="Z17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.99789185737427777</v>
+        <v>0.99700804792465858</v>
       </c>
       <c r="AB17">
-        <v>38.649281471573786</v>
+        <v>54.85245471459325</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -7946,10 +7955,10 @@
         <v>376</v>
       </c>
       <c r="AM17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN17" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO17">
         <v>0.99719673945277698</v>
@@ -7982,16 +7991,16 @@
         <v>481</v>
       </c>
       <c r="BA17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="BB17" t="s">
-        <v>337</v>
+        <v>459</v>
       </c>
       <c r="BC17">
-        <v>0.98380382000267219</v>
+        <v>0.99850355933568513</v>
       </c>
       <c r="BD17">
-        <v>296.92996661767575</v>
+        <v>27.434745512439168</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8056,16 +8065,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Z18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.99603217268588318</v>
+        <v>0.99768389076925323</v>
       </c>
       <c r="AB18">
-        <v>72.743500758808537</v>
+        <v>42.462002563689758</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8092,16 +8101,16 @@
         <v>378</v>
       </c>
       <c r="AM18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN18" t="s">
-        <v>351</v>
+        <v>435</v>
       </c>
       <c r="AO18">
-        <v>0.99778204559874861</v>
+        <v>0.99808767667924114</v>
       </c>
       <c r="AP18">
-        <v>40.662497356275288</v>
+        <v>35.059260880579068</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8128,16 +8137,16 @@
         <v>483</v>
       </c>
       <c r="BA18" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="BB18" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="BC18">
-        <v>0.99093284602677045</v>
+        <v>0.97849331544243145</v>
       </c>
       <c r="BD18">
-        <v>166.23115617587521</v>
+        <v>394.28921688875596</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8202,16 +8211,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="Z19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99851075781809495</v>
+        <v>0.99678800794697264</v>
       </c>
       <c r="AB19">
-        <v>27.30277333492506</v>
+        <v>58.88652097216788</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8238,16 +8247,16 @@
         <v>380</v>
       </c>
       <c r="AM19" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AN19" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="AO19">
-        <v>0.99784198809622926</v>
+        <v>0.99789185043252149</v>
       </c>
       <c r="AP19">
-        <v>39.563551569129636</v>
+        <v>38.649408737106661</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8274,16 +8283,16 @@
         <v>485</v>
       </c>
       <c r="BA19" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="BB19" t="s">
-        <v>426</v>
+        <v>356</v>
       </c>
       <c r="BC19">
-        <v>0.99703425039877824</v>
+        <v>0.99093284602677045</v>
       </c>
       <c r="BD19">
-        <v>54.372076022398424</v>
+        <v>166.23115617587521</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8348,16 +8357,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="Z20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.99807548905811494</v>
+        <v>0.9967781407005234</v>
       </c>
       <c r="AB20">
-        <v>35.282700601226196</v>
+        <v>59.06742049040524</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -8384,16 +8393,16 @@
         <v>382</v>
       </c>
       <c r="AM20" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN20" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO20">
-        <v>0.99746485747937264</v>
+        <v>0.99739565808689357</v>
       </c>
       <c r="AP20">
-        <v>46.477612878168472</v>
+        <v>47.746268406951614</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -8420,16 +8429,16 @@
         <v>487</v>
       </c>
       <c r="BA20" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="BB20" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="BC20">
-        <v>0.99850355933568513</v>
+        <v>0.99703425039877824</v>
       </c>
       <c r="BD20">
-        <v>27.434745512439168</v>
+        <v>54.372076022398424</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8494,16 +8503,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="Z21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA21">
-        <v>0.99812782016534596</v>
+        <v>0.9980700000086743</v>
       </c>
       <c r="AB21">
-        <v>34.323296968657118</v>
+        <v>35.38333317430456</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -8530,16 +8539,16 @@
         <v>384</v>
       </c>
       <c r="AM21" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN21" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO21">
-        <v>0.99808767667924114</v>
+        <v>0.99648757714768388</v>
       </c>
       <c r="AP21">
-        <v>35.059260880579068</v>
+        <v>64.394418959127933</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -8566,16 +8575,16 @@
         <v>489</v>
       </c>
       <c r="BA21" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="BB21" t="s">
-        <v>337</v>
+        <v>435</v>
       </c>
       <c r="BC21">
-        <v>0.97849331544243145</v>
+        <v>0.99440716597809709</v>
       </c>
       <c r="BD21">
-        <v>394.28921688875596</v>
+        <v>102.53529040155342</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8640,16 +8649,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="Z22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA22">
-        <v>0.99873749004157653</v>
+        <v>0.99767867140691957</v>
       </c>
       <c r="AB22">
-        <v>23.146015904430175</v>
+        <v>42.55769087314146</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -8676,16 +8685,16 @@
         <v>386</v>
       </c>
       <c r="AM22" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN22" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AO22">
-        <v>0.99804245386379287</v>
+        <v>0.9988955767418648</v>
       </c>
       <c r="AP22">
-        <v>35.888345830464296</v>
+        <v>20.247759732477729</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -8712,16 +8721,16 @@
         <v>491</v>
       </c>
       <c r="BA22" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="BB22" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="BC22">
-        <v>0.9911086854453236</v>
+        <v>0.99419387483019273</v>
       </c>
       <c r="BD22">
-        <v>163.0074335024004</v>
+        <v>106.44562811313425</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8786,16 +8795,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Z23" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA23">
-        <v>0.99820251673680249</v>
+        <v>0.9987681422400152</v>
       </c>
       <c r="AB23">
-        <v>32.953859825288589</v>
+        <v>22.584058933054997</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -8822,16 +8831,16 @@
         <v>388</v>
       </c>
       <c r="AM23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN23" t="s">
-        <v>443</v>
+        <v>361</v>
       </c>
       <c r="AO23">
-        <v>0.9970097215210143</v>
+        <v>0.99512455257015542</v>
       </c>
       <c r="AP23">
-        <v>54.82177211473752</v>
+        <v>89.383202880483722</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -8858,16 +8867,16 @@
         <v>493</v>
       </c>
       <c r="BA23" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="BB23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="BC23">
-        <v>0.98973273644055293</v>
+        <v>0.99863344496525219</v>
       </c>
       <c r="BD23">
-        <v>188.23316525652893</v>
+        <v>25.053508970375976</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8932,16 +8941,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA24">
-        <v>0.99719319688440999</v>
+        <v>0.99807548905811494</v>
       </c>
       <c r="AB24">
-        <v>51.458057119150247</v>
+        <v>35.282700601226196</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -8974,10 +8983,10 @@
         <v>445</v>
       </c>
       <c r="AO24">
-        <v>0.9979962856207204</v>
+        <v>0.99854067090268706</v>
       </c>
       <c r="AP24">
-        <v>36.734763620126827</v>
+        <v>26.754366784069809</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9004,16 +9013,16 @@
         <v>495</v>
       </c>
       <c r="BA24" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="BB24" t="s">
-        <v>519</v>
+        <v>468</v>
       </c>
       <c r="BC24">
-        <v>0.98905121950258512</v>
+        <v>0.99536965776860997</v>
       </c>
       <c r="BD24">
-        <v>200.72764245260552</v>
+        <v>84.889607575482927</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9078,16 +9087,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="Z25" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA25">
-        <v>0.99700804792465858</v>
+        <v>0.99812782016534596</v>
       </c>
       <c r="AB25">
-        <v>54.85245471459325</v>
+        <v>34.323296968657118</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9120,10 +9129,10 @@
         <v>447</v>
       </c>
       <c r="AO25">
-        <v>0.99648757714768388</v>
+        <v>0.99742029995821757</v>
       </c>
       <c r="AP25">
-        <v>64.394418959127933</v>
+        <v>47.294500766011943</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9153,13 +9162,13 @@
         <v>520</v>
       </c>
       <c r="BB25" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="BC25">
-        <v>0.99441277928791383</v>
+        <v>0.98973273644055293</v>
       </c>
       <c r="BD25">
-        <v>102.43237972158009</v>
+        <v>188.23316525652893</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9224,16 +9233,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="Z26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA26">
-        <v>0.99775269613274897</v>
+        <v>0.99873749004157653</v>
       </c>
       <c r="AB26">
-        <v>41.200570899602418</v>
+        <v>23.146015904430175</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9263,13 +9272,13 @@
         <v>448</v>
       </c>
       <c r="AN26" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AO26">
-        <v>0.9988955767418648</v>
+        <v>0.99817633840500364</v>
       </c>
       <c r="AP26">
-        <v>20.247759732477729</v>
+        <v>33.433795908267413</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9302,10 +9311,10 @@
         <v>522</v>
       </c>
       <c r="BC26">
-        <v>0.99419387483019273</v>
+        <v>0.98905121950258512</v>
       </c>
       <c r="BD26">
-        <v>106.44562811313425</v>
+        <v>200.72764245260552</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9370,16 +9379,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA27">
-        <v>0.99737794036187466</v>
+        <v>0.99820251673680249</v>
       </c>
       <c r="AB27">
-        <v>48.07109336563137</v>
+        <v>32.953859825288589</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -9406,16 +9415,16 @@
         <v>396</v>
       </c>
       <c r="AM27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN27" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="AO27">
-        <v>0.99512455257015542</v>
+        <v>0.99724350262056138</v>
       </c>
       <c r="AP27">
-        <v>89.383202880483722</v>
+        <v>50.535785289707377</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -9445,13 +9454,13 @@
         <v>523</v>
       </c>
       <c r="BB27" t="s">
-        <v>439</v>
+        <v>361</v>
       </c>
       <c r="BC27">
-        <v>0.99440716597809709</v>
+        <v>0.99441277928791383</v>
       </c>
       <c r="BD27">
-        <v>102.53529040155342</v>
+        <v>102.43237972158009</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9516,16 +9525,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Z28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA28">
-        <v>0.99790569401710338</v>
+        <v>0.99719319688440999</v>
       </c>
       <c r="AB28">
-        <v>38.395609686438895</v>
+        <v>51.458057119150247</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -9552,16 +9561,16 @@
         <v>398</v>
       </c>
       <c r="AM28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO28">
-        <v>0.99518717763850095</v>
+        <v>0.99816665404006633</v>
       </c>
       <c r="AP28">
-        <v>88.235076627481902</v>
+        <v>33.611342598783573</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9626,16 +9635,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="Z29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA29">
-        <v>0.99777826206332976</v>
+        <v>0.99754382386829921</v>
       </c>
       <c r="AB29">
-        <v>40.731862172288039</v>
+        <v>45.029895747848158</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -9662,16 +9671,16 @@
         <v>400</v>
       </c>
       <c r="AM29" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN29" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO29">
-        <v>0.99810940368916978</v>
+        <v>0.98918214360614543</v>
       </c>
       <c r="AP29">
-        <v>34.660932365220965</v>
+        <v>198.32736722066633</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9736,16 +9745,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="Z30" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA30">
-        <v>0.99764504969214185</v>
+        <v>0.99783160220227129</v>
       </c>
       <c r="AB30">
-        <v>43.174088977399613</v>
+        <v>39.753959625025857</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -9772,16 +9781,16 @@
         <v>402</v>
       </c>
       <c r="AM30" t="s">
+        <v>455</v>
+      </c>
+      <c r="AN30" t="s">
         <v>454</v>
       </c>
-      <c r="AN30" t="s">
-        <v>455</v>
-      </c>
       <c r="AO30">
-        <v>0.99586599256158292</v>
+        <v>0.99857814187768335</v>
       </c>
       <c r="AP30">
-        <v>75.790136370979724</v>
+        <v>26.067398909139413</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9846,16 +9855,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="Z31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA31">
-        <v>0.99738643688349482</v>
+        <v>0.99764504969214185</v>
       </c>
       <c r="AB31">
-        <v>47.915323802595424</v>
+        <v>43.174088977399613</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -9888,10 +9897,10 @@
         <v>457</v>
       </c>
       <c r="AO31">
-        <v>0.99742293468348531</v>
+        <v>0.99586599256158292</v>
       </c>
       <c r="AP31">
-        <v>47.246197469436119</v>
+        <v>75.790136370979724</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9956,16 +9965,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Z32" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA32">
-        <v>0.99757113701984168</v>
+        <v>0.99775269613274897</v>
       </c>
       <c r="AB32">
-        <v>44.529154636235894</v>
+        <v>41.200570899602418</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -9995,13 +10004,13 @@
         <v>458</v>
       </c>
       <c r="AN32" t="s">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="AO32">
-        <v>0.99857814187768335</v>
+        <v>0.99742293468348531</v>
       </c>
       <c r="AP32">
-        <v>26.067398909139413</v>
+        <v>47.246197469436119</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10066,16 +10075,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="Z33" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA33">
-        <v>0.9967781407005234</v>
+        <v>0.99737794036187466</v>
       </c>
       <c r="AB33">
-        <v>59.06742049040524</v>
+        <v>48.07109336563137</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10102,16 +10111,16 @@
         <v>408</v>
       </c>
       <c r="AM33" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN33" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="AO33">
-        <v>0.99789185043252149</v>
+        <v>0.99518717763850095</v>
       </c>
       <c r="AP33">
-        <v>38.649408737106661</v>
+        <v>88.235076627481902</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10176,16 +10185,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="Z34" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA34">
-        <v>0.99754382386829921</v>
+        <v>0.99790569401710338</v>
       </c>
       <c r="AB34">
-        <v>45.029895747848158</v>
+        <v>38.395609686438895</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -10215,13 +10224,13 @@
         <v>461</v>
       </c>
       <c r="AN34" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="AO34">
-        <v>0.99742029995821757</v>
+        <v>0.99810940368916978</v>
       </c>
       <c r="AP34">
-        <v>47.294500766011943</v>
+        <v>34.660932365220965</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10286,16 +10295,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="Z35" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA35">
-        <v>0.99783160220227129</v>
+        <v>0.99777826206332976</v>
       </c>
       <c r="AB35">
-        <v>39.753959625025857</v>
+        <v>40.731862172288039</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -10322,16 +10331,16 @@
         <v>412</v>
       </c>
       <c r="AM35" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN35" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="AO35">
-        <v>0.99817633840500364</v>
+        <v>0.9979962856207204</v>
       </c>
       <c r="AP35">
-        <v>33.433795908267413</v>
+        <v>36.734763620126827</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10396,16 +10405,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="Z36" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA36">
-        <v>0.99768389076925323</v>
+        <v>0.99811888657672254</v>
       </c>
       <c r="AB36">
-        <v>42.462002563689758</v>
+        <v>34.487079426754121</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -10435,13 +10444,13 @@
         <v>464</v>
       </c>
       <c r="AN36" t="s">
-        <v>460</v>
+        <v>358</v>
       </c>
       <c r="AO36">
-        <v>0.99712165362217109</v>
+        <v>0.99778204559874861</v>
       </c>
       <c r="AP36">
-        <v>52.769683593529635</v>
+        <v>40.662497356275288</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10506,16 +10515,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="Z37" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AA37">
-        <v>0.99678800794697264</v>
+        <v>0.99796668524605581</v>
       </c>
       <c r="AB37">
-        <v>58.88652097216788</v>
+        <v>37.277437155643319</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -10548,10 +10557,10 @@
         <v>466</v>
       </c>
       <c r="AO37">
-        <v>0.99650877616217826</v>
+        <v>0.99784198809622926</v>
       </c>
       <c r="AP37">
-        <v>64.005770360066109</v>
+        <v>39.563551569129636</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10616,16 +10625,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="Z38" t="s">
         <v>361</v>
       </c>
       <c r="AA38">
-        <v>0.9980700000086743</v>
+        <v>0.98282786238014608</v>
       </c>
       <c r="AB38">
-        <v>35.38333317430456</v>
+        <v>314.82252303065502</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -10658,10 +10667,10 @@
         <v>468</v>
       </c>
       <c r="AO38">
-        <v>0.99854067090268706</v>
+        <v>0.99746485747937264</v>
       </c>
       <c r="AP38">
-        <v>26.754366784069809</v>
+        <v>46.477612878168472</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10726,16 +10735,16 @@
         <v>329</v>
       </c>
       <c r="Y39" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="Z39" t="s">
         <v>362</v>
       </c>
       <c r="AA39">
-        <v>0.99767867140691957</v>
+        <v>0.99738643688349482</v>
       </c>
       <c r="AB39">
-        <v>42.55769087314146</v>
+        <v>47.915323802595424</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10800,16 +10809,16 @@
         <v>331</v>
       </c>
       <c r="Y40" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="Z40" t="s">
         <v>363</v>
       </c>
       <c r="AA40">
-        <v>0.9987681422400152</v>
+        <v>0.99757113701984168</v>
       </c>
       <c r="AB40">
-        <v>22.584058933054997</v>
+        <v>44.529154636235894</v>
       </c>
     </row>
   </sheetData>
@@ -10818,7 +10827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752F1278-533E-4A35-BCAD-71005CB9BB87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6705CB-44D2-47CC-8BF8-B76DCF9CE440}">
   <dimension ref="B9:Z38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10930,7 +10939,7 @@
         <v>524</v>
       </c>
       <c r="K11" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="L11">
         <v>7.5214385218371174</v>
@@ -10963,7 +10972,7 @@
         <v>580</v>
       </c>
       <c r="X11" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="Y11">
         <v>38.3018</v>
@@ -10998,7 +11007,7 @@
         <v>526</v>
       </c>
       <c r="K12" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="L12">
         <v>8.5464211426904182</v>
@@ -11031,7 +11040,7 @@
         <v>582</v>
       </c>
       <c r="X12" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="Y12">
         <v>9.3112499999999994</v>
@@ -11066,7 +11075,7 @@
         <v>528</v>
       </c>
       <c r="K13" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="L13">
         <v>1.5340845206129941</v>
@@ -11099,7 +11108,7 @@
         <v>584</v>
       </c>
       <c r="X13" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="Y13">
         <v>9.5287500000000005</v>
@@ -11134,7 +11143,7 @@
         <v>530</v>
       </c>
       <c r="K14" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="L14">
         <v>17.642367792804524</v>
@@ -11167,7 +11176,7 @@
         <v>586</v>
       </c>
       <c r="X14" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="Y14">
         <v>2.1749999999999999E-2</v>
@@ -11202,7 +11211,7 @@
         <v>532</v>
       </c>
       <c r="K15" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L15">
         <v>3.7020770759557711</v>
@@ -11235,7 +11244,7 @@
         <v>588</v>
       </c>
       <c r="X15" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Y15">
         <v>8.2590000000000003</v>
@@ -11270,7 +11279,7 @@
         <v>534</v>
       </c>
       <c r="K16" t="s">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="L16">
         <v>28.142418601835601</v>
@@ -11303,7 +11312,7 @@
         <v>590</v>
       </c>
       <c r="X16" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Y16">
         <v>0.40575</v>
@@ -11338,7 +11347,7 @@
         <v>536</v>
       </c>
       <c r="K17" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="L17">
         <v>52.588193451360631</v>
@@ -11371,7 +11380,7 @@
         <v>592</v>
       </c>
       <c r="X17" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Y17">
         <v>6.4290000000000003</v>
@@ -11406,7 +11415,7 @@
         <v>538</v>
       </c>
       <c r="K18" t="s">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="L18">
         <v>21.66872817402496</v>
@@ -11439,7 +11448,7 @@
         <v>594</v>
       </c>
       <c r="X18" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Y18">
         <v>0.10199999999999999</v>
@@ -11474,7 +11483,7 @@
         <v>540</v>
       </c>
       <c r="K19" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="L19">
         <v>75.448981284454376</v>
@@ -11507,7 +11516,7 @@
         <v>596</v>
       </c>
       <c r="X19" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="Y19">
         <v>27.910499999999999</v>
@@ -11542,7 +11551,7 @@
         <v>542</v>
       </c>
       <c r="K20" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="L20">
         <v>15.373849239963436</v>
@@ -11575,7 +11584,7 @@
         <v>598</v>
       </c>
       <c r="X20" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="Y20">
         <v>2.7322500000000001</v>
@@ -11610,7 +11619,7 @@
         <v>544</v>
       </c>
       <c r="K21" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="L21">
         <v>20.923088433115996</v>
@@ -11643,7 +11652,7 @@
         <v>600</v>
       </c>
       <c r="X21" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="Y21">
         <v>69.386250000000004</v>
@@ -11678,7 +11687,7 @@
         <v>546</v>
       </c>
       <c r="K22" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="L22">
         <v>10.348692721070078</v>
@@ -11711,7 +11720,7 @@
         <v>602</v>
       </c>
       <c r="X22" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="Y22">
         <v>79.72475</v>
@@ -11746,7 +11755,7 @@
         <v>548</v>
       </c>
       <c r="K23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L23">
         <v>30.731418987588004</v>
@@ -11779,7 +11788,7 @@
         <v>604</v>
       </c>
       <c r="X23" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="Y23">
         <v>19.849499999999999</v>
@@ -11814,7 +11823,7 @@
         <v>550</v>
       </c>
       <c r="K24" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="L24">
         <v>6.8734480919946561</v>
@@ -11847,7 +11856,7 @@
         <v>606</v>
       </c>
       <c r="X24" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="Y24">
         <v>34.275750000000002</v>
@@ -11882,7 +11891,7 @@
         <v>552</v>
       </c>
       <c r="K25" t="s">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="L25">
         <v>44.470842554915507</v>
@@ -11915,7 +11924,7 @@
         <v>608</v>
       </c>
       <c r="X25" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Y25">
         <v>88.0535</v>
@@ -11950,7 +11959,7 @@
         <v>554</v>
       </c>
       <c r="K26" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="L26">
         <v>94.751954680638562</v>
@@ -11983,7 +11992,7 @@
         <v>610</v>
       </c>
       <c r="X26" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="Y26">
         <v>42.073500000000003</v>
@@ -12018,7 +12027,7 @@
         <v>556</v>
       </c>
       <c r="K27" t="s">
-        <v>434</v>
+        <v>465</v>
       </c>
       <c r="L27">
         <v>32.871207794729088</v>
@@ -12051,7 +12060,7 @@
         <v>612</v>
       </c>
       <c r="X27" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="Y27">
         <v>65.507249999999999</v>
@@ -12086,7 +12095,7 @@
         <v>558</v>
       </c>
       <c r="K28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L28">
         <v>113.99847062392492</v>
@@ -12121,7 +12130,7 @@
         <v>560</v>
       </c>
       <c r="K29" t="s">
-        <v>465</v>
+        <v>426</v>
       </c>
       <c r="L29">
         <v>18.2196769426582</v>
@@ -12156,7 +12165,7 @@
         <v>562</v>
       </c>
       <c r="K30" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="L30">
         <v>53.979644051935594</v>
@@ -12191,7 +12200,7 @@
         <v>564</v>
       </c>
       <c r="K31" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="L31">
         <v>17.215449395412726</v>
@@ -12226,7 +12235,7 @@
         <v>566</v>
       </c>
       <c r="K32" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="L32">
         <v>29.852997664126345</v>
@@ -12261,7 +12270,7 @@
         <v>568</v>
       </c>
       <c r="K33" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="L33">
         <v>33.097235865274165</v>
@@ -12296,7 +12305,7 @@
         <v>570</v>
       </c>
       <c r="K34" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L34">
         <v>50.818330360170975</v>
@@ -12331,7 +12340,7 @@
         <v>572</v>
       </c>
       <c r="K35" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="L35">
         <v>93.018246457332225</v>
@@ -12366,7 +12375,7 @@
         <v>574</v>
       </c>
       <c r="K36" t="s">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="L36">
         <v>48.982209359452717</v>
@@ -12401,7 +12410,7 @@
         <v>576</v>
       </c>
       <c r="K37" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L37">
         <v>22.316533209679985</v>
@@ -12436,7 +12445,7 @@
         <v>578</v>
       </c>
       <c r="K38" t="s">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="L38">
         <v>43.496233223332773</v>
@@ -12451,19 +12460,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25756439-EB5F-4164-9BA8-9A25FEA023D4}">
-  <dimension ref="B9:S128"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977F3ECF-2390-4CB5-B4CF-297D4A330281}">
+  <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:19">
+    <row r="9" spans="2:21">
       <c r="B9" t="s">
-        <v>235</v>
-      </c>
-      <c r="M9" t="s">
+        <v>614</v>
+      </c>
+      <c r="O9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="10" spans="2:19">
+    <row r="10" spans="2:21">
       <c r="B10" t="s">
         <v>166</v>
       </c>
@@ -12474,51 +12483,57 @@
         <v>236</v>
       </c>
       <c r="E10">
+        <v>2020</v>
+      </c>
+      <c r="F10">
         <v>2024</v>
       </c>
-      <c r="F10">
+      <c r="G10">
+        <v>2025</v>
+      </c>
+      <c r="H10">
         <v>2030</v>
       </c>
-      <c r="G10">
+      <c r="I10">
         <v>2035</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>2040</v>
       </c>
-      <c r="I10">
+      <c r="K10">
         <v>2045</v>
       </c>
-      <c r="J10">
+      <c r="L10">
         <v>2050</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>54</v>
       </c>
-      <c r="M10" t="s">
+      <c r="O10" t="s">
         <v>165</v>
       </c>
-      <c r="N10" t="s">
+      <c r="P10" t="s">
         <v>166</v>
       </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
         <v>167</v>
       </c>
-      <c r="P10" t="s">
+      <c r="R10" t="s">
         <v>168</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="S10" t="s">
         <v>169</v>
       </c>
-      <c r="R10" t="s">
+      <c r="T10" t="s">
         <v>170</v>
       </c>
-      <c r="S10" t="s">
+      <c r="U10" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="2:19">
+    <row r="11" spans="2:21">
       <c r="B11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
@@ -12526,40 +12541,40 @@
       <c r="D11" t="s">
         <v>19</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>941</v>
       </c>
-      <c r="G11">
+      <c r="I11">
         <v>941</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>941</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
+        <v>616</v>
+      </c>
+      <c r="O11" t="s">
+        <v>172</v>
+      </c>
+      <c r="P11" t="s">
         <v>615</v>
       </c>
-      <c r="M11" t="s">
-        <v>172</v>
-      </c>
-      <c r="N11" t="s">
-        <v>614</v>
-      </c>
-      <c r="P11" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>21</v>
-      </c>
       <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
         <v>274</v>
       </c>
-      <c r="S11" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19">
+      <c r="U11" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21">
       <c r="B12" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
@@ -12567,40 +12582,40 @@
       <c r="D12" t="s">
         <v>19</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>23.5</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>23.5</v>
       </c>
-      <c r="J12">
+      <c r="L12">
         <v>23.5</v>
       </c>
-      <c r="K12" t="s">
-        <v>616</v>
-      </c>
       <c r="M12" t="s">
+        <v>617</v>
+      </c>
+      <c r="O12" t="s">
         <v>172</v>
       </c>
-      <c r="N12" t="s">
-        <v>620</v>
-      </c>
       <c r="P12" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>21</v>
+        <v>621</v>
       </c>
       <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
         <v>274</v>
       </c>
-      <c r="S12" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19">
+      <c r="U12" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21">
       <c r="B13" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
@@ -12608,40 +12623,40 @@
       <c r="D13" t="s">
         <v>19</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.58899999999999997</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>0.54400000000000004</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>0.497</v>
       </c>
-      <c r="K13" t="s">
-        <v>617</v>
-      </c>
       <c r="M13" t="s">
+        <v>618</v>
+      </c>
+      <c r="O13" t="s">
+        <v>644</v>
+      </c>
+      <c r="P13" t="s">
+        <v>622</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>274</v>
+      </c>
+      <c r="U13" t="s">
         <v>643</v>
       </c>
-      <c r="N13" t="s">
-        <v>621</v>
-      </c>
-      <c r="P13" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" t="s">
-        <v>274</v>
-      </c>
-      <c r="S13" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19">
+    </row>
+    <row r="14" spans="2:21">
       <c r="B14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
@@ -12649,40 +12664,40 @@
       <c r="D14" t="s">
         <v>19</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.59</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>0.61</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>0.61</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>145</v>
       </c>
-      <c r="M14" t="s">
+      <c r="O14" t="s">
         <v>172</v>
       </c>
-      <c r="N14" t="s">
-        <v>624</v>
-      </c>
       <c r="P14" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>21</v>
+        <v>626</v>
       </c>
       <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
         <v>274</v>
       </c>
-      <c r="S14" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19">
+      <c r="U14" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21">
       <c r="B15" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -12708,31 +12723,37 @@
       <c r="J15">
         <v>30</v>
       </c>
-      <c r="K15" t="s">
-        <v>618</v>
+      <c r="K15">
+        <v>30</v>
+      </c>
+      <c r="L15">
+        <v>30</v>
       </c>
       <c r="M15" t="s">
+        <v>619</v>
+      </c>
+      <c r="O15" t="s">
         <v>172</v>
       </c>
-      <c r="N15" t="s">
-        <v>625</v>
-      </c>
       <c r="P15" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>21</v>
+        <v>628</v>
       </c>
       <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
         <v>274</v>
       </c>
-      <c r="S15" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19">
+      <c r="U15" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21">
       <c r="B16" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -12758,31 +12779,37 @@
       <c r="J16">
         <v>3</v>
       </c>
-      <c r="K16" t="s">
-        <v>619</v>
+      <c r="K16">
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <v>3</v>
       </c>
       <c r="M16" t="s">
+        <v>620</v>
+      </c>
+      <c r="O16" t="s">
         <v>172</v>
       </c>
-      <c r="N16" t="s">
-        <v>627</v>
-      </c>
       <c r="P16" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
+        <v>629</v>
       </c>
       <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
         <v>274</v>
       </c>
-      <c r="S16" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="17" spans="2:19">
+      <c r="U16" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21">
       <c r="B17" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -12790,40 +12817,40 @@
       <c r="D17" t="s">
         <v>19</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>470.5</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>470.5</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>470.5</v>
       </c>
-      <c r="K17" t="s">
-        <v>615</v>
-      </c>
       <c r="M17" t="s">
+        <v>616</v>
+      </c>
+      <c r="O17" t="s">
         <v>172</v>
       </c>
-      <c r="N17" t="s">
-        <v>628</v>
-      </c>
       <c r="P17" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>21</v>
+        <v>630</v>
       </c>
       <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
         <v>274</v>
       </c>
-      <c r="S17" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="18" spans="2:19">
+      <c r="U17" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21">
       <c r="B18" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C18" t="s">
         <v>33</v>
@@ -12831,40 +12858,40 @@
       <c r="D18" t="s">
         <v>19</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>18.8</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>18.8</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>18.8</v>
       </c>
-      <c r="K18" t="s">
-        <v>616</v>
-      </c>
       <c r="M18" t="s">
+        <v>617</v>
+      </c>
+      <c r="O18" t="s">
         <v>172</v>
       </c>
-      <c r="N18" t="s">
-        <v>629</v>
-      </c>
       <c r="P18" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>21</v>
+        <v>631</v>
       </c>
       <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
         <v>274</v>
       </c>
-      <c r="S18" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="19" spans="2:19">
+      <c r="U18" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21">
       <c r="B19" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -12872,40 +12899,40 @@
       <c r="D19" t="s">
         <v>19</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>1.9279999999999999</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>1.9279999999999999</v>
       </c>
-      <c r="J19">
+      <c r="L19">
         <v>1.9279999999999999</v>
       </c>
-      <c r="K19" t="s">
-        <v>617</v>
-      </c>
       <c r="M19" t="s">
+        <v>618</v>
+      </c>
+      <c r="O19" t="s">
         <v>172</v>
       </c>
-      <c r="N19" t="s">
-        <v>630</v>
-      </c>
       <c r="P19" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>21</v>
+        <v>632</v>
       </c>
       <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
         <v>274</v>
       </c>
-      <c r="S19" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="20" spans="2:19">
+      <c r="U19" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21">
       <c r="B20" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
@@ -12913,40 +12940,40 @@
       <c r="D20" t="s">
         <v>19</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.41</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>0.42</v>
       </c>
-      <c r="J20">
+      <c r="L20">
         <v>0.42</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>145</v>
       </c>
-      <c r="M20" t="s">
+      <c r="O20" t="s">
         <v>172</v>
       </c>
-      <c r="N20" t="s">
-        <v>631</v>
-      </c>
       <c r="P20" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>21</v>
+        <v>633</v>
       </c>
       <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
         <v>274</v>
       </c>
-      <c r="S20" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="21" spans="2:19">
+      <c r="U20" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21">
       <c r="B21" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -12972,31 +12999,37 @@
       <c r="J21">
         <v>30</v>
       </c>
-      <c r="K21" t="s">
-        <v>618</v>
+      <c r="K21">
+        <v>30</v>
+      </c>
+      <c r="L21">
+        <v>30</v>
       </c>
       <c r="M21" t="s">
+        <v>619</v>
+      </c>
+      <c r="O21" t="s">
         <v>172</v>
       </c>
-      <c r="N21" t="s">
-        <v>632</v>
-      </c>
       <c r="P21" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>21</v>
+        <v>634</v>
       </c>
       <c r="R21" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s">
         <v>274</v>
       </c>
-      <c r="S21" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="22" spans="2:19">
+      <c r="U21" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21">
       <c r="B22" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -13022,201 +13055,207 @@
       <c r="J22">
         <v>2</v>
       </c>
-      <c r="K22" t="s">
-        <v>619</v>
+      <c r="K22">
+        <v>2</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>172</v>
-      </c>
-      <c r="N22" t="s">
-        <v>633</v>
+        <v>620</v>
+      </c>
+      <c r="O22" t="s">
+        <v>644</v>
       </c>
       <c r="P22" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>21</v>
+        <v>636</v>
       </c>
       <c r="R22" t="s">
+        <v>10</v>
+      </c>
+      <c r="S22" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" t="s">
         <v>274</v>
       </c>
-      <c r="S22" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="23" spans="2:19">
+      <c r="U22" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21">
       <c r="B23" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
+        <v>623</v>
+      </c>
+      <c r="E23">
+        <v>967.6</v>
+      </c>
+      <c r="H23">
+        <v>912.6</v>
+      </c>
+      <c r="L23">
+        <v>879.6</v>
+      </c>
+      <c r="M23" t="s">
+        <v>616</v>
+      </c>
+      <c r="O23" t="s">
+        <v>645</v>
+      </c>
+      <c r="P23" t="s">
+        <v>637</v>
+      </c>
+      <c r="R23" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23" t="s">
+        <v>21</v>
+      </c>
+      <c r="T23" t="s">
+        <v>646</v>
+      </c>
+      <c r="U23" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="B24" t="s">
         <v>622</v>
-      </c>
-      <c r="E23">
-        <v>1223.3</v>
-      </c>
-      <c r="G23">
-        <v>1223.3</v>
-      </c>
-      <c r="J23">
-        <v>1223.3</v>
-      </c>
-      <c r="K23" t="s">
-        <v>615</v>
-      </c>
-      <c r="M23" t="s">
-        <v>172</v>
-      </c>
-      <c r="N23" t="s">
-        <v>634</v>
-      </c>
-      <c r="P23" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>21</v>
-      </c>
-      <c r="R23" t="s">
-        <v>274</v>
-      </c>
-      <c r="S23" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="24" spans="2:19">
-      <c r="B24" t="s">
-        <v>621</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
       </c>
       <c r="D24" t="s">
+        <v>623</v>
+      </c>
+      <c r="E24">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="H24">
+        <v>30.6</v>
+      </c>
+      <c r="L24">
+        <v>28.6</v>
+      </c>
+      <c r="M24" t="s">
+        <v>617</v>
+      </c>
+      <c r="O24" t="s">
+        <v>645</v>
+      </c>
+      <c r="P24" t="s">
+        <v>638</v>
+      </c>
+      <c r="R24" t="s">
+        <v>10</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" t="s">
+        <v>646</v>
+      </c>
+      <c r="U24" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21">
+      <c r="B25" t="s">
         <v>622</v>
-      </c>
-      <c r="E24">
-        <v>37.6</v>
-      </c>
-      <c r="G24">
-        <v>37.6</v>
-      </c>
-      <c r="J24">
-        <v>37.6</v>
-      </c>
-      <c r="K24" t="s">
-        <v>616</v>
-      </c>
-      <c r="M24" t="s">
-        <v>172</v>
-      </c>
-      <c r="N24" t="s">
-        <v>635</v>
-      </c>
-      <c r="P24" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" t="s">
-        <v>274</v>
-      </c>
-      <c r="S24" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="25" spans="2:19">
-      <c r="B25" t="s">
-        <v>621</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
       </c>
       <c r="D25" t="s">
+        <v>623</v>
+      </c>
+      <c r="E25">
+        <v>1.3</v>
+      </c>
+      <c r="H25">
+        <v>1.3</v>
+      </c>
+      <c r="L25">
+        <v>1.2</v>
+      </c>
+      <c r="M25" t="s">
+        <v>618</v>
+      </c>
+      <c r="O25" t="s">
+        <v>645</v>
+      </c>
+      <c r="P25" t="s">
+        <v>639</v>
+      </c>
+      <c r="R25" t="s">
+        <v>10</v>
+      </c>
+      <c r="S25" t="s">
+        <v>21</v>
+      </c>
+      <c r="T25" t="s">
+        <v>274</v>
+      </c>
+      <c r="U25" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21">
+      <c r="B26" t="s">
         <v>622</v>
-      </c>
-      <c r="E25">
-        <v>0.69399999999999995</v>
-      </c>
-      <c r="G25">
-        <v>0.69399999999999995</v>
-      </c>
-      <c r="J25">
-        <v>0.69399999999999995</v>
-      </c>
-      <c r="K25" t="s">
-        <v>617</v>
-      </c>
-      <c r="M25" t="s">
-        <v>172</v>
-      </c>
-      <c r="N25" t="s">
-        <v>636</v>
-      </c>
-      <c r="P25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" t="s">
-        <v>274</v>
-      </c>
-      <c r="S25" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19">
-      <c r="B26" t="s">
-        <v>621</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
       </c>
       <c r="D26" t="s">
+        <v>623</v>
+      </c>
+      <c r="E26">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H26">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="L26">
+        <v>0.6</v>
+      </c>
+      <c r="M26" t="s">
+        <v>145</v>
+      </c>
+      <c r="O26" t="s">
+        <v>645</v>
+      </c>
+      <c r="P26" t="s">
+        <v>640</v>
+      </c>
+      <c r="R26" t="s">
+        <v>10</v>
+      </c>
+      <c r="S26" t="s">
+        <v>21</v>
+      </c>
+      <c r="T26" t="s">
+        <v>274</v>
+      </c>
+      <c r="U26" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21">
+      <c r="B27" t="s">
         <v>622</v>
-      </c>
-      <c r="E26">
-        <v>0.53300000000000003</v>
-      </c>
-      <c r="G26">
-        <v>0.54600000000000004</v>
-      </c>
-      <c r="J26">
-        <v>0.54600000000000004</v>
-      </c>
-      <c r="K26" t="s">
-        <v>145</v>
-      </c>
-      <c r="M26" t="s">
-        <v>172</v>
-      </c>
-      <c r="N26" t="s">
-        <v>638</v>
-      </c>
-      <c r="P26" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" t="s">
-        <v>274</v>
-      </c>
-      <c r="S26" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19">
-      <c r="B27" t="s">
-        <v>621</v>
       </c>
       <c r="C27" t="s">
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E27">
         <v>25</v>
@@ -13236,37 +13275,43 @@
       <c r="J27">
         <v>25</v>
       </c>
-      <c r="K27" t="s">
-        <v>618</v>
+      <c r="K27">
+        <v>25</v>
+      </c>
+      <c r="L27">
+        <v>25</v>
       </c>
       <c r="M27" t="s">
+        <v>619</v>
+      </c>
+      <c r="O27" t="s">
+        <v>644</v>
+      </c>
+      <c r="P27" t="s">
+        <v>641</v>
+      </c>
+      <c r="R27" t="s">
+        <v>10</v>
+      </c>
+      <c r="S27" t="s">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s">
+        <v>274</v>
+      </c>
+      <c r="U27" t="s">
         <v>643</v>
       </c>
-      <c r="N27" t="s">
-        <v>639</v>
-      </c>
-      <c r="P27" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>21</v>
-      </c>
-      <c r="R27" t="s">
-        <v>274</v>
-      </c>
-      <c r="S27" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="28" spans="2:19">
+    </row>
+    <row r="28" spans="2:21">
       <c r="B28" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -13286,393 +13331,363 @@
       <c r="J28">
         <v>3</v>
       </c>
-      <c r="K28" t="s">
-        <v>619</v>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>172</v>
-      </c>
-      <c r="N28" t="s">
-        <v>640</v>
-      </c>
-      <c r="P28" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>21</v>
-      </c>
-      <c r="R28" t="s">
-        <v>274</v>
-      </c>
-      <c r="S28" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21">
       <c r="B29" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C29" t="s">
         <v>33</v>
       </c>
       <c r="D29" t="s">
+        <v>623</v>
+      </c>
+      <c r="E29">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="H29">
+        <v>0.5</v>
+      </c>
+      <c r="L29">
+        <v>0.45450000000000002</v>
+      </c>
+      <c r="M29" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21">
+      <c r="B30" t="s">
         <v>622</v>
-      </c>
-      <c r="E29">
-        <v>1.7134</v>
-      </c>
-      <c r="F29">
-        <v>1.7134</v>
-      </c>
-      <c r="G29">
-        <v>1.7134</v>
-      </c>
-      <c r="H29">
-        <v>1.7134</v>
-      </c>
-      <c r="I29">
-        <v>1.7134</v>
-      </c>
-      <c r="J29">
-        <v>1.7134</v>
-      </c>
-      <c r="K29" t="s">
-        <v>623</v>
-      </c>
-      <c r="M29" t="s">
-        <v>172</v>
-      </c>
-      <c r="N29" t="s">
-        <v>641</v>
-      </c>
-      <c r="P29" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>21</v>
-      </c>
-      <c r="R29" t="s">
-        <v>274</v>
-      </c>
-      <c r="S29" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="30" spans="2:19">
-      <c r="B30" t="s">
-        <v>624</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>623</v>
       </c>
       <c r="E30">
-        <v>4704.8</v>
-      </c>
-      <c r="G30">
-        <v>2352.4</v>
-      </c>
-      <c r="J30">
-        <v>2352.4</v>
-      </c>
-      <c r="K30" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="31" spans="2:19">
+        <v>-0.15</v>
+      </c>
+      <c r="H30">
+        <v>-0.15</v>
+      </c>
+      <c r="L30">
+        <v>-0.15</v>
+      </c>
+      <c r="M30" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21">
       <c r="B31" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31">
-        <v>94.1</v>
-      </c>
-      <c r="G31">
-        <v>47</v>
-      </c>
-      <c r="J31">
-        <v>47</v>
-      </c>
-      <c r="K31" t="s">
+        <v>627</v>
+      </c>
+      <c r="F31">
+        <v>2917</v>
+      </c>
+      <c r="I31">
+        <v>2681.7</v>
+      </c>
+      <c r="L31">
+        <v>2446.5</v>
+      </c>
+      <c r="M31" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="32" spans="2:19">
+    <row r="32" spans="2:21">
       <c r="B32" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="G32">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="J32">
-        <v>0.83299999999999996</v>
-      </c>
-      <c r="K32" t="s">
+        <v>627</v>
+      </c>
+      <c r="F32">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="I32">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="L32">
+        <v>61.2</v>
+      </c>
+      <c r="M32" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
+    <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C33" t="s">
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33">
-        <v>0.52</v>
-      </c>
-      <c r="G33">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="J33">
-        <v>0.6</v>
-      </c>
-      <c r="K33" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
+        <v>627</v>
+      </c>
+      <c r="F33">
+        <v>1.294</v>
+      </c>
+      <c r="I33">
+        <v>1.1060000000000001</v>
+      </c>
+      <c r="L33">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="M33" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C34" t="s">
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34">
-        <v>20</v>
+        <v>627</v>
       </c>
       <c r="F34">
-        <v>20</v>
-      </c>
-      <c r="G34">
-        <v>20</v>
-      </c>
-      <c r="H34">
-        <v>20</v>
+        <v>0.52</v>
       </c>
       <c r="I34">
-        <v>20</v>
-      </c>
-      <c r="J34">
-        <v>20</v>
-      </c>
-      <c r="K34" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
+        <v>0.54</v>
+      </c>
+      <c r="L34">
+        <v>0.54</v>
+      </c>
+      <c r="M34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C35" t="s">
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>627</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="J35">
-        <v>2</v>
-      </c>
-      <c r="K35" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35">
+        <v>30</v>
+      </c>
+      <c r="L35">
+        <v>30</v>
+      </c>
+      <c r="M35" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
+    <row r="36" spans="2:13">
       <c r="B36" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C36" t="s">
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E36">
-        <v>2917</v>
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
       </c>
       <c r="G36">
-        <v>2681.7</v>
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <v>4</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>2446.5</v>
-      </c>
-      <c r="K36" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
+        <v>4</v>
+      </c>
+      <c r="K36">
+        <v>4</v>
+      </c>
+      <c r="L36">
+        <v>4</v>
+      </c>
+      <c r="M36" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13">
       <c r="B37" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>626</v>
-      </c>
-      <c r="E37">
-        <v>70.599999999999994</v>
-      </c>
-      <c r="G37">
-        <v>65.900000000000006</v>
-      </c>
-      <c r="J37">
-        <v>61.2</v>
-      </c>
-      <c r="K37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37">
+        <v>1599.6</v>
+      </c>
+      <c r="I37">
+        <v>1599.6</v>
+      </c>
+      <c r="L37">
+        <v>1599.6</v>
+      </c>
+      <c r="M37" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
+    <row r="38" spans="2:13">
       <c r="B38" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>626</v>
-      </c>
-      <c r="E38">
-        <v>1.294</v>
-      </c>
-      <c r="G38">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="J38">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="K38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38">
+        <v>42.3</v>
+      </c>
+      <c r="I38">
+        <v>42.3</v>
+      </c>
+      <c r="L38">
+        <v>42.3</v>
+      </c>
+      <c r="M38" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
+    <row r="39" spans="2:13">
       <c r="B39" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>626</v>
-      </c>
-      <c r="E39">
-        <v>0.52</v>
-      </c>
-      <c r="G39">
-        <v>0.54</v>
-      </c>
-      <c r="J39">
-        <v>0.54</v>
-      </c>
-      <c r="K39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="I39">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="L39">
+        <v>2.3610000000000002</v>
+      </c>
+      <c r="M39" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13">
+      <c r="B40" t="s">
+        <v>628</v>
+      </c>
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40">
+        <v>0.39</v>
+      </c>
+      <c r="I40">
+        <v>0.39</v>
+      </c>
+      <c r="L40">
+        <v>0.39</v>
+      </c>
+      <c r="M40" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
-      <c r="B40" t="s">
-        <v>625</v>
-      </c>
-      <c r="C40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D40" t="s">
-        <v>626</v>
-      </c>
-      <c r="E40">
-        <v>30</v>
-      </c>
-      <c r="F40">
-        <v>30</v>
-      </c>
-      <c r="G40">
-        <v>30</v>
-      </c>
-      <c r="H40">
-        <v>30</v>
-      </c>
-      <c r="I40">
-        <v>30</v>
-      </c>
-      <c r="J40">
-        <v>30</v>
-      </c>
-      <c r="K40" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
+    <row r="41" spans="2:13">
       <c r="B41" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>626</v>
+        <v>19</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H41">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="J41">
-        <v>4</v>
-      </c>
-      <c r="K41" t="s">
+        <v>40</v>
+      </c>
+      <c r="K41">
+        <v>40</v>
+      </c>
+      <c r="L41">
+        <v>40</v>
+      </c>
+      <c r="M41" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="42" spans="2:11">
+    <row r="42" spans="2:13">
       <c r="B42" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -13681,21 +13696,36 @@
         <v>19</v>
       </c>
       <c r="E42">
-        <v>1599.6</v>
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>1599.6</v>
+        <v>4</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
       </c>
       <c r="J42">
-        <v>1599.6</v>
-      </c>
-      <c r="K42" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
+        <v>4</v>
+      </c>
+      <c r="K42">
+        <v>4</v>
+      </c>
+      <c r="L42">
+        <v>4</v>
+      </c>
+      <c r="M42" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13">
       <c r="B43" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -13703,22 +13733,22 @@
       <c r="D43" t="s">
         <v>19</v>
       </c>
-      <c r="E43">
-        <v>42.3</v>
-      </c>
-      <c r="G43">
-        <v>42.3</v>
-      </c>
-      <c r="J43">
-        <v>42.3</v>
-      </c>
-      <c r="K43" t="s">
+      <c r="F43">
+        <v>1881.9</v>
+      </c>
+      <c r="I43">
+        <v>1881.9</v>
+      </c>
+      <c r="L43">
+        <v>1881.9</v>
+      </c>
+      <c r="M43" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="44" spans="2:11">
+    <row r="44" spans="2:13">
       <c r="B44" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
@@ -13726,22 +13756,22 @@
       <c r="D44" t="s">
         <v>19</v>
       </c>
-      <c r="E44">
-        <v>2.3610000000000002</v>
-      </c>
-      <c r="G44">
-        <v>2.3610000000000002</v>
-      </c>
-      <c r="J44">
-        <v>2.3610000000000002</v>
-      </c>
-      <c r="K44" t="s">
+      <c r="F44">
+        <v>56.5</v>
+      </c>
+      <c r="I44">
+        <v>56.5</v>
+      </c>
+      <c r="L44">
+        <v>56.5</v>
+      </c>
+      <c r="M44" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="45" spans="2:11">
+    <row r="45" spans="2:13">
       <c r="B45" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
@@ -13749,22 +13779,22 @@
       <c r="D45" t="s">
         <v>19</v>
       </c>
-      <c r="E45">
-        <v>0.39</v>
-      </c>
-      <c r="G45">
-        <v>0.39</v>
-      </c>
-      <c r="J45">
-        <v>0.39</v>
-      </c>
-      <c r="K45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
+      <c r="F45">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="I45">
+        <v>2.4420000000000002</v>
+      </c>
+      <c r="L45">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="M45" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13">
       <c r="B46" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
@@ -13772,31 +13802,22 @@
       <c r="D46" t="s">
         <v>19</v>
       </c>
-      <c r="E46">
-        <v>40</v>
-      </c>
       <c r="F46">
-        <v>40</v>
-      </c>
-      <c r="G46">
-        <v>40</v>
-      </c>
-      <c r="H46">
-        <v>40</v>
+        <v>0.43</v>
       </c>
       <c r="I46">
-        <v>40</v>
-      </c>
-      <c r="J46">
-        <v>40</v>
-      </c>
-      <c r="K46" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
+        <v>0.43</v>
+      </c>
+      <c r="L46">
+        <v>0.43</v>
+      </c>
+      <c r="M46" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13">
       <c r="B47" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -13805,30 +13826,36 @@
         <v>19</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I47">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="J47">
-        <v>4</v>
-      </c>
-      <c r="K47" t="s">
+        <v>40</v>
+      </c>
+      <c r="K47">
+        <v>40</v>
+      </c>
+      <c r="L47">
+        <v>40</v>
+      </c>
+      <c r="M47" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="48" spans="2:11">
+    <row r="48" spans="2:13">
       <c r="B48" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -13837,21 +13864,36 @@
         <v>19</v>
       </c>
       <c r="E48">
-        <v>1881.9</v>
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>1881.9</v>
+        <v>4</v>
+      </c>
+      <c r="H48">
+        <v>4</v>
+      </c>
+      <c r="I48">
+        <v>4</v>
       </c>
       <c r="J48">
-        <v>1881.9</v>
-      </c>
-      <c r="K48" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
+        <v>4</v>
+      </c>
+      <c r="K48">
+        <v>4</v>
+      </c>
+      <c r="L48">
+        <v>4</v>
+      </c>
+      <c r="M48" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13">
       <c r="B49" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -13859,22 +13901,22 @@
       <c r="D49" t="s">
         <v>19</v>
       </c>
-      <c r="E49">
-        <v>56.5</v>
-      </c>
-      <c r="G49">
-        <v>56.5</v>
-      </c>
-      <c r="J49">
-        <v>56.5</v>
-      </c>
-      <c r="K49" t="s">
+      <c r="F49">
+        <v>2070.1</v>
+      </c>
+      <c r="I49">
+        <v>2070.1</v>
+      </c>
+      <c r="L49">
+        <v>2070.1</v>
+      </c>
+      <c r="M49" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="50" spans="2:11">
+    <row r="50" spans="2:13">
       <c r="B50" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C50" t="s">
         <v>32</v>
@@ -13882,22 +13924,22 @@
       <c r="D50" t="s">
         <v>19</v>
       </c>
-      <c r="E50">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="G50">
-        <v>2.4420000000000002</v>
-      </c>
-      <c r="J50">
-        <v>2.3170000000000002</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="F50">
+        <v>61.2</v>
+      </c>
+      <c r="I50">
+        <v>61.2</v>
+      </c>
+      <c r="L50">
+        <v>61.2</v>
+      </c>
+      <c r="M50" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="51" spans="2:11">
+    <row r="51" spans="2:13">
       <c r="B51" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C51" t="s">
         <v>32</v>
@@ -13905,22 +13947,22 @@
       <c r="D51" t="s">
         <v>19</v>
       </c>
-      <c r="E51">
-        <v>0.43</v>
-      </c>
-      <c r="G51">
-        <v>0.43</v>
-      </c>
-      <c r="J51">
-        <v>0.43</v>
-      </c>
-      <c r="K51" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
+      <c r="F51">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="I51">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="L51">
+        <v>2.6389999999999998</v>
+      </c>
+      <c r="M51" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13">
       <c r="B52" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C52" t="s">
         <v>32</v>
@@ -13928,31 +13970,22 @@
       <c r="D52" t="s">
         <v>19</v>
       </c>
-      <c r="E52">
-        <v>40</v>
-      </c>
       <c r="F52">
-        <v>40</v>
-      </c>
-      <c r="G52">
-        <v>40</v>
-      </c>
-      <c r="H52">
-        <v>40</v>
+        <v>0.46</v>
       </c>
       <c r="I52">
-        <v>40</v>
-      </c>
-      <c r="J52">
-        <v>40</v>
-      </c>
-      <c r="K52" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
+        <v>0.47</v>
+      </c>
+      <c r="L52">
+        <v>0.48</v>
+      </c>
+      <c r="M52" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13">
       <c r="B53" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C53" t="s">
         <v>32</v>
@@ -13961,30 +13994,36 @@
         <v>19</v>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I53">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="J53">
-        <v>4</v>
-      </c>
-      <c r="K53" t="s">
+        <v>40</v>
+      </c>
+      <c r="K53">
+        <v>40</v>
+      </c>
+      <c r="L53">
+        <v>40</v>
+      </c>
+      <c r="M53" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="54" spans="2:11">
+    <row r="54" spans="2:13">
       <c r="B54" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C54" t="s">
         <v>32</v>
@@ -13993,21 +14032,36 @@
         <v>19</v>
       </c>
       <c r="E54">
-        <v>2070.1</v>
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>4</v>
       </c>
       <c r="G54">
-        <v>2070.1</v>
+        <v>4</v>
+      </c>
+      <c r="H54">
+        <v>4</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
       </c>
       <c r="J54">
-        <v>2070.1</v>
-      </c>
-      <c r="K54" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
+        <v>4</v>
+      </c>
+      <c r="K54">
+        <v>4</v>
+      </c>
+      <c r="L54">
+        <v>4</v>
+      </c>
+      <c r="M54" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
       <c r="B55" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -14015,22 +14069,22 @@
       <c r="D55" t="s">
         <v>19</v>
       </c>
-      <c r="E55">
-        <v>61.2</v>
-      </c>
-      <c r="G55">
-        <v>61.2</v>
-      </c>
-      <c r="J55">
-        <v>61.2</v>
-      </c>
-      <c r="K55" t="s">
+      <c r="F55">
+        <v>2352.4</v>
+      </c>
+      <c r="I55">
+        <v>2164.1999999999998</v>
+      </c>
+      <c r="L55">
+        <v>2164.1999999999998</v>
+      </c>
+      <c r="M55" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="56" spans="2:11">
+    <row r="56" spans="2:13">
       <c r="B56" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -14038,22 +14092,22 @@
       <c r="D56" t="s">
         <v>19</v>
       </c>
-      <c r="E56">
-        <v>2.6389999999999998</v>
-      </c>
-      <c r="G56">
-        <v>2.6389999999999998</v>
-      </c>
-      <c r="J56">
-        <v>2.6389999999999998</v>
-      </c>
-      <c r="K56" t="s">
+      <c r="F56">
+        <v>84.7</v>
+      </c>
+      <c r="I56">
+        <v>75.3</v>
+      </c>
+      <c r="L56">
+        <v>75.3</v>
+      </c>
+      <c r="M56" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="57" spans="2:11">
+    <row r="57" spans="2:13">
       <c r="B57" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -14061,22 +14115,22 @@
       <c r="D57" t="s">
         <v>19</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>0.46</v>
       </c>
-      <c r="G57">
-        <v>0.47</v>
-      </c>
-      <c r="J57">
-        <v>0.48</v>
-      </c>
-      <c r="K57" t="s">
+      <c r="I57">
+        <v>0.49</v>
+      </c>
+      <c r="L57">
+        <v>0.5</v>
+      </c>
+      <c r="M57" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="58" spans="2:11">
+    <row r="58" spans="2:13">
       <c r="B58" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -14102,13 +14156,19 @@
       <c r="J58">
         <v>40</v>
       </c>
-      <c r="K58" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
+      <c r="K58">
+        <v>40</v>
+      </c>
+      <c r="L58">
+        <v>40</v>
+      </c>
+      <c r="M58" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="59" spans="2:13">
       <c r="B59" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -14134,1817 +14194,1748 @@
       <c r="J59">
         <v>4</v>
       </c>
-      <c r="K59" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
+      <c r="K59">
+        <v>4</v>
+      </c>
+      <c r="L59">
+        <v>4</v>
+      </c>
+      <c r="M59" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13">
       <c r="B60" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C60" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
       </c>
-      <c r="E60">
-        <v>2352.4</v>
-      </c>
-      <c r="G60">
-        <v>2164.1999999999998</v>
-      </c>
-      <c r="J60">
-        <v>2164.1999999999998</v>
-      </c>
-      <c r="K60" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
+      <c r="F60">
+        <v>6210.4</v>
+      </c>
+      <c r="I60">
+        <v>4704.8</v>
+      </c>
+      <c r="L60">
+        <v>4234.3</v>
+      </c>
+      <c r="M60" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13">
       <c r="B61" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C61" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D61" t="s">
         <v>19</v>
       </c>
-      <c r="E61">
-        <v>84.7</v>
-      </c>
-      <c r="G61">
-        <v>75.3</v>
-      </c>
-      <c r="J61">
-        <v>75.3</v>
-      </c>
-      <c r="K61" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
+      <c r="F61">
+        <v>155.30000000000001</v>
+      </c>
+      <c r="I61">
+        <v>160</v>
+      </c>
+      <c r="L61">
+        <v>150.6</v>
+      </c>
+      <c r="M61" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13">
       <c r="B62" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s">
         <v>19</v>
       </c>
-      <c r="E62">
-        <v>0.46</v>
-      </c>
-      <c r="G62">
-        <v>0.49</v>
-      </c>
-      <c r="J62">
-        <v>0.5</v>
-      </c>
-      <c r="K62" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
+      <c r="I62">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="L62">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="M62" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13">
       <c r="B63" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C63" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D63" t="s">
         <v>19</v>
       </c>
       <c r="E63">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F63">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G63">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H63">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I63">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J63">
-        <v>40</v>
-      </c>
-      <c r="K63" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
+        <v>60</v>
+      </c>
+      <c r="K63">
+        <v>60</v>
+      </c>
+      <c r="L63">
+        <v>60</v>
+      </c>
+      <c r="M63" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13">
       <c r="B64" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J64">
-        <v>4</v>
-      </c>
-      <c r="K64" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64">
+        <v>7</v>
+      </c>
+      <c r="L64">
+        <v>7</v>
+      </c>
+      <c r="M64" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13">
+      <c r="B65" t="s">
+        <v>633</v>
+      </c>
+      <c r="C65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65">
+        <v>10266</v>
+      </c>
+      <c r="I65">
+        <v>8364.9</v>
+      </c>
+      <c r="J65">
+        <v>6373.8</v>
+      </c>
+      <c r="K65">
+        <v>5480.2</v>
+      </c>
+      <c r="L65">
+        <v>4884.6000000000004</v>
+      </c>
+      <c r="M65" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13">
+      <c r="B66" t="s">
+        <v>633</v>
+      </c>
+      <c r="C66" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66">
+        <v>144.69999999999999</v>
+      </c>
+      <c r="I66">
+        <v>144.69999999999999</v>
+      </c>
+      <c r="J66">
+        <v>136</v>
+      </c>
+      <c r="K66">
+        <v>136</v>
+      </c>
+      <c r="L66">
+        <v>136</v>
+      </c>
+      <c r="M66" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13">
+      <c r="B67" t="s">
+        <v>633</v>
+      </c>
+      <c r="C67" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="I67">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="J67">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="K67">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="L67">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="M67" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
+      <c r="B68" t="s">
+        <v>633</v>
+      </c>
+      <c r="C68" t="s">
+        <v>36</v>
+      </c>
+      <c r="D68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68">
+        <v>40</v>
+      </c>
+      <c r="F68">
+        <v>40</v>
+      </c>
+      <c r="G68">
+        <v>40</v>
+      </c>
+      <c r="H68">
+        <v>40</v>
+      </c>
+      <c r="I68">
+        <v>40</v>
+      </c>
+      <c r="J68">
+        <v>40</v>
+      </c>
+      <c r="K68">
+        <v>40</v>
+      </c>
+      <c r="L68">
+        <v>40</v>
+      </c>
+      <c r="M68" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="65" spans="2:11">
-      <c r="B65" t="s">
-        <v>631</v>
-      </c>
-      <c r="C65" t="s">
-        <v>32</v>
-      </c>
-      <c r="D65" t="s">
-        <v>626</v>
-      </c>
-      <c r="E65">
-        <v>5175.3</v>
-      </c>
-      <c r="G65">
-        <v>4798.8999999999996</v>
-      </c>
-      <c r="J65">
-        <v>4375.5</v>
-      </c>
-      <c r="K65" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" t="s">
-        <v>631</v>
-      </c>
-      <c r="C66" t="s">
-        <v>32</v>
-      </c>
-      <c r="D66" t="s">
-        <v>626</v>
-      </c>
-      <c r="E66">
-        <v>155.30000000000001</v>
-      </c>
-      <c r="G66">
-        <v>145.80000000000001</v>
-      </c>
-      <c r="J66">
-        <v>131.69999999999999</v>
-      </c>
-      <c r="K66" t="s">
+    <row r="69" spans="2:13">
+      <c r="B69" t="s">
+        <v>633</v>
+      </c>
+      <c r="C69" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69">
+        <v>3</v>
+      </c>
+      <c r="G69">
+        <v>3</v>
+      </c>
+      <c r="H69">
+        <v>3</v>
+      </c>
+      <c r="I69">
+        <v>3</v>
+      </c>
+      <c r="J69">
+        <v>3</v>
+      </c>
+      <c r="K69">
+        <v>3</v>
+      </c>
+      <c r="L69">
+        <v>3</v>
+      </c>
+      <c r="M69" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13">
+      <c r="B70" t="s">
+        <v>634</v>
+      </c>
+      <c r="C70" t="s">
+        <v>31</v>
+      </c>
+      <c r="D70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70">
+        <v>2258.3000000000002</v>
+      </c>
+      <c r="I70">
+        <v>2211.3000000000002</v>
+      </c>
+      <c r="L70">
+        <v>2164.1999999999998</v>
+      </c>
+      <c r="M70" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="67" spans="2:11">
-      <c r="B67" t="s">
-        <v>631</v>
-      </c>
-      <c r="C67" t="s">
-        <v>32</v>
-      </c>
-      <c r="D67" t="s">
-        <v>626</v>
-      </c>
-      <c r="E67">
-        <v>4.3559999999999999</v>
-      </c>
-      <c r="G67">
-        <v>3.95</v>
-      </c>
-      <c r="J67">
-        <v>3.7309999999999999</v>
-      </c>
-      <c r="K67" t="s">
+    <row r="71" spans="2:13">
+      <c r="B71" t="s">
+        <v>634</v>
+      </c>
+      <c r="C71" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71">
+        <v>80</v>
+      </c>
+      <c r="I71">
+        <v>75.3</v>
+      </c>
+      <c r="L71">
+        <v>75.3</v>
+      </c>
+      <c r="M71" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="68" spans="2:11">
-      <c r="B68" t="s">
-        <v>631</v>
-      </c>
-      <c r="C68" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" t="s">
-        <v>626</v>
-      </c>
-      <c r="E68">
-        <v>0.37</v>
-      </c>
-      <c r="G68">
-        <v>0.39</v>
-      </c>
-      <c r="J68">
-        <v>0.39</v>
-      </c>
-      <c r="K68" t="s">
+    <row r="72" spans="2:13">
+      <c r="B72" t="s">
+        <v>634</v>
+      </c>
+      <c r="C72" t="s">
+        <v>31</v>
+      </c>
+      <c r="D72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="I72">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="L72">
+        <v>1.4570000000000001</v>
+      </c>
+      <c r="M72" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13">
+      <c r="B73" t="s">
+        <v>634</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73">
+        <v>0.35</v>
+      </c>
+      <c r="I73">
+        <v>0.35</v>
+      </c>
+      <c r="L73">
+        <v>0.35</v>
+      </c>
+      <c r="M73" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="69" spans="2:11">
-      <c r="B69" t="s">
-        <v>631</v>
-      </c>
-      <c r="C69" t="s">
-        <v>32</v>
-      </c>
-      <c r="D69" t="s">
-        <v>626</v>
-      </c>
-      <c r="E69">
-        <v>40</v>
-      </c>
-      <c r="F69">
-        <v>40</v>
-      </c>
-      <c r="G69">
-        <v>40</v>
-      </c>
-      <c r="H69">
-        <v>40</v>
-      </c>
-      <c r="I69">
-        <v>40</v>
-      </c>
-      <c r="J69">
-        <v>40</v>
-      </c>
-      <c r="K69" t="s">
+    <row r="74" spans="2:13">
+      <c r="B74" t="s">
+        <v>634</v>
+      </c>
+      <c r="C74" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74">
+        <v>0.6</v>
+      </c>
+      <c r="I74">
+        <v>0.6</v>
+      </c>
+      <c r="L74">
+        <v>0.6</v>
+      </c>
+      <c r="M74" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13">
+      <c r="B75" t="s">
+        <v>634</v>
+      </c>
+      <c r="C75" t="s">
+        <v>31</v>
+      </c>
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75">
+        <v>45</v>
+      </c>
+      <c r="F75">
+        <v>45</v>
+      </c>
+      <c r="G75">
+        <v>45</v>
+      </c>
+      <c r="H75">
+        <v>45</v>
+      </c>
+      <c r="I75">
+        <v>45</v>
+      </c>
+      <c r="J75">
+        <v>45</v>
+      </c>
+      <c r="K75">
+        <v>45</v>
+      </c>
+      <c r="L75">
+        <v>45</v>
+      </c>
+      <c r="M75" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13">
+      <c r="B76" t="s">
+        <v>634</v>
+      </c>
+      <c r="C76" t="s">
+        <v>31</v>
+      </c>
+      <c r="D76" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+      <c r="H76">
+        <v>3</v>
+      </c>
+      <c r="I76">
+        <v>3</v>
+      </c>
+      <c r="J76">
+        <v>3</v>
+      </c>
+      <c r="K76">
+        <v>3</v>
+      </c>
+      <c r="L76">
+        <v>3</v>
+      </c>
+      <c r="M76" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13">
+      <c r="B77" t="s">
+        <v>636</v>
+      </c>
+      <c r="C77" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" t="s">
+        <v>623</v>
+      </c>
+      <c r="E77">
+        <v>2748.9</v>
+      </c>
+      <c r="H77">
+        <v>2638.9</v>
+      </c>
+      <c r="L77">
+        <v>2528.9</v>
+      </c>
+      <c r="M77" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13">
+      <c r="B78" t="s">
+        <v>636</v>
+      </c>
+      <c r="C78" t="s">
+        <v>31</v>
+      </c>
+      <c r="D78" t="s">
+        <v>623</v>
+      </c>
+      <c r="E78">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="H78">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="L78">
+        <v>68.2</v>
+      </c>
+      <c r="M78" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13">
+      <c r="B79" t="s">
+        <v>636</v>
+      </c>
+      <c r="C79" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" t="s">
+        <v>623</v>
+      </c>
+      <c r="E79">
+        <v>0.8</v>
+      </c>
+      <c r="H79">
+        <v>0.8</v>
+      </c>
+      <c r="L79">
+        <v>0.8</v>
+      </c>
+      <c r="M79" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="70" spans="2:11">
-      <c r="B70" t="s">
-        <v>631</v>
-      </c>
-      <c r="C70" t="s">
-        <v>32</v>
-      </c>
-      <c r="D70" t="s">
-        <v>626</v>
-      </c>
-      <c r="E70">
-        <v>5</v>
-      </c>
-      <c r="F70">
-        <v>5</v>
-      </c>
-      <c r="G70">
-        <v>5</v>
-      </c>
-      <c r="H70">
-        <v>5</v>
-      </c>
-      <c r="I70">
-        <v>5</v>
-      </c>
-      <c r="J70">
-        <v>5</v>
-      </c>
-      <c r="K70" t="s">
+    <row r="80" spans="2:13">
+      <c r="B80" t="s">
+        <v>636</v>
+      </c>
+      <c r="C80" t="s">
+        <v>31</v>
+      </c>
+      <c r="D80" t="s">
+        <v>623</v>
+      </c>
+      <c r="E80">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="H80">
+        <v>0.41</v>
+      </c>
+      <c r="L80">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="M80" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13">
+      <c r="B81" t="s">
+        <v>636</v>
+      </c>
+      <c r="C81" t="s">
+        <v>31</v>
+      </c>
+      <c r="D81" t="s">
+        <v>623</v>
+      </c>
+      <c r="E81">
+        <v>25</v>
+      </c>
+      <c r="F81">
+        <v>25</v>
+      </c>
+      <c r="G81">
+        <v>25</v>
+      </c>
+      <c r="H81">
+        <v>25</v>
+      </c>
+      <c r="I81">
+        <v>25</v>
+      </c>
+      <c r="J81">
+        <v>25</v>
+      </c>
+      <c r="K81">
+        <v>25</v>
+      </c>
+      <c r="L81">
+        <v>25</v>
+      </c>
+      <c r="M81" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="71" spans="2:11">
-      <c r="B71" t="s">
-        <v>632</v>
-      </c>
-      <c r="C71" t="s">
-        <v>32</v>
-      </c>
-      <c r="D71" t="s">
-        <v>626</v>
-      </c>
-      <c r="E71">
-        <v>5504.6</v>
-      </c>
-      <c r="G71">
-        <v>5128.2</v>
-      </c>
-      <c r="J71">
-        <v>4893</v>
-      </c>
-      <c r="K71" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" t="s">
-        <v>632</v>
-      </c>
-      <c r="C72" t="s">
-        <v>32</v>
-      </c>
-      <c r="D72" t="s">
-        <v>626</v>
-      </c>
-      <c r="E72">
-        <v>192.9</v>
-      </c>
-      <c r="G72">
-        <v>178.8</v>
-      </c>
-      <c r="J72">
-        <v>174.1</v>
-      </c>
-      <c r="K72" t="s">
+    <row r="82" spans="2:13">
+      <c r="B82" t="s">
+        <v>636</v>
+      </c>
+      <c r="C82" t="s">
+        <v>31</v>
+      </c>
+      <c r="D82" t="s">
+        <v>623</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <v>2</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82">
+        <v>2</v>
+      </c>
+      <c r="L82">
+        <v>2</v>
+      </c>
+      <c r="M82" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13">
+      <c r="B83" t="s">
+        <v>636</v>
+      </c>
+      <c r="C83" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" t="s">
+        <v>623</v>
+      </c>
+      <c r="E83">
+        <v>1.8237000000000001</v>
+      </c>
+      <c r="H83">
+        <v>1.8137000000000001</v>
+      </c>
+      <c r="L83">
+        <v>1.9169</v>
+      </c>
+      <c r="M83" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="84" spans="2:13">
+      <c r="B84" t="s">
+        <v>636</v>
+      </c>
+      <c r="C84" t="s">
+        <v>31</v>
+      </c>
+      <c r="D84" t="s">
+        <v>623</v>
+      </c>
+      <c r="E84">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="H84">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="L84">
+        <v>-0.13</v>
+      </c>
+      <c r="M84" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="85" spans="2:13">
+      <c r="B85" t="s">
+        <v>637</v>
+      </c>
+      <c r="C85" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" t="s">
+        <v>623</v>
+      </c>
+      <c r="E85">
+        <v>66</v>
+      </c>
+      <c r="H85">
+        <v>55</v>
+      </c>
+      <c r="L85">
+        <v>55</v>
+      </c>
+      <c r="M85" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="73" spans="2:11">
-      <c r="B73" t="s">
-        <v>632</v>
-      </c>
-      <c r="C73" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" t="s">
-        <v>626</v>
-      </c>
-      <c r="E73">
-        <v>4.5830000000000002</v>
-      </c>
-      <c r="G73">
-        <v>4.5830000000000002</v>
-      </c>
-      <c r="J73">
-        <v>4.5830000000000002</v>
-      </c>
-      <c r="K73" t="s">
+    <row r="86" spans="2:13">
+      <c r="B86" t="s">
+        <v>637</v>
+      </c>
+      <c r="C86" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" t="s">
+        <v>623</v>
+      </c>
+      <c r="E86">
+        <v>2.1</v>
+      </c>
+      <c r="H86">
+        <v>2.1</v>
+      </c>
+      <c r="L86">
+        <v>1.9</v>
+      </c>
+      <c r="M86" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="74" spans="2:11">
-      <c r="B74" t="s">
-        <v>632</v>
-      </c>
-      <c r="C74" t="s">
-        <v>32</v>
-      </c>
-      <c r="D74" t="s">
-        <v>626</v>
-      </c>
-      <c r="E74">
-        <v>0.37</v>
-      </c>
-      <c r="G74">
-        <v>0.41</v>
-      </c>
-      <c r="J74">
-        <v>0.43</v>
-      </c>
-      <c r="K74" t="s">
+    <row r="87" spans="2:13">
+      <c r="B87" t="s">
+        <v>637</v>
+      </c>
+      <c r="C87" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" t="s">
+        <v>623</v>
+      </c>
+      <c r="E87">
+        <v>0.3</v>
+      </c>
+      <c r="H87">
+        <v>0.3</v>
+      </c>
+      <c r="L87">
+        <v>0.3</v>
+      </c>
+      <c r="M87" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="88" spans="2:13">
+      <c r="B88" t="s">
+        <v>637</v>
+      </c>
+      <c r="C88" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" t="s">
+        <v>623</v>
+      </c>
+      <c r="E88">
+        <v>1.03</v>
+      </c>
+      <c r="H88">
+        <v>1.04</v>
+      </c>
+      <c r="L88">
+        <v>1.04</v>
+      </c>
+      <c r="M88" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="75" spans="2:11">
-      <c r="B75" t="s">
-        <v>632</v>
-      </c>
-      <c r="C75" t="s">
-        <v>32</v>
-      </c>
-      <c r="D75" t="s">
-        <v>626</v>
-      </c>
-      <c r="E75">
-        <v>40</v>
-      </c>
-      <c r="F75">
-        <v>40</v>
-      </c>
-      <c r="G75">
-        <v>40</v>
-      </c>
-      <c r="H75">
-        <v>40</v>
-      </c>
-      <c r="I75">
-        <v>40</v>
-      </c>
-      <c r="J75">
-        <v>40</v>
-      </c>
-      <c r="K75" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" t="s">
-        <v>632</v>
-      </c>
-      <c r="C76" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" t="s">
-        <v>626</v>
-      </c>
-      <c r="E76">
-        <v>5</v>
-      </c>
-      <c r="F76">
-        <v>5</v>
-      </c>
-      <c r="G76">
-        <v>5</v>
-      </c>
-      <c r="H76">
-        <v>5</v>
-      </c>
-      <c r="I76">
-        <v>5</v>
-      </c>
-      <c r="J76">
-        <v>5</v>
-      </c>
-      <c r="K76" t="s">
+    <row r="89" spans="2:13">
+      <c r="B89" t="s">
+        <v>637</v>
+      </c>
+      <c r="C89" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" t="s">
+        <v>623</v>
+      </c>
+      <c r="E89">
+        <v>25</v>
+      </c>
+      <c r="F89">
+        <v>25</v>
+      </c>
+      <c r="G89">
+        <v>25</v>
+      </c>
+      <c r="H89">
+        <v>25</v>
+      </c>
+      <c r="I89">
+        <v>25</v>
+      </c>
+      <c r="J89">
+        <v>25</v>
+      </c>
+      <c r="K89">
+        <v>25</v>
+      </c>
+      <c r="L89">
+        <v>25</v>
+      </c>
+      <c r="M89" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="77" spans="2:11">
-      <c r="B77" t="s">
-        <v>633</v>
-      </c>
-      <c r="C77" t="s">
-        <v>32</v>
-      </c>
-      <c r="D77" t="s">
-        <v>626</v>
-      </c>
-      <c r="E77">
-        <v>5363.5</v>
-      </c>
-      <c r="G77">
-        <v>5128.2</v>
-      </c>
-      <c r="J77">
-        <v>4940.1000000000004</v>
-      </c>
-      <c r="K77" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" t="s">
-        <v>633</v>
-      </c>
-      <c r="C78" t="s">
-        <v>32</v>
-      </c>
-      <c r="D78" t="s">
-        <v>626</v>
-      </c>
-      <c r="E78">
-        <v>160</v>
-      </c>
-      <c r="G78">
-        <v>155.30000000000001</v>
-      </c>
-      <c r="J78">
-        <v>145.80000000000001</v>
-      </c>
-      <c r="K78" t="s">
+    <row r="90" spans="2:13">
+      <c r="B90" t="s">
+        <v>637</v>
+      </c>
+      <c r="C90" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" t="s">
+        <v>623</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13">
+      <c r="B91" t="s">
+        <v>638</v>
+      </c>
+      <c r="C91" t="s">
+        <v>31</v>
+      </c>
+      <c r="D91" t="s">
+        <v>623</v>
+      </c>
+      <c r="E91">
+        <v>483.8</v>
+      </c>
+      <c r="H91">
+        <v>461.8</v>
+      </c>
+      <c r="L91">
+        <v>439.8</v>
+      </c>
+      <c r="M91" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="79" spans="2:11">
-      <c r="B79" t="s">
-        <v>633</v>
-      </c>
-      <c r="C79" t="s">
-        <v>32</v>
-      </c>
-      <c r="D79" t="s">
-        <v>626</v>
-      </c>
-      <c r="E79">
-        <v>4.306</v>
-      </c>
-      <c r="G79">
-        <v>4.306</v>
-      </c>
-      <c r="J79">
-        <v>4.306</v>
-      </c>
-      <c r="K79" t="s">
+    <row r="92" spans="2:13">
+      <c r="B92" t="s">
+        <v>638</v>
+      </c>
+      <c r="C92" t="s">
+        <v>31</v>
+      </c>
+      <c r="D92" t="s">
+        <v>623</v>
+      </c>
+      <c r="E92">
+        <v>38</v>
+      </c>
+      <c r="H92">
+        <v>36.6</v>
+      </c>
+      <c r="L92">
+        <v>34.5</v>
+      </c>
+      <c r="M92" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="80" spans="2:11">
-      <c r="B80" t="s">
-        <v>633</v>
-      </c>
-      <c r="C80" t="s">
-        <v>32</v>
-      </c>
-      <c r="D80" t="s">
-        <v>626</v>
-      </c>
-      <c r="E80">
-        <v>0.37</v>
-      </c>
-      <c r="G80">
-        <v>0.39</v>
-      </c>
-      <c r="J80">
-        <v>0.39</v>
-      </c>
-      <c r="K80" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81" t="s">
-        <v>633</v>
-      </c>
-      <c r="C81" t="s">
-        <v>32</v>
-      </c>
-      <c r="D81" t="s">
-        <v>626</v>
-      </c>
-      <c r="E81">
-        <v>40</v>
-      </c>
-      <c r="F81">
-        <v>40</v>
-      </c>
-      <c r="G81">
-        <v>40</v>
-      </c>
-      <c r="H81">
-        <v>40</v>
-      </c>
-      <c r="I81">
-        <v>40</v>
-      </c>
-      <c r="J81">
-        <v>40</v>
-      </c>
-      <c r="K81" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" t="s">
-        <v>633</v>
-      </c>
-      <c r="C82" t="s">
-        <v>32</v>
-      </c>
-      <c r="D82" t="s">
-        <v>626</v>
-      </c>
-      <c r="E82">
-        <v>5</v>
-      </c>
-      <c r="F82">
-        <v>5</v>
-      </c>
-      <c r="G82">
-        <v>5</v>
-      </c>
-      <c r="H82">
-        <v>5</v>
-      </c>
-      <c r="I82">
-        <v>5</v>
-      </c>
-      <c r="J82">
-        <v>5</v>
-      </c>
-      <c r="K82" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83" t="s">
-        <v>634</v>
-      </c>
-      <c r="C83" t="s">
-        <v>36</v>
-      </c>
-      <c r="D83" t="s">
-        <v>19</v>
-      </c>
-      <c r="E83">
-        <v>6210.4</v>
-      </c>
-      <c r="G83">
-        <v>4704.8</v>
-      </c>
-      <c r="J83">
-        <v>4234.3</v>
-      </c>
-      <c r="K83" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" t="s">
-        <v>634</v>
-      </c>
-      <c r="C84" t="s">
-        <v>36</v>
-      </c>
-      <c r="D84" t="s">
-        <v>19</v>
-      </c>
-      <c r="E84">
-        <v>155.30000000000001</v>
-      </c>
-      <c r="G84">
-        <v>160</v>
-      </c>
-      <c r="J84">
-        <v>150.6</v>
-      </c>
-      <c r="K84" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85" t="s">
-        <v>634</v>
-      </c>
-      <c r="C85" t="s">
-        <v>36</v>
-      </c>
-      <c r="D85" t="s">
-        <v>19</v>
-      </c>
-      <c r="G85">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="J85">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="K85" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" t="s">
-        <v>634</v>
-      </c>
-      <c r="C86" t="s">
-        <v>36</v>
-      </c>
-      <c r="D86" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86">
-        <v>60</v>
-      </c>
-      <c r="F86">
-        <v>60</v>
-      </c>
-      <c r="G86">
-        <v>60</v>
-      </c>
-      <c r="H86">
-        <v>60</v>
-      </c>
-      <c r="I86">
-        <v>60</v>
-      </c>
-      <c r="J86">
-        <v>60</v>
-      </c>
-      <c r="K86" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87" t="s">
-        <v>634</v>
-      </c>
-      <c r="C87" t="s">
-        <v>36</v>
-      </c>
-      <c r="D87" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87">
-        <v>7</v>
-      </c>
-      <c r="F87">
-        <v>7</v>
-      </c>
-      <c r="G87">
-        <v>7</v>
-      </c>
-      <c r="H87">
-        <v>7</v>
-      </c>
-      <c r="I87">
-        <v>7</v>
-      </c>
-      <c r="J87">
-        <v>7</v>
-      </c>
-      <c r="K87" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88" t="s">
-        <v>635</v>
-      </c>
-      <c r="C88" t="s">
-        <v>36</v>
-      </c>
-      <c r="D88" t="s">
-        <v>19</v>
-      </c>
-      <c r="F88">
-        <v>10266</v>
-      </c>
-      <c r="G88">
-        <v>8364.9</v>
-      </c>
-      <c r="H88">
-        <v>6373.8</v>
-      </c>
-      <c r="I88">
-        <v>5480.2</v>
-      </c>
-      <c r="J88">
-        <v>4884.6000000000004</v>
-      </c>
-      <c r="K88" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89" t="s">
-        <v>635</v>
-      </c>
-      <c r="C89" t="s">
-        <v>36</v>
-      </c>
-      <c r="D89" t="s">
-        <v>19</v>
-      </c>
-      <c r="F89">
-        <v>144.69999999999999</v>
-      </c>
-      <c r="G89">
-        <v>144.69999999999999</v>
-      </c>
-      <c r="H89">
-        <v>136</v>
-      </c>
-      <c r="I89">
-        <v>136</v>
-      </c>
-      <c r="J89">
-        <v>136</v>
-      </c>
-      <c r="K89" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90" t="s">
-        <v>635</v>
-      </c>
-      <c r="C90" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90">
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="G90">
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="H90">
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="I90">
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="J90">
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="K90" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91" t="s">
-        <v>635</v>
-      </c>
-      <c r="C91" t="s">
-        <v>36</v>
-      </c>
-      <c r="D91" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91">
-        <v>40</v>
-      </c>
-      <c r="F91">
-        <v>40</v>
-      </c>
-      <c r="G91">
-        <v>40</v>
-      </c>
-      <c r="H91">
-        <v>40</v>
-      </c>
-      <c r="I91">
-        <v>40</v>
-      </c>
-      <c r="J91">
-        <v>40</v>
-      </c>
-      <c r="K91" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="B92" t="s">
-        <v>635</v>
-      </c>
-      <c r="C92" t="s">
-        <v>36</v>
-      </c>
-      <c r="D92" t="s">
-        <v>19</v>
-      </c>
-      <c r="E92">
-        <v>3</v>
-      </c>
-      <c r="F92">
-        <v>3</v>
-      </c>
-      <c r="G92">
-        <v>3</v>
-      </c>
-      <c r="H92">
-        <v>3</v>
-      </c>
-      <c r="I92">
-        <v>3</v>
-      </c>
-      <c r="J92">
-        <v>3</v>
-      </c>
-      <c r="K92" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
+    <row r="93" spans="2:13">
       <c r="B93" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>19</v>
+        <v>623</v>
       </c>
       <c r="E93">
-        <v>2258.3000000000002</v>
-      </c>
-      <c r="G93">
-        <v>2211.3000000000002</v>
-      </c>
-      <c r="J93">
-        <v>2164.1999999999998</v>
-      </c>
-      <c r="K93" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
+        <v>0.4</v>
+      </c>
+      <c r="H93">
+        <v>0.4</v>
+      </c>
+      <c r="L93">
+        <v>0.4</v>
+      </c>
+      <c r="M93" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="94" spans="2:13">
       <c r="B94" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C94" t="s">
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>19</v>
+        <v>623</v>
       </c>
       <c r="E94">
-        <v>80</v>
-      </c>
-      <c r="G94">
-        <v>75.3</v>
-      </c>
-      <c r="J94">
-        <v>75.3</v>
-      </c>
-      <c r="K94" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11">
+        <v>1.149</v>
+      </c>
+      <c r="H94">
+        <v>1.149</v>
+      </c>
+      <c r="L94">
+        <v>1.149</v>
+      </c>
+      <c r="M94" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="95" spans="2:13">
       <c r="B95" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C95" t="s">
         <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>19</v>
+        <v>623</v>
       </c>
       <c r="E95">
-        <v>1.4570000000000001</v>
+        <v>25</v>
+      </c>
+      <c r="F95">
+        <v>25</v>
       </c>
       <c r="G95">
-        <v>1.4570000000000001</v>
+        <v>25</v>
+      </c>
+      <c r="H95">
+        <v>25</v>
+      </c>
+      <c r="I95">
+        <v>25</v>
       </c>
       <c r="J95">
-        <v>1.4570000000000001</v>
-      </c>
-      <c r="K95" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
+        <v>25</v>
+      </c>
+      <c r="K95">
+        <v>25</v>
+      </c>
+      <c r="L95">
+        <v>25</v>
+      </c>
+      <c r="M95" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="96" spans="2:13">
       <c r="B96" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C96" t="s">
         <v>31</v>
       </c>
       <c r="D96" t="s">
+        <v>623</v>
+      </c>
+      <c r="E96">
+        <v>3</v>
+      </c>
+      <c r="F96">
+        <v>3</v>
+      </c>
+      <c r="G96">
+        <v>3</v>
+      </c>
+      <c r="H96">
+        <v>3</v>
+      </c>
+      <c r="I96">
+        <v>3</v>
+      </c>
+      <c r="J96">
+        <v>3</v>
+      </c>
+      <c r="K96">
+        <v>3</v>
+      </c>
+      <c r="L96">
+        <v>3</v>
+      </c>
+      <c r="M96" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13">
+      <c r="B97" t="s">
+        <v>639</v>
+      </c>
+      <c r="C97" t="s">
         <v>19</v>
       </c>
-      <c r="E96">
-        <v>0.35</v>
-      </c>
-      <c r="G96">
-        <v>0.35</v>
-      </c>
-      <c r="J96">
-        <v>0.35</v>
-      </c>
-      <c r="K96" t="s">
+      <c r="D97" t="s">
+        <v>623</v>
+      </c>
+      <c r="G97">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="H97">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="I97">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="J97">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="L97">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="M97" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13">
+      <c r="B98" t="s">
+        <v>639</v>
+      </c>
+      <c r="C98" t="s">
+        <v>19</v>
+      </c>
+      <c r="D98" t="s">
+        <v>623</v>
+      </c>
+      <c r="G98">
+        <v>1.2</v>
+      </c>
+      <c r="H98">
+        <v>1.2</v>
+      </c>
+      <c r="I98">
+        <v>1.2</v>
+      </c>
+      <c r="J98">
+        <v>1.2</v>
+      </c>
+      <c r="L98">
+        <v>1.2</v>
+      </c>
+      <c r="M98" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13">
+      <c r="B99" t="s">
+        <v>639</v>
+      </c>
+      <c r="C99" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" t="s">
+        <v>623</v>
+      </c>
+      <c r="G99">
+        <v>0.2</v>
+      </c>
+      <c r="H99">
+        <v>0.2</v>
+      </c>
+      <c r="I99">
+        <v>0.2</v>
+      </c>
+      <c r="J99">
+        <v>0.2</v>
+      </c>
+      <c r="L99">
+        <v>0.2</v>
+      </c>
+      <c r="M99" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="100" spans="2:13">
+      <c r="B100" t="s">
+        <v>639</v>
+      </c>
+      <c r="C100" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" t="s">
+        <v>623</v>
+      </c>
+      <c r="G100">
+        <v>0.99</v>
+      </c>
+      <c r="H100">
+        <v>0.99</v>
+      </c>
+      <c r="I100">
+        <v>0.99</v>
+      </c>
+      <c r="J100">
+        <v>0.99</v>
+      </c>
+      <c r="L100">
+        <v>0.99</v>
+      </c>
+      <c r="M100" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="97" spans="2:11">
-      <c r="B97" t="s">
-        <v>636</v>
-      </c>
-      <c r="C97" t="s">
-        <v>31</v>
-      </c>
-      <c r="D97" t="s">
+    <row r="101" spans="2:13">
+      <c r="B101" t="s">
+        <v>639</v>
+      </c>
+      <c r="C101" t="s">
         <v>19</v>
       </c>
-      <c r="E97">
-        <v>0.6</v>
-      </c>
-      <c r="G97">
-        <v>0.6</v>
-      </c>
-      <c r="J97">
-        <v>0.6</v>
-      </c>
-      <c r="K97" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11">
-      <c r="B98" t="s">
-        <v>636</v>
-      </c>
-      <c r="C98" t="s">
-        <v>31</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="D101" t="s">
+        <v>623</v>
+      </c>
+      <c r="E101">
+        <v>20</v>
+      </c>
+      <c r="F101">
+        <v>20</v>
+      </c>
+      <c r="G101">
+        <v>20</v>
+      </c>
+      <c r="H101">
+        <v>20</v>
+      </c>
+      <c r="I101">
+        <v>20</v>
+      </c>
+      <c r="J101">
+        <v>20</v>
+      </c>
+      <c r="K101">
+        <v>20</v>
+      </c>
+      <c r="L101">
+        <v>20</v>
+      </c>
+      <c r="M101" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13">
+      <c r="B102" t="s">
+        <v>639</v>
+      </c>
+      <c r="C102" t="s">
         <v>19</v>
       </c>
-      <c r="E98">
-        <v>45</v>
-      </c>
-      <c r="F98">
-        <v>45</v>
-      </c>
-      <c r="G98">
-        <v>45</v>
-      </c>
-      <c r="H98">
-        <v>45</v>
-      </c>
-      <c r="I98">
-        <v>45</v>
-      </c>
-      <c r="J98">
-        <v>45</v>
-      </c>
-      <c r="K98" t="s">
+      <c r="D102" t="s">
+        <v>623</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="M102" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13">
+      <c r="B103" t="s">
+        <v>640</v>
+      </c>
+      <c r="C103" t="s">
+        <v>19</v>
+      </c>
+      <c r="D103" t="s">
+        <v>623</v>
+      </c>
+      <c r="G103">
+        <v>1054.7</v>
+      </c>
+      <c r="H103">
+        <v>1028.3</v>
+      </c>
+      <c r="I103">
+        <v>1002</v>
+      </c>
+      <c r="J103">
+        <v>976.9</v>
+      </c>
+      <c r="L103">
+        <v>951.9</v>
+      </c>
+      <c r="M103" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="104" spans="2:13">
+      <c r="B104" t="s">
+        <v>640</v>
+      </c>
+      <c r="C104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" t="s">
+        <v>623</v>
+      </c>
+      <c r="G104">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H104">
+        <v>2.1</v>
+      </c>
+      <c r="I104">
+        <v>2.1</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="105" spans="2:13">
+      <c r="B105" t="s">
+        <v>640</v>
+      </c>
+      <c r="C105" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" t="s">
+        <v>623</v>
+      </c>
+      <c r="G105">
+        <v>0.2</v>
+      </c>
+      <c r="H105">
+        <v>0.2</v>
+      </c>
+      <c r="I105">
+        <v>0.2</v>
+      </c>
+      <c r="J105">
+        <v>0.2</v>
+      </c>
+      <c r="L105">
+        <v>0.2</v>
+      </c>
+      <c r="M105" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="99" spans="2:11">
-      <c r="B99" t="s">
-        <v>636</v>
-      </c>
-      <c r="C99" t="s">
-        <v>31</v>
-      </c>
-      <c r="D99" t="s">
+    <row r="106" spans="2:13">
+      <c r="B106" t="s">
+        <v>640</v>
+      </c>
+      <c r="C106" t="s">
         <v>19</v>
       </c>
-      <c r="E99">
-        <v>3</v>
-      </c>
-      <c r="F99">
-        <v>3</v>
-      </c>
-      <c r="G99">
-        <v>3</v>
-      </c>
-      <c r="H99">
-        <v>3</v>
-      </c>
-      <c r="I99">
-        <v>3</v>
-      </c>
-      <c r="J99">
-        <v>3</v>
-      </c>
-      <c r="K99" t="s">
+      <c r="D106" t="s">
+        <v>623</v>
+      </c>
+      <c r="G106">
+        <v>2.8</v>
+      </c>
+      <c r="H106">
+        <v>2.8</v>
+      </c>
+      <c r="I106">
+        <v>2.8</v>
+      </c>
+      <c r="J106">
+        <v>2.8</v>
+      </c>
+      <c r="L106">
+        <v>2.9169999999999998</v>
+      </c>
+      <c r="M106" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13">
+      <c r="B107" t="s">
+        <v>640</v>
+      </c>
+      <c r="C107" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" t="s">
+        <v>623</v>
+      </c>
+      <c r="E107">
+        <v>25</v>
+      </c>
+      <c r="F107">
+        <v>25</v>
+      </c>
+      <c r="G107">
+        <v>25</v>
+      </c>
+      <c r="H107">
+        <v>25</v>
+      </c>
+      <c r="I107">
+        <v>25</v>
+      </c>
+      <c r="J107">
+        <v>25</v>
+      </c>
+      <c r="K107">
+        <v>25</v>
+      </c>
+      <c r="L107">
+        <v>25</v>
+      </c>
+      <c r="M107" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="100" spans="2:11">
-      <c r="B100" t="s">
-        <v>638</v>
-      </c>
-      <c r="C100" t="s">
-        <v>31</v>
-      </c>
-      <c r="D100" t="s">
+    <row r="108" spans="2:13">
+      <c r="B108" t="s">
+        <v>640</v>
+      </c>
+      <c r="C108" t="s">
         <v>19</v>
       </c>
-      <c r="E100">
-        <v>564.6</v>
-      </c>
-      <c r="G100">
-        <v>564.6</v>
-      </c>
-      <c r="J100">
-        <v>541.1</v>
-      </c>
-      <c r="K100" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11">
-      <c r="B101" t="s">
-        <v>638</v>
-      </c>
-      <c r="C101" t="s">
-        <v>31</v>
-      </c>
-      <c r="D101" t="s">
-        <v>19</v>
-      </c>
-      <c r="E101">
-        <v>23.5</v>
-      </c>
-      <c r="G101">
-        <v>18.8</v>
-      </c>
-      <c r="J101">
-        <v>18.8</v>
-      </c>
-      <c r="K101" t="s">
+      <c r="D108" t="s">
+        <v>623</v>
+      </c>
+      <c r="E108">
+        <v>1</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
+      </c>
+      <c r="M108" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13">
+      <c r="B109" t="s">
+        <v>641</v>
+      </c>
+      <c r="C109" t="s">
+        <v>33</v>
+      </c>
+      <c r="D109" t="s">
+        <v>642</v>
+      </c>
+      <c r="E109">
+        <v>0.52</v>
+      </c>
+      <c r="F109">
+        <v>0.52</v>
+      </c>
+      <c r="G109">
+        <v>0.52</v>
+      </c>
+      <c r="H109">
+        <v>0.52</v>
+      </c>
+      <c r="I109">
+        <v>0.52</v>
+      </c>
+      <c r="J109">
+        <v>0.52</v>
+      </c>
+      <c r="K109">
+        <v>0.52</v>
+      </c>
+      <c r="L109">
+        <v>0.52</v>
+      </c>
+      <c r="M109" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="110" spans="2:13">
+      <c r="B110" t="s">
+        <v>641</v>
+      </c>
+      <c r="C110" t="s">
+        <v>33</v>
+      </c>
+      <c r="D110" t="s">
+        <v>642</v>
+      </c>
+      <c r="E110">
+        <v>2917</v>
+      </c>
+      <c r="F110">
+        <v>2917</v>
+      </c>
+      <c r="G110">
+        <v>2917</v>
+      </c>
+      <c r="H110">
+        <v>2917</v>
+      </c>
+      <c r="I110">
+        <v>2917</v>
+      </c>
+      <c r="J110">
+        <v>2917</v>
+      </c>
+      <c r="K110">
+        <v>2917</v>
+      </c>
+      <c r="L110">
+        <v>2917</v>
+      </c>
+      <c r="M110" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="102" spans="2:11">
-      <c r="B102" t="s">
-        <v>638</v>
-      </c>
-      <c r="C102" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102">
-        <v>1.111</v>
-      </c>
-      <c r="G102">
-        <v>1.111</v>
-      </c>
-      <c r="J102">
-        <v>1.111</v>
-      </c>
-      <c r="K102" t="s">
+    <row r="111" spans="2:13">
+      <c r="B111" t="s">
+        <v>641</v>
+      </c>
+      <c r="C111" t="s">
+        <v>33</v>
+      </c>
+      <c r="D111" t="s">
+        <v>642</v>
+      </c>
+      <c r="E111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="F111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="G111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="H111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="I111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="J111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="K111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L111">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="M111" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="103" spans="2:11">
-      <c r="B103" t="s">
-        <v>638</v>
-      </c>
-      <c r="C103" t="s">
-        <v>31</v>
-      </c>
-      <c r="D103" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103">
-        <v>0.37</v>
-      </c>
-      <c r="G103">
-        <v>0.37</v>
-      </c>
-      <c r="J103">
-        <v>0.37</v>
-      </c>
-      <c r="K103" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11">
-      <c r="B104" t="s">
-        <v>638</v>
-      </c>
-      <c r="C104" t="s">
-        <v>31</v>
-      </c>
-      <c r="D104" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104">
-        <v>0.6</v>
-      </c>
-      <c r="G104">
-        <v>0.6</v>
-      </c>
-      <c r="J104">
-        <v>0.6</v>
-      </c>
-      <c r="K104" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11">
-      <c r="B105" t="s">
-        <v>638</v>
-      </c>
-      <c r="C105" t="s">
-        <v>31</v>
-      </c>
-      <c r="D105" t="s">
-        <v>19</v>
-      </c>
-      <c r="E105">
-        <v>40</v>
-      </c>
-      <c r="F105">
-        <v>40</v>
-      </c>
-      <c r="G105">
-        <v>40</v>
-      </c>
-      <c r="H105">
-        <v>40</v>
-      </c>
-      <c r="I105">
-        <v>40</v>
-      </c>
-      <c r="J105">
-        <v>40</v>
-      </c>
-      <c r="K105" t="s">
+    <row r="112" spans="2:13">
+      <c r="B112" t="s">
+        <v>641</v>
+      </c>
+      <c r="C112" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" t="s">
+        <v>642</v>
+      </c>
+      <c r="E112">
+        <v>1.3</v>
+      </c>
+      <c r="F112">
+        <v>1.3</v>
+      </c>
+      <c r="G112">
+        <v>1.3</v>
+      </c>
+      <c r="H112">
+        <v>1.3</v>
+      </c>
+      <c r="I112">
+        <v>1.3</v>
+      </c>
+      <c r="J112">
+        <v>1.3</v>
+      </c>
+      <c r="K112">
+        <v>1.3</v>
+      </c>
+      <c r="L112">
+        <v>1.3</v>
+      </c>
+      <c r="M112" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="106" spans="2:11">
-      <c r="B106" t="s">
-        <v>638</v>
-      </c>
-      <c r="C106" t="s">
-        <v>31</v>
-      </c>
-      <c r="D106" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106">
-        <v>2</v>
-      </c>
-      <c r="F106">
-        <v>2</v>
-      </c>
-      <c r="G106">
-        <v>2</v>
-      </c>
-      <c r="H106">
-        <v>2</v>
-      </c>
-      <c r="I106">
-        <v>2</v>
-      </c>
-      <c r="J106">
-        <v>2</v>
-      </c>
-      <c r="K106" t="s">
+    <row r="113" spans="2:13">
+      <c r="B113" t="s">
+        <v>641</v>
+      </c>
+      <c r="C113" t="s">
+        <v>33</v>
+      </c>
+      <c r="D113" t="s">
+        <v>642</v>
+      </c>
+      <c r="E113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="F113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="G113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="H113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="I113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="J113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="K113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="L113">
+        <v>0.55559999999999998</v>
+      </c>
+      <c r="M113" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="114" spans="2:13">
+      <c r="B114" t="s">
+        <v>641</v>
+      </c>
+      <c r="C114" t="s">
+        <v>33</v>
+      </c>
+      <c r="D114" t="s">
+        <v>642</v>
+      </c>
+      <c r="E114">
+        <v>-0.15</v>
+      </c>
+      <c r="F114">
+        <v>-0.15</v>
+      </c>
+      <c r="G114">
+        <v>-0.15</v>
+      </c>
+      <c r="H114">
+        <v>-0.15</v>
+      </c>
+      <c r="I114">
+        <v>-0.15</v>
+      </c>
+      <c r="J114">
+        <v>-0.15</v>
+      </c>
+      <c r="K114">
+        <v>-0.15</v>
+      </c>
+      <c r="L114">
+        <v>-0.15</v>
+      </c>
+      <c r="M114" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="115" spans="2:13">
+      <c r="B115" t="s">
+        <v>641</v>
+      </c>
+      <c r="C115" t="s">
+        <v>33</v>
+      </c>
+      <c r="D115" t="s">
+        <v>642</v>
+      </c>
+      <c r="E115">
+        <v>25</v>
+      </c>
+      <c r="F115">
+        <v>25</v>
+      </c>
+      <c r="G115">
+        <v>25</v>
+      </c>
+      <c r="H115">
+        <v>25</v>
+      </c>
+      <c r="I115">
+        <v>25</v>
+      </c>
+      <c r="J115">
+        <v>25</v>
+      </c>
+      <c r="K115">
+        <v>25</v>
+      </c>
+      <c r="L115">
+        <v>25</v>
+      </c>
+      <c r="M115" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="107" spans="2:11">
-      <c r="B107" t="s">
-        <v>639</v>
-      </c>
-      <c r="C107" t="s">
-        <v>31</v>
-      </c>
-      <c r="D107" t="s">
-        <v>622</v>
-      </c>
-      <c r="E107">
-        <v>3528.6</v>
-      </c>
-      <c r="G107">
-        <v>3481.6</v>
-      </c>
-      <c r="J107">
-        <v>3434.5</v>
-      </c>
-      <c r="K107" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11">
-      <c r="B108" t="s">
-        <v>639</v>
-      </c>
-      <c r="C108" t="s">
-        <v>31</v>
-      </c>
-      <c r="D108" t="s">
-        <v>622</v>
-      </c>
-      <c r="E108">
-        <v>131.69999999999999</v>
-      </c>
-      <c r="G108">
-        <v>131.69999999999999</v>
-      </c>
-      <c r="J108">
-        <v>127</v>
-      </c>
-      <c r="K108" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11">
-      <c r="B109" t="s">
-        <v>639</v>
-      </c>
-      <c r="C109" t="s">
-        <v>31</v>
-      </c>
-      <c r="D109" t="s">
-        <v>622</v>
-      </c>
-      <c r="E109">
-        <v>1.667</v>
-      </c>
-      <c r="G109">
-        <v>1.667</v>
-      </c>
-      <c r="J109">
-        <v>1.667</v>
-      </c>
-      <c r="K109" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11">
-      <c r="B110" t="s">
-        <v>639</v>
-      </c>
-      <c r="C110" t="s">
-        <v>31</v>
-      </c>
-      <c r="D110" t="s">
-        <v>622</v>
-      </c>
-      <c r="E110">
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="G110">
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="J110">
-        <v>0.38500000000000001</v>
-      </c>
-      <c r="K110" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11">
-      <c r="B111" t="s">
-        <v>639</v>
-      </c>
-      <c r="C111" t="s">
-        <v>31</v>
-      </c>
-      <c r="D111" t="s">
-        <v>622</v>
-      </c>
-      <c r="E111">
-        <v>0.7</v>
-      </c>
-      <c r="G111">
-        <v>0.7</v>
-      </c>
-      <c r="J111">
-        <v>0.7</v>
-      </c>
-      <c r="K111" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11">
-      <c r="B112" t="s">
-        <v>639</v>
-      </c>
-      <c r="C112" t="s">
-        <v>31</v>
-      </c>
-      <c r="D112" t="s">
-        <v>622</v>
-      </c>
-      <c r="E112">
-        <v>25</v>
-      </c>
-      <c r="F112">
-        <v>25</v>
-      </c>
-      <c r="G112">
-        <v>25</v>
-      </c>
-      <c r="H112">
-        <v>25</v>
-      </c>
-      <c r="I112">
-        <v>25</v>
-      </c>
-      <c r="J112">
-        <v>25</v>
-      </c>
-      <c r="K112" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="113" spans="2:11">
-      <c r="B113" t="s">
-        <v>639</v>
-      </c>
-      <c r="C113" t="s">
-        <v>31</v>
-      </c>
-      <c r="D113" t="s">
-        <v>622</v>
-      </c>
-      <c r="E113">
-        <v>2</v>
-      </c>
-      <c r="F113">
-        <v>2</v>
-      </c>
-      <c r="G113">
-        <v>2</v>
-      </c>
-      <c r="H113">
-        <v>2</v>
-      </c>
-      <c r="I113">
-        <v>2</v>
-      </c>
-      <c r="J113">
-        <v>2</v>
-      </c>
-      <c r="K113" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="114" spans="2:11">
-      <c r="B114" t="s">
-        <v>639</v>
-      </c>
-      <c r="C114" t="s">
-        <v>31</v>
-      </c>
-      <c r="D114" t="s">
-        <v>622</v>
-      </c>
-      <c r="E114">
-        <v>1.7134</v>
-      </c>
-      <c r="F114">
-        <v>1.7134</v>
-      </c>
-      <c r="G114">
-        <v>1.7134</v>
-      </c>
-      <c r="H114">
-        <v>1.7134</v>
-      </c>
-      <c r="I114">
-        <v>1.7134</v>
-      </c>
-      <c r="J114">
-        <v>1.7134</v>
-      </c>
-      <c r="K114" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="115" spans="2:11">
-      <c r="B115" t="s">
-        <v>640</v>
-      </c>
-      <c r="C115" t="s">
-        <v>31</v>
-      </c>
-      <c r="D115" t="s">
-        <v>626</v>
-      </c>
-      <c r="E115">
-        <v>5410.5</v>
-      </c>
-      <c r="G115">
-        <v>5175.3</v>
-      </c>
-      <c r="J115">
-        <v>4940.1000000000004</v>
-      </c>
-      <c r="K115" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="116" spans="2:11">
+    <row r="116" spans="2:13">
       <c r="B116" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C116" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D116" t="s">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="E116">
-        <v>188.2</v>
+        <v>4</v>
+      </c>
+      <c r="F116">
+        <v>4</v>
       </c>
       <c r="G116">
-        <v>178.8</v>
+        <v>4</v>
+      </c>
+      <c r="H116">
+        <v>4</v>
+      </c>
+      <c r="I116">
+        <v>4</v>
       </c>
       <c r="J116">
-        <v>174.1</v>
-      </c>
-      <c r="K116" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="117" spans="2:11">
-      <c r="B117" t="s">
-        <v>640</v>
-      </c>
-      <c r="C117" t="s">
-        <v>31</v>
-      </c>
-      <c r="D117" t="s">
-        <v>626</v>
-      </c>
-      <c r="E117">
-        <v>2.3610000000000002</v>
-      </c>
-      <c r="G117">
-        <v>2.3610000000000002</v>
-      </c>
-      <c r="J117">
-        <v>2.3610000000000002</v>
-      </c>
-      <c r="K117" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="118" spans="2:11">
-      <c r="B118" t="s">
-        <v>640</v>
-      </c>
-      <c r="C118" t="s">
-        <v>31</v>
-      </c>
-      <c r="D118" t="s">
-        <v>626</v>
-      </c>
-      <c r="E118">
-        <v>0.3</v>
-      </c>
-      <c r="G118">
-        <v>0.3</v>
-      </c>
-      <c r="J118">
-        <v>0.3</v>
-      </c>
-      <c r="K118" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="119" spans="2:11">
-      <c r="B119" t="s">
-        <v>640</v>
-      </c>
-      <c r="C119" t="s">
-        <v>31</v>
-      </c>
-      <c r="D119" t="s">
-        <v>626</v>
-      </c>
-      <c r="E119">
-        <v>0.6</v>
-      </c>
-      <c r="G119">
-        <v>0.6</v>
-      </c>
-      <c r="J119">
-        <v>0.6</v>
-      </c>
-      <c r="K119" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="120" spans="2:11">
-      <c r="B120" t="s">
-        <v>640</v>
-      </c>
-      <c r="C120" t="s">
-        <v>31</v>
-      </c>
-      <c r="D120" t="s">
-        <v>626</v>
-      </c>
-      <c r="E120">
-        <v>30</v>
-      </c>
-      <c r="F120">
-        <v>30</v>
-      </c>
-      <c r="G120">
-        <v>30</v>
-      </c>
-      <c r="H120">
-        <v>30</v>
-      </c>
-      <c r="I120">
-        <v>30</v>
-      </c>
-      <c r="J120">
-        <v>30</v>
-      </c>
-      <c r="K120" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="121" spans="2:11">
-      <c r="B121" t="s">
-        <v>640</v>
-      </c>
-      <c r="C121" t="s">
-        <v>31</v>
-      </c>
-      <c r="D121" t="s">
-        <v>626</v>
-      </c>
-      <c r="E121">
-        <v>3</v>
-      </c>
-      <c r="F121">
-        <v>3</v>
-      </c>
-      <c r="G121">
-        <v>3</v>
-      </c>
-      <c r="H121">
-        <v>3</v>
-      </c>
-      <c r="I121">
-        <v>3</v>
-      </c>
-      <c r="J121">
-        <v>3</v>
-      </c>
-      <c r="K121" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="122" spans="2:11">
-      <c r="B122" t="s">
-        <v>641</v>
-      </c>
-      <c r="C122" t="s">
-        <v>34</v>
-      </c>
-      <c r="D122" t="s">
-        <v>19</v>
-      </c>
-      <c r="E122">
-        <v>2681.7</v>
-      </c>
-      <c r="G122">
-        <v>2587.6</v>
-      </c>
-      <c r="J122">
-        <v>2446.5</v>
-      </c>
-      <c r="K122" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="123" spans="2:11">
-      <c r="B123" t="s">
-        <v>641</v>
-      </c>
-      <c r="C123" t="s">
-        <v>34</v>
-      </c>
-      <c r="D123" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123">
-        <v>51.8</v>
-      </c>
-      <c r="G123">
-        <v>51.8</v>
-      </c>
-      <c r="J123">
-        <v>47</v>
-      </c>
-      <c r="K123" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="124" spans="2:11">
-      <c r="B124" t="s">
-        <v>641</v>
-      </c>
-      <c r="C124" t="s">
-        <v>34</v>
-      </c>
-      <c r="D124" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124">
-        <v>0</v>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="125" spans="2:11">
-      <c r="B125" t="s">
-        <v>641</v>
-      </c>
-      <c r="C125" t="s">
-        <v>34</v>
-      </c>
-      <c r="D125" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125">
-        <v>0.1</v>
-      </c>
-      <c r="G125">
-        <v>0.1</v>
-      </c>
-      <c r="J125">
-        <v>0.1</v>
-      </c>
-      <c r="K125" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="126" spans="2:11">
-      <c r="B126" t="s">
-        <v>641</v>
-      </c>
-      <c r="C126" t="s">
-        <v>34</v>
-      </c>
-      <c r="D126" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126">
-        <v>0.85</v>
-      </c>
-      <c r="G126">
-        <v>0.85</v>
-      </c>
-      <c r="J126">
-        <v>0.85</v>
-      </c>
-      <c r="K126" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="127" spans="2:11">
-      <c r="B127" t="s">
-        <v>641</v>
-      </c>
-      <c r="C127" t="s">
-        <v>34</v>
-      </c>
-      <c r="D127" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127">
-        <v>30</v>
-      </c>
-      <c r="F127">
-        <v>30</v>
-      </c>
-      <c r="G127">
-        <v>30</v>
-      </c>
-      <c r="H127">
-        <v>30</v>
-      </c>
-      <c r="I127">
-        <v>30</v>
-      </c>
-      <c r="J127">
-        <v>30</v>
-      </c>
-      <c r="K127" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="128" spans="2:11">
-      <c r="B128" t="s">
-        <v>641</v>
-      </c>
-      <c r="C128" t="s">
-        <v>34</v>
-      </c>
-      <c r="D128" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128">
+      <c r="K116">
         <v>4</v>
       </c>
-      <c r="G128">
+      <c r="L116">
         <v>4</v>
       </c>
-      <c r="H128">
-        <v>4</v>
-      </c>
-      <c r="I128">
-        <v>4</v>
-      </c>
-      <c r="J128">
-        <v>4</v>
-      </c>
-      <c r="K128" t="s">
-        <v>619</v>
+      <c r="M116" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCB76F6B-22CA-4D8A-9D2F-2B0695154B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55103FB5-0894-458E-9986-5011D3071B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -942,18 +942,156 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_FRA_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_FRA_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_FRA_007</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_FRA_028</t>
   </si>
   <si>
@@ -978,144 +1116,6 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_FRA_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_FRA_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_FRA_009</t>
   </si>
   <si>
@@ -1134,6 +1134,72 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w24020601-400_FRA,e_w159167277-400_FRA,e_w147132694-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w98890904-400_FRA,e_w110086345-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w90842395-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA,e_w147132694-400_FRA,e_w90842395-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w147132694-400_FRA,e_w159167277-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w112342683-400_FRA,e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w49510896-400_FRA,e_w98890904-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w99722046-400_FRA,e_w85995894-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w85710783-400_FRA,e_w85203486-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w179260933-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w179260933-400_FRA,e_w81641090-400_FRA,e_w159167277-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w82825438-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w81641090-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w79866837-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
     <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
   </si>
   <si>
@@ -1149,78 +1215,102 @@
     <t>e_w79866837-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
   </si>
   <si>
-    <t>e_w98890904-400_FRA,e_w110086345-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w49510896-400_FRA,e_w98890904-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w112342683-400_FRA,e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA,e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w27259817-400_FRA,e_w147132694-400_FRA,e_w90842395-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w147132694-400_FRA,e_w159167277-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w99722046-400_FRA,e_w85995894-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w85710783-400_FRA,e_w85203486-400_FRA,e_w85047359-400_FRA,e_w36805588-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w179260933-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w179260933-400_FRA,e_w81641090-400_FRA,e_w159167277-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w79866837-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w24020601-400_FRA,e_w159167277-400_FRA,e_w147132694-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w82825438-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w81641090-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
-  </si>
-  <si>
-    <t>e_w90842395-400_FRA</t>
-  </si>
-  <si>
     <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA</t>
   </si>
   <si>
     <t>e_w79866837-400_FRA,e_w82599261-400_FRA,e_w179260933-400_FRA</t>
   </si>
   <si>
+    <t>distr_wonelc_won_FRA_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_FRA_025</t>
   </si>
   <si>
@@ -1233,6 +1323,42 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wonelc_won_FRA_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_FRA_028</t>
   </si>
   <si>
@@ -1245,114 +1371,12 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_FRA_026</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_FRA_014</t>
   </si>
   <si>
@@ -1365,28 +1389,85 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_FRA_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_FRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_FRA_022</t>
+  </si>
+  <si>
+    <t>e_w159167277-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_012</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_020</t>
+  </si>
+  <si>
+    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA,e_w118086309-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_001</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA,e_w90842395-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_010</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w235370803-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_002</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_004</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA,e_w147132694-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_018</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_013</t>
+  </si>
+  <si>
+    <t>e_w49510896-400_FRA,e_w98890904-400_FRA,e_w71933077-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_024</t>
+  </si>
+  <si>
+    <t>e_w71933077-400_FRA,e_w79866837-400_FRA,e_w179260933-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_011</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_006</t>
+  </si>
+  <si>
+    <t>e_w110086345-400_FRA,e_w24020601-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_027</t>
+  </si>
+  <si>
+    <t>e_w235370803-400_FRA,e_w49510896-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_005</t>
+  </si>
+  <si>
+    <t>e_w27259817-400_FRA</t>
   </si>
   <si>
     <t>elc_won_FRA_025</t>
@@ -1401,6 +1482,36 @@
     <t>e_w71933077-400_FRA,e_w98890904-400_FRA,e_w110086345-400_FRA,e_w24020601-400_FRA</t>
   </si>
   <si>
+    <t>elc_won_FRA_017</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w85710783-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_007</t>
+  </si>
+  <si>
+    <t>e_w98890904-400_FRA,e_w110086345-400_FRA,e_w27259817-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_023</t>
+  </si>
+  <si>
+    <t>e_w179260933-400_FRA,e_w24020601-400_FRA,e_w159167277-400_FRA,e_w81641090-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_021</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_003</t>
+  </si>
+  <si>
+    <t>elc_won_FRA_008</t>
+  </si>
+  <si>
+    <t>e_w24020601-400_FRA</t>
+  </si>
+  <si>
     <t>elc_won_FRA_028</t>
   </si>
   <si>
@@ -1413,102 +1524,9 @@
     <t>e_w118086309-400_FRA</t>
   </si>
   <si>
-    <t>elc_won_FRA_018</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w112342683-400_FRA,e_w85995894-400_FRA,e_w99722046-400_FRA,e_w85710783-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_013</t>
-  </si>
-  <si>
-    <t>e_w49510896-400_FRA,e_w98890904-400_FRA,e_w71933077-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_024</t>
-  </si>
-  <si>
-    <t>e_w71933077-400_FRA,e_w79866837-400_FRA,e_w179260933-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_010</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w235370803-400_FRA</t>
-  </si>
-  <si>
     <t>elc_won_FRA_026</t>
   </si>
   <si>
-    <t>elc_won_FRA_004</t>
-  </si>
-  <si>
-    <t>e_w27259817-400_FRA,e_w147132694-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_023</t>
-  </si>
-  <si>
-    <t>e_w179260933-400_FRA,e_w24020601-400_FRA,e_w159167277-400_FRA,e_w81641090-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_021</t>
-  </si>
-  <si>
-    <t>e_w159167277-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_003</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_008</t>
-  </si>
-  <si>
-    <t>e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_011</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_006</t>
-  </si>
-  <si>
-    <t>e_w110086345-400_FRA,e_w24020601-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_012</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_020</t>
-  </si>
-  <si>
-    <t>e_w82599261-400_FRA,e_w82825438-400_FRA,e_w81641090-400_FRA,e_w118086309-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_001</t>
-  </si>
-  <si>
-    <t>e_w27259817-400_FRA,e_w90842395-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_002</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_027</t>
-  </si>
-  <si>
-    <t>e_w235370803-400_FRA,e_w49510896-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_005</t>
-  </si>
-  <si>
-    <t>e_w27259817-400_FRA</t>
-  </si>
-  <si>
     <t>elc_won_FRA_014</t>
   </si>
   <si>
@@ -1518,30 +1536,48 @@
     <t>e_w85710783-400_FRA,e_w85047359-400_FRA,e_w85203486-400_FRA,e_w36805588-400_FRA,e_w85605950-400_FRA,e_w82825438-400_FRA</t>
   </si>
   <si>
-    <t>elc_won_FRA_022</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_015</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_017</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w85995894-400_FRA,e_w85710783-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_won_FRA_007</t>
-  </si>
-  <si>
-    <t>e_w98890904-400_FRA,e_w110086345-400_FRA,e_w27259817-400_FRA</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_FRA_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_FRA_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_FRA_017</t>
   </si>
   <si>
@@ -1560,6 +1596,30 @@
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_FRA_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_FRA_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_FRA_014</t>
   </si>
   <si>
@@ -1572,75 +1632,33 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_FRA_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_FRA_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_FRA_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>elc_wof_FRA_006</t>
   </si>
   <si>
+    <t>elc_wof_FRA_015</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_007</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_001</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_008</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_005</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_010</t>
+  </si>
+  <si>
     <t>elc_wof_FRA_017</t>
   </si>
   <si>
@@ -1650,6 +1668,24 @@
     <t>elc_wof_FRA_002</t>
   </si>
   <si>
+    <t>elc_wof_FRA_016</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_011</t>
+  </si>
+  <si>
+    <t>e_w111558550-400_FRA,e_w146695955-400_FRA,e_w235370803-400_FRA,e_w112342683-400_FRA,e_w99722046-400_FRA</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_004</t>
+  </si>
+  <si>
+    <t>elc_wof_FRA_013</t>
+  </si>
+  <si>
+    <t>e_w146695955-400_FRA,e_w85995894-400_FRA</t>
+  </si>
+  <si>
     <t>elc_wof_FRA_014</t>
   </si>
   <si>
@@ -1662,43 +1698,7 @@
     <t>e_w146695955-400_FRA,e_w112342683-400_FRA</t>
   </si>
   <si>
-    <t>elc_wof_FRA_008</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_005</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_015</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_007</t>
-  </si>
-  <si>
     <t>elc_wof_FRA_009</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_013</t>
-  </si>
-  <si>
-    <t>e_w146695955-400_FRA,e_w85995894-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_010</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_001</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_016</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_011</t>
-  </si>
-  <si>
-    <t>e_w111558550-400_FRA,e_w146695955-400_FRA,e_w235370803-400_FRA,e_w112342683-400_FRA,e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>elc_wof_FRA_004</t>
   </si>
   <si>
     <t>e_won_FRA_001</t>
@@ -6805,7 +6805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189A85CE-BCCC-4BB0-8E42-A19D57C50955}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC6243BB-DB89-4E3D-81D4-CE91E7D29543}">
   <dimension ref="B9:BD40"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7043,16 +7043,16 @@
         <v>271</v>
       </c>
       <c r="Y11" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="Z11" t="s">
         <v>335</v>
       </c>
       <c r="AA11">
-        <v>0.99760073307445152</v>
+        <v>0.99764504969214185</v>
       </c>
       <c r="AB11">
-        <v>43.986560301722875</v>
+        <v>43.174088977399613</v>
       </c>
       <c r="AD11" t="s">
         <v>270</v>
@@ -7085,10 +7085,10 @@
         <v>421</v>
       </c>
       <c r="AO11">
-        <v>0.99804245386379287</v>
+        <v>0.9979962856207204</v>
       </c>
       <c r="AP11">
-        <v>35.888345830464296</v>
+        <v>36.734763620126827</v>
       </c>
       <c r="AR11" t="s">
         <v>270</v>
@@ -7118,7 +7118,7 @@
         <v>503</v>
       </c>
       <c r="BB11" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="BC11">
         <v>0.98772606347662006</v>
@@ -7189,16 +7189,16 @@
         <v>275</v>
       </c>
       <c r="Y12" t="s">
-        <v>266</v>
+        <v>241</v>
       </c>
       <c r="Z12" t="s">
         <v>336</v>
       </c>
       <c r="AA12">
-        <v>0.99771094718615749</v>
+        <v>0.99811888657672254</v>
       </c>
       <c r="AB12">
-        <v>41.965968253779806</v>
+        <v>34.487079426754121</v>
       </c>
       <c r="AD12" t="s">
         <v>270</v>
@@ -7228,13 +7228,13 @@
         <v>422</v>
       </c>
       <c r="AN12" t="s">
-        <v>423</v>
+        <v>345</v>
       </c>
       <c r="AO12">
-        <v>0.9970097215210143</v>
+        <v>0.99724350262056138</v>
       </c>
       <c r="AP12">
-        <v>54.82177211473752</v>
+        <v>50.535785289707377</v>
       </c>
       <c r="AR12" t="s">
         <v>270</v>
@@ -7264,13 +7264,13 @@
         <v>504</v>
       </c>
       <c r="BB12" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="BC12">
-        <v>0.98065397607653604</v>
+        <v>0.99093284602677045</v>
       </c>
       <c r="BD12">
-        <v>354.67710526350635</v>
+        <v>166.23115617587521</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7335,16 +7335,16 @@
         <v>277</v>
       </c>
       <c r="Y13" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="Z13" t="s">
         <v>337</v>
       </c>
       <c r="AA13">
-        <v>0.99789185737427777</v>
+        <v>0.99796668524605581</v>
       </c>
       <c r="AB13">
-        <v>38.649281471573786</v>
+        <v>37.277437155643319</v>
       </c>
       <c r="AD13" t="s">
         <v>270</v>
@@ -7371,16 +7371,16 @@
         <v>368</v>
       </c>
       <c r="AM13" t="s">
+        <v>423</v>
+      </c>
+      <c r="AN13" t="s">
         <v>424</v>
       </c>
-      <c r="AN13" t="s">
-        <v>425</v>
-      </c>
       <c r="AO13">
-        <v>0.99712165362217109</v>
+        <v>0.99816665404006633</v>
       </c>
       <c r="AP13">
-        <v>52.769683593529635</v>
+        <v>33.611342598783573</v>
       </c>
       <c r="AR13" t="s">
         <v>270</v>
@@ -7410,13 +7410,13 @@
         <v>505</v>
       </c>
       <c r="BB13" t="s">
-        <v>361</v>
+        <v>426</v>
       </c>
       <c r="BC13">
-        <v>0.98299346510038665</v>
+        <v>0.99703425039877824</v>
       </c>
       <c r="BD13">
-        <v>311.78647315957892</v>
+        <v>54.372076022398424</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7481,16 +7481,16 @@
         <v>279</v>
       </c>
       <c r="Y14" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="Z14" t="s">
         <v>338</v>
       </c>
       <c r="AA14">
-        <v>0.99603217268588318</v>
+        <v>0.98282786238014608</v>
       </c>
       <c r="AB14">
-        <v>72.743500758808537</v>
+        <v>314.82252303065502</v>
       </c>
       <c r="AD14" t="s">
         <v>270</v>
@@ -7517,16 +7517,16 @@
         <v>370</v>
       </c>
       <c r="AM14" t="s">
+        <v>425</v>
+      </c>
+      <c r="AN14" t="s">
         <v>426</v>
       </c>
-      <c r="AN14" t="s">
-        <v>427</v>
-      </c>
       <c r="AO14">
-        <v>0.99650877616217826</v>
+        <v>0.98918214360614543</v>
       </c>
       <c r="AP14">
-        <v>64.005770360066109</v>
+        <v>198.32736722066633</v>
       </c>
       <c r="AR14" t="s">
         <v>270</v>
@@ -7556,13 +7556,13 @@
         <v>506</v>
       </c>
       <c r="BB14" t="s">
-        <v>361</v>
+        <v>454</v>
       </c>
       <c r="BC14">
-        <v>0.98380382000267219</v>
+        <v>0.99536965776860997</v>
       </c>
       <c r="BD14">
-        <v>296.92996661767575</v>
+        <v>84.889607575482927</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7627,16 +7627,16 @@
         <v>281</v>
       </c>
       <c r="Y15" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="Z15" t="s">
         <v>339</v>
       </c>
       <c r="AA15">
-        <v>0.99851075781809495</v>
+        <v>0.9980700000086743</v>
       </c>
       <c r="AB15">
-        <v>27.30277333492506</v>
+        <v>35.38333317430456</v>
       </c>
       <c r="AD15" t="s">
         <v>270</v>
@@ -7663,16 +7663,16 @@
         <v>372</v>
       </c>
       <c r="AM15" t="s">
+        <v>427</v>
+      </c>
+      <c r="AN15" t="s">
         <v>428</v>
       </c>
-      <c r="AN15" t="s">
-        <v>429</v>
-      </c>
       <c r="AO15">
-        <v>0.99765345145842399</v>
+        <v>0.99808767667924114</v>
       </c>
       <c r="AP15">
-        <v>43.020056595559488</v>
+        <v>35.059260880579068</v>
       </c>
       <c r="AR15" t="s">
         <v>270</v>
@@ -7702,13 +7702,13 @@
         <v>507</v>
       </c>
       <c r="BB15" t="s">
-        <v>508</v>
+        <v>446</v>
       </c>
       <c r="BC15">
-        <v>0.99579717949467605</v>
+        <v>0.99850355933568513</v>
       </c>
       <c r="BD15">
-        <v>77.051709264272191</v>
+        <v>27.434745512439168</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7773,16 +7773,16 @@
         <v>283</v>
       </c>
       <c r="Y16" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Z16" t="s">
         <v>340</v>
       </c>
       <c r="AA16">
-        <v>0.99778628553476412</v>
+        <v>0.99767867140691957</v>
       </c>
       <c r="AB16">
-        <v>40.584765195991288</v>
+        <v>42.55769087314146</v>
       </c>
       <c r="AD16" t="s">
         <v>270</v>
@@ -7809,16 +7809,16 @@
         <v>374</v>
       </c>
       <c r="AM16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN16" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AO16">
-        <v>0.99756226071513543</v>
+        <v>0.99857814187768335</v>
       </c>
       <c r="AP16">
-        <v>44.691886889183898</v>
+        <v>26.067398909139413</v>
       </c>
       <c r="AR16" t="s">
         <v>270</v>
@@ -7845,16 +7845,16 @@
         <v>479</v>
       </c>
       <c r="BA16" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="BB16" t="s">
-        <v>510</v>
+        <v>338</v>
       </c>
       <c r="BC16">
-        <v>0.9911086854453236</v>
+        <v>0.97849331544243145</v>
       </c>
       <c r="BD16">
-        <v>163.0074335024004</v>
+        <v>394.28921688875596</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7919,16 +7919,16 @@
         <v>285</v>
       </c>
       <c r="Y17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z17" t="s">
         <v>341</v>
       </c>
       <c r="AA17">
-        <v>0.99700804792465858</v>
+        <v>0.9987681422400152</v>
       </c>
       <c r="AB17">
-        <v>54.85245471459325</v>
+        <v>22.584058933054997</v>
       </c>
       <c r="AD17" t="s">
         <v>270</v>
@@ -7955,16 +7955,16 @@
         <v>376</v>
       </c>
       <c r="AM17" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN17" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AO17">
-        <v>0.99719673945277698</v>
+        <v>0.99739565808689357</v>
       </c>
       <c r="AP17">
-        <v>51.393110032423003</v>
+        <v>47.746268406951614</v>
       </c>
       <c r="AR17" t="s">
         <v>270</v>
@@ -7991,16 +7991,16 @@
         <v>481</v>
       </c>
       <c r="BA17" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="BB17" t="s">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="BC17">
-        <v>0.99850355933568513</v>
+        <v>0.99863344496525219</v>
       </c>
       <c r="BD17">
-        <v>27.434745512439168</v>
+        <v>25.053508970375976</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8065,16 +8065,16 @@
         <v>287</v>
       </c>
       <c r="Y18" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="Z18" t="s">
         <v>342</v>
       </c>
       <c r="AA18">
-        <v>0.99768389076925323</v>
+        <v>0.9967781407005234</v>
       </c>
       <c r="AB18">
-        <v>42.462002563689758</v>
+        <v>59.06742049040524</v>
       </c>
       <c r="AD18" t="s">
         <v>270</v>
@@ -8101,16 +8101,16 @@
         <v>378</v>
       </c>
       <c r="AM18" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AN18" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AO18">
-        <v>0.99808767667924114</v>
+        <v>0.99765345145842399</v>
       </c>
       <c r="AP18">
-        <v>35.059260880579068</v>
+        <v>43.020056595559488</v>
       </c>
       <c r="AR18" t="s">
         <v>270</v>
@@ -8137,16 +8137,16 @@
         <v>483</v>
       </c>
       <c r="BA18" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="BB18" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="BC18">
-        <v>0.97849331544243145</v>
+        <v>0.98065397607653604</v>
       </c>
       <c r="BD18">
-        <v>394.28921688875596</v>
+        <v>354.67710526350635</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8211,16 +8211,16 @@
         <v>289</v>
       </c>
       <c r="Y19" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Z19" t="s">
         <v>343</v>
       </c>
       <c r="AA19">
-        <v>0.99678800794697264</v>
+        <v>0.99768389076925323</v>
       </c>
       <c r="AB19">
-        <v>58.88652097216788</v>
+        <v>42.462002563689758</v>
       </c>
       <c r="AD19" t="s">
         <v>270</v>
@@ -8247,16 +8247,16 @@
         <v>380</v>
       </c>
       <c r="AM19" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AN19" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="AO19">
-        <v>0.99789185043252149</v>
+        <v>0.99756226071513543</v>
       </c>
       <c r="AP19">
-        <v>38.649408737106661</v>
+        <v>44.691886889183898</v>
       </c>
       <c r="AR19" t="s">
         <v>270</v>
@@ -8283,16 +8283,16 @@
         <v>485</v>
       </c>
       <c r="BA19" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="BB19" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="BC19">
-        <v>0.99093284602677045</v>
+        <v>0.98299346510038665</v>
       </c>
       <c r="BD19">
-        <v>166.23115617587521</v>
+        <v>311.78647315957892</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8357,16 +8357,16 @@
         <v>291</v>
       </c>
       <c r="Y20" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="Z20" t="s">
         <v>344</v>
       </c>
       <c r="AA20">
-        <v>0.9967781407005234</v>
+        <v>0.99678800794697264</v>
       </c>
       <c r="AB20">
-        <v>59.06742049040524</v>
+        <v>58.88652097216788</v>
       </c>
       <c r="AD20" t="s">
         <v>270</v>
@@ -8393,16 +8393,16 @@
         <v>382</v>
       </c>
       <c r="AM20" t="s">
+        <v>436</v>
+      </c>
+      <c r="AN20" t="s">
         <v>437</v>
       </c>
-      <c r="AN20" t="s">
-        <v>438</v>
-      </c>
       <c r="AO20">
-        <v>0.99739565808689357</v>
+        <v>0.99719673945277698</v>
       </c>
       <c r="AP20">
-        <v>47.746268406951614</v>
+        <v>51.393110032423003</v>
       </c>
       <c r="AR20" t="s">
         <v>270</v>
@@ -8429,16 +8429,16 @@
         <v>487</v>
       </c>
       <c r="BA20" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="BB20" t="s">
-        <v>454</v>
+        <v>338</v>
       </c>
       <c r="BC20">
-        <v>0.99703425039877824</v>
+        <v>0.98380382000267219</v>
       </c>
       <c r="BD20">
-        <v>54.372076022398424</v>
+        <v>296.92996661767575</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8503,16 +8503,16 @@
         <v>293</v>
       </c>
       <c r="Y21" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="Z21" t="s">
         <v>345</v>
       </c>
       <c r="AA21">
-        <v>0.9980700000086743</v>
+        <v>0.99807548905811494</v>
       </c>
       <c r="AB21">
-        <v>35.38333317430456</v>
+        <v>35.282700601226196</v>
       </c>
       <c r="AD21" t="s">
         <v>270</v>
@@ -8539,16 +8539,16 @@
         <v>384</v>
       </c>
       <c r="AM21" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN21" t="s">
-        <v>440</v>
+        <v>352</v>
       </c>
       <c r="AO21">
-        <v>0.99648757714768388</v>
+        <v>0.99778204559874861</v>
       </c>
       <c r="AP21">
-        <v>64.394418959127933</v>
+        <v>40.662497356275288</v>
       </c>
       <c r="AR21" t="s">
         <v>270</v>
@@ -8575,16 +8575,16 @@
         <v>489</v>
       </c>
       <c r="BA21" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="BB21" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="BC21">
-        <v>0.99440716597809709</v>
+        <v>0.98973273644055293</v>
       </c>
       <c r="BD21">
-        <v>102.53529040155342</v>
+        <v>188.23316525652893</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8649,16 +8649,16 @@
         <v>295</v>
       </c>
       <c r="Y22" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="Z22" t="s">
         <v>346</v>
       </c>
       <c r="AA22">
-        <v>0.99767867140691957</v>
+        <v>0.99812782016534596</v>
       </c>
       <c r="AB22">
-        <v>42.55769087314146</v>
+        <v>34.323296968657118</v>
       </c>
       <c r="AD22" t="s">
         <v>270</v>
@@ -8685,16 +8685,16 @@
         <v>386</v>
       </c>
       <c r="AM22" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN22" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AO22">
-        <v>0.9988955767418648</v>
+        <v>0.99742029995821757</v>
       </c>
       <c r="AP22">
-        <v>20.247759732477729</v>
+        <v>47.294500766011943</v>
       </c>
       <c r="AR22" t="s">
         <v>270</v>
@@ -8721,16 +8721,16 @@
         <v>491</v>
       </c>
       <c r="BA22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="BB22" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="BC22">
-        <v>0.99419387483019273</v>
+        <v>0.98905121950258512</v>
       </c>
       <c r="BD22">
-        <v>106.44562811313425</v>
+        <v>200.72764245260552</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8795,16 +8795,16 @@
         <v>297</v>
       </c>
       <c r="Y23" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="Z23" t="s">
         <v>347</v>
       </c>
       <c r="AA23">
-        <v>0.9987681422400152</v>
+        <v>0.99873749004157653</v>
       </c>
       <c r="AB23">
-        <v>22.584058933054997</v>
+        <v>23.146015904430175</v>
       </c>
       <c r="AD23" t="s">
         <v>270</v>
@@ -8831,16 +8831,16 @@
         <v>388</v>
       </c>
       <c r="AM23" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AN23" t="s">
-        <v>361</v>
+        <v>442</v>
       </c>
       <c r="AO23">
-        <v>0.99512455257015542</v>
+        <v>0.99817633840500364</v>
       </c>
       <c r="AP23">
-        <v>89.383202880483722</v>
+        <v>33.433795908267413</v>
       </c>
       <c r="AR23" t="s">
         <v>270</v>
@@ -8867,16 +8867,16 @@
         <v>493</v>
       </c>
       <c r="BA23" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="BB23" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="BC23">
-        <v>0.99863344496525219</v>
+        <v>0.99441277928791383</v>
       </c>
       <c r="BD23">
-        <v>25.053508970375976</v>
+        <v>102.43237972158009</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8941,16 +8941,16 @@
         <v>299</v>
       </c>
       <c r="Y24" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Z24" t="s">
         <v>348</v>
       </c>
       <c r="AA24">
-        <v>0.99807548905811494</v>
+        <v>0.99820251673680249</v>
       </c>
       <c r="AB24">
-        <v>35.282700601226196</v>
+        <v>32.953859825288589</v>
       </c>
       <c r="AD24" t="s">
         <v>270</v>
@@ -8977,16 +8977,16 @@
         <v>390</v>
       </c>
       <c r="AM24" t="s">
+        <v>443</v>
+      </c>
+      <c r="AN24" t="s">
         <v>444</v>
       </c>
-      <c r="AN24" t="s">
-        <v>445</v>
-      </c>
       <c r="AO24">
-        <v>0.99854067090268706</v>
+        <v>0.99586599256158292</v>
       </c>
       <c r="AP24">
-        <v>26.754366784069809</v>
+        <v>75.790136370979724</v>
       </c>
       <c r="AR24" t="s">
         <v>270</v>
@@ -9013,16 +9013,16 @@
         <v>495</v>
       </c>
       <c r="BA24" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="BB24" t="s">
-        <v>468</v>
+        <v>518</v>
       </c>
       <c r="BC24">
-        <v>0.99536965776860997</v>
+        <v>0.99419387483019273</v>
       </c>
       <c r="BD24">
-        <v>84.889607575482927</v>
+        <v>106.44562811313425</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9087,16 +9087,16 @@
         <v>301</v>
       </c>
       <c r="Y25" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Z25" t="s">
         <v>349</v>
       </c>
       <c r="AA25">
-        <v>0.99812782016534596</v>
+        <v>0.99719319688440999</v>
       </c>
       <c r="AB25">
-        <v>34.323296968657118</v>
+        <v>51.458057119150247</v>
       </c>
       <c r="AD25" t="s">
         <v>270</v>
@@ -9123,16 +9123,16 @@
         <v>392</v>
       </c>
       <c r="AM25" t="s">
+        <v>445</v>
+      </c>
+      <c r="AN25" t="s">
         <v>446</v>
       </c>
-      <c r="AN25" t="s">
-        <v>447</v>
-      </c>
       <c r="AO25">
-        <v>0.99742029995821757</v>
+        <v>0.99742293468348531</v>
       </c>
       <c r="AP25">
-        <v>47.294500766011943</v>
+        <v>47.246197469436119</v>
       </c>
       <c r="AR25" t="s">
         <v>270</v>
@@ -9159,16 +9159,16 @@
         <v>497</v>
       </c>
       <c r="BA25" t="s">
+        <v>519</v>
+      </c>
+      <c r="BB25" t="s">
         <v>520</v>
       </c>
-      <c r="BB25" t="s">
-        <v>356</v>
-      </c>
       <c r="BC25">
-        <v>0.98973273644055293</v>
+        <v>0.99579717949467605</v>
       </c>
       <c r="BD25">
-        <v>188.23316525652893</v>
+        <v>77.051709264272191</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9233,16 +9233,16 @@
         <v>303</v>
       </c>
       <c r="Y26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Z26" t="s">
         <v>350</v>
       </c>
       <c r="AA26">
-        <v>0.99873749004157653</v>
+        <v>0.99775269613274897</v>
       </c>
       <c r="AB26">
-        <v>23.146015904430175</v>
+        <v>41.200570899602418</v>
       </c>
       <c r="AD26" t="s">
         <v>270</v>
@@ -9269,16 +9269,16 @@
         <v>394</v>
       </c>
       <c r="AM26" t="s">
+        <v>447</v>
+      </c>
+      <c r="AN26" t="s">
         <v>448</v>
       </c>
-      <c r="AN26" t="s">
-        <v>449</v>
-      </c>
       <c r="AO26">
-        <v>0.99817633840500364</v>
+        <v>0.99804245386379287</v>
       </c>
       <c r="AP26">
-        <v>33.433795908267413</v>
+        <v>35.888345830464296</v>
       </c>
       <c r="AR26" t="s">
         <v>270</v>
@@ -9311,10 +9311,10 @@
         <v>522</v>
       </c>
       <c r="BC26">
-        <v>0.98905121950258512</v>
+        <v>0.9911086854453236</v>
       </c>
       <c r="BD26">
-        <v>200.72764245260552</v>
+        <v>163.0074335024004</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9379,16 +9379,16 @@
         <v>305</v>
       </c>
       <c r="Y27" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s">
         <v>351</v>
       </c>
       <c r="AA27">
-        <v>0.99820251673680249</v>
+        <v>0.99737794036187466</v>
       </c>
       <c r="AB27">
-        <v>32.953859825288589</v>
+        <v>48.07109336563137</v>
       </c>
       <c r="AD27" t="s">
         <v>270</v>
@@ -9415,16 +9415,16 @@
         <v>396</v>
       </c>
       <c r="AM27" t="s">
+        <v>449</v>
+      </c>
+      <c r="AN27" t="s">
         <v>450</v>
       </c>
-      <c r="AN27" t="s">
-        <v>348</v>
-      </c>
       <c r="AO27">
-        <v>0.99724350262056138</v>
+        <v>0.9970097215210143</v>
       </c>
       <c r="AP27">
-        <v>50.535785289707377</v>
+        <v>54.82177211473752</v>
       </c>
       <c r="AR27" t="s">
         <v>270</v>
@@ -9454,13 +9454,13 @@
         <v>523</v>
       </c>
       <c r="BB27" t="s">
-        <v>361</v>
+        <v>428</v>
       </c>
       <c r="BC27">
-        <v>0.99441277928791383</v>
+        <v>0.99440716597809709</v>
       </c>
       <c r="BD27">
-        <v>102.43237972158009</v>
+        <v>102.53529040155342</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9525,16 +9525,16 @@
         <v>307</v>
       </c>
       <c r="Y28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Z28" t="s">
         <v>352</v>
       </c>
       <c r="AA28">
-        <v>0.99719319688440999</v>
+        <v>0.99790569401710338</v>
       </c>
       <c r="AB28">
-        <v>51.458057119150247</v>
+        <v>38.395609686438895</v>
       </c>
       <c r="AD28" t="s">
         <v>270</v>
@@ -9567,10 +9567,10 @@
         <v>452</v>
       </c>
       <c r="AO28">
-        <v>0.99816665404006633</v>
+        <v>0.99784198809622926</v>
       </c>
       <c r="AP28">
-        <v>33.611342598783573</v>
+        <v>39.563551569129636</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9635,16 +9635,16 @@
         <v>309</v>
       </c>
       <c r="Y29" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="Z29" t="s">
         <v>353</v>
       </c>
       <c r="AA29">
-        <v>0.99754382386829921</v>
+        <v>0.99777826206332976</v>
       </c>
       <c r="AB29">
-        <v>45.029895747848158</v>
+        <v>40.731862172288039</v>
       </c>
       <c r="AD29" t="s">
         <v>270</v>
@@ -9677,10 +9677,10 @@
         <v>454</v>
       </c>
       <c r="AO29">
-        <v>0.98918214360614543</v>
+        <v>0.99746485747937264</v>
       </c>
       <c r="AP29">
-        <v>198.32736722066633</v>
+        <v>46.477612878168472</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9745,16 +9745,16 @@
         <v>311</v>
       </c>
       <c r="Y30" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="Z30" t="s">
         <v>354</v>
       </c>
       <c r="AA30">
-        <v>0.99783160220227129</v>
+        <v>0.99700804792465858</v>
       </c>
       <c r="AB30">
-        <v>39.753959625025857</v>
+        <v>54.85245471459325</v>
       </c>
       <c r="AD30" t="s">
         <v>270</v>
@@ -9784,13 +9784,13 @@
         <v>455</v>
       </c>
       <c r="AN30" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AO30">
-        <v>0.99857814187768335</v>
+        <v>0.99648757714768388</v>
       </c>
       <c r="AP30">
-        <v>26.067398909139413</v>
+        <v>64.394418959127933</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9855,16 +9855,16 @@
         <v>313</v>
       </c>
       <c r="Y31" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Z31" t="s">
         <v>355</v>
       </c>
       <c r="AA31">
-        <v>0.99764504969214185</v>
+        <v>0.99754382386829921</v>
       </c>
       <c r="AB31">
-        <v>43.174088977399613</v>
+        <v>45.029895747848158</v>
       </c>
       <c r="AD31" t="s">
         <v>270</v>
@@ -9891,16 +9891,16 @@
         <v>404</v>
       </c>
       <c r="AM31" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN31" t="s">
-        <v>457</v>
+        <v>421</v>
       </c>
       <c r="AO31">
-        <v>0.99586599256158292</v>
+        <v>0.9988955767418648</v>
       </c>
       <c r="AP31">
-        <v>75.790136370979724</v>
+        <v>20.247759732477729</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9965,16 +9965,16 @@
         <v>315</v>
       </c>
       <c r="Y32" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Z32" t="s">
         <v>356</v>
       </c>
       <c r="AA32">
-        <v>0.99775269613274897</v>
+        <v>0.99783160220227129</v>
       </c>
       <c r="AB32">
-        <v>41.200570899602418</v>
+        <v>39.753959625025857</v>
       </c>
       <c r="AD32" t="s">
         <v>270</v>
@@ -10004,13 +10004,13 @@
         <v>458</v>
       </c>
       <c r="AN32" t="s">
-        <v>459</v>
+        <v>338</v>
       </c>
       <c r="AO32">
-        <v>0.99742293468348531</v>
+        <v>0.99512455257015542</v>
       </c>
       <c r="AP32">
-        <v>47.246197469436119</v>
+        <v>89.383202880483722</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10075,16 +10075,16 @@
         <v>317</v>
       </c>
       <c r="Y33" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="Z33" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="AA33">
-        <v>0.99737794036187466</v>
+        <v>0.99778628553476412</v>
       </c>
       <c r="AB33">
-        <v>48.07109336563137</v>
+        <v>40.584765195991288</v>
       </c>
       <c r="AD33" t="s">
         <v>270</v>
@@ -10111,16 +10111,16 @@
         <v>408</v>
       </c>
       <c r="AM33" t="s">
+        <v>459</v>
+      </c>
+      <c r="AN33" t="s">
         <v>460</v>
       </c>
-      <c r="AN33" t="s">
-        <v>447</v>
-      </c>
       <c r="AO33">
-        <v>0.99518717763850095</v>
+        <v>0.99854067090268706</v>
       </c>
       <c r="AP33">
-        <v>88.235076627481902</v>
+        <v>26.754366784069809</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10185,16 +10185,16 @@
         <v>319</v>
       </c>
       <c r="Y34" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Z34" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AA34">
-        <v>0.99790569401710338</v>
+        <v>0.99760073307445152</v>
       </c>
       <c r="AB34">
-        <v>38.395609686438895</v>
+        <v>43.986560301722875</v>
       </c>
       <c r="AD34" t="s">
         <v>270</v>
@@ -10227,10 +10227,10 @@
         <v>462</v>
       </c>
       <c r="AO34">
-        <v>0.99810940368916978</v>
+        <v>0.99712165362217109</v>
       </c>
       <c r="AP34">
-        <v>34.660932365220965</v>
+        <v>52.769683593529635</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10295,16 +10295,16 @@
         <v>321</v>
       </c>
       <c r="Y35" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="Z35" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AA35">
-        <v>0.99777826206332976</v>
+        <v>0.99771094718615749</v>
       </c>
       <c r="AB35">
-        <v>40.731862172288039</v>
+        <v>41.965968253779806</v>
       </c>
       <c r="AD35" t="s">
         <v>270</v>
@@ -10334,13 +10334,13 @@
         <v>463</v>
       </c>
       <c r="AN35" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="AO35">
-        <v>0.9979962856207204</v>
+        <v>0.99650877616217826</v>
       </c>
       <c r="AP35">
-        <v>36.734763620126827</v>
+        <v>64.005770360066109</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10405,16 +10405,16 @@
         <v>323</v>
       </c>
       <c r="Y36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Z36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AA36">
-        <v>0.99811888657672254</v>
+        <v>0.99789185737427777</v>
       </c>
       <c r="AB36">
-        <v>34.487079426754121</v>
+        <v>38.649281471573786</v>
       </c>
       <c r="AD36" t="s">
         <v>270</v>
@@ -10441,16 +10441,16 @@
         <v>414</v>
       </c>
       <c r="AM36" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN36" t="s">
-        <v>358</v>
+        <v>462</v>
       </c>
       <c r="AO36">
-        <v>0.99778204559874861</v>
+        <v>0.99789185043252149</v>
       </c>
       <c r="AP36">
-        <v>40.662497356275288</v>
+        <v>38.649408737106661</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10515,16 +10515,16 @@
         <v>325</v>
       </c>
       <c r="Y37" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="Z37" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AA37">
-        <v>0.99796668524605581</v>
+        <v>0.99603217268588318</v>
       </c>
       <c r="AB37">
-        <v>37.277437155643319</v>
+        <v>72.743500758808537</v>
       </c>
       <c r="AD37" t="s">
         <v>270</v>
@@ -10551,16 +10551,16 @@
         <v>416</v>
       </c>
       <c r="AM37" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN37" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="AO37">
-        <v>0.99784198809622926</v>
+        <v>0.99518717763850095</v>
       </c>
       <c r="AP37">
-        <v>39.563551569129636</v>
+        <v>88.235076627481902</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10625,16 +10625,16 @@
         <v>327</v>
       </c>
       <c r="Y38" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="Z38" t="s">
         <v>361</v>
       </c>
       <c r="AA38">
-        <v>0.98282786238014608</v>
+        <v>0.99851075781809495</v>
       </c>
       <c r="AB38">
-        <v>314.82252303065502</v>
+        <v>27.30277333492506</v>
       </c>
       <c r="AD38" t="s">
         <v>270</v>
@@ -10667,10 +10667,10 @@
         <v>468</v>
       </c>
       <c r="AO38">
-        <v>0.99746485747937264</v>
+        <v>0.99810940368916978</v>
       </c>
       <c r="AP38">
-        <v>46.477612878168472</v>
+        <v>34.660932365220965</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10827,7 +10827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6705CB-44D2-47CC-8BF8-B76DCF9CE440}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD339B1-4FBC-41F8-981F-81A0FEC8D00F}">
   <dimension ref="B9:Z38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10939,7 +10939,7 @@
         <v>524</v>
       </c>
       <c r="K11" t="s">
-        <v>453</v>
+        <v>425</v>
       </c>
       <c r="L11">
         <v>7.5214385218371174</v>
@@ -10972,7 +10972,7 @@
         <v>580</v>
       </c>
       <c r="X11" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="Y11">
         <v>38.3018</v>
@@ -11007,7 +11007,7 @@
         <v>526</v>
       </c>
       <c r="K12" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="L12">
         <v>8.5464211426904182</v>
@@ -11040,7 +11040,7 @@
         <v>582</v>
       </c>
       <c r="X12" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="Y12">
         <v>9.3112499999999994</v>
@@ -11075,7 +11075,7 @@
         <v>528</v>
       </c>
       <c r="K13" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="L13">
         <v>1.5340845206129941</v>
@@ -11108,7 +11108,7 @@
         <v>584</v>
       </c>
       <c r="X13" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="Y13">
         <v>9.5287500000000005</v>
@@ -11143,7 +11143,7 @@
         <v>530</v>
       </c>
       <c r="K14" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="L14">
         <v>17.642367792804524</v>
@@ -11176,7 +11176,7 @@
         <v>586</v>
       </c>
       <c r="X14" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="Y14">
         <v>2.1749999999999999E-2</v>
@@ -11211,7 +11211,7 @@
         <v>532</v>
       </c>
       <c r="K15" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="L15">
         <v>3.7020770759557711</v>
@@ -11244,7 +11244,7 @@
         <v>588</v>
       </c>
       <c r="X15" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="Y15">
         <v>8.2590000000000003</v>
@@ -11279,7 +11279,7 @@
         <v>534</v>
       </c>
       <c r="K16" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="L16">
         <v>28.142418601835601</v>
@@ -11347,7 +11347,7 @@
         <v>536</v>
       </c>
       <c r="K17" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="L17">
         <v>52.588193451360631</v>
@@ -11380,7 +11380,7 @@
         <v>592</v>
       </c>
       <c r="X17" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="Y17">
         <v>6.4290000000000003</v>
@@ -11415,7 +11415,7 @@
         <v>538</v>
       </c>
       <c r="K18" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="L18">
         <v>21.66872817402496</v>
@@ -11448,7 +11448,7 @@
         <v>594</v>
       </c>
       <c r="X18" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="Y18">
         <v>0.10199999999999999</v>
@@ -11483,7 +11483,7 @@
         <v>540</v>
       </c>
       <c r="K19" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="L19">
         <v>75.448981284454376</v>
@@ -11516,7 +11516,7 @@
         <v>596</v>
       </c>
       <c r="X19" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="Y19">
         <v>27.910499999999999</v>
@@ -11551,7 +11551,7 @@
         <v>542</v>
       </c>
       <c r="K20" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="L20">
         <v>15.373849239963436</v>
@@ -11584,7 +11584,7 @@
         <v>598</v>
       </c>
       <c r="X20" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="Y20">
         <v>2.7322500000000001</v>
@@ -11619,7 +11619,7 @@
         <v>544</v>
       </c>
       <c r="K21" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="L21">
         <v>20.923088433115996</v>
@@ -11652,7 +11652,7 @@
         <v>600</v>
       </c>
       <c r="X21" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="Y21">
         <v>69.386250000000004</v>
@@ -11687,7 +11687,7 @@
         <v>546</v>
       </c>
       <c r="K22" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="L22">
         <v>10.348692721070078</v>
@@ -11720,7 +11720,7 @@
         <v>602</v>
       </c>
       <c r="X22" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="Y22">
         <v>79.72475</v>
@@ -11755,7 +11755,7 @@
         <v>548</v>
       </c>
       <c r="K23" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L23">
         <v>30.731418987588004</v>
@@ -11788,7 +11788,7 @@
         <v>604</v>
       </c>
       <c r="X23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Y23">
         <v>19.849499999999999</v>
@@ -11823,7 +11823,7 @@
         <v>550</v>
       </c>
       <c r="K24" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="L24">
         <v>6.8734480919946561</v>
@@ -11856,7 +11856,7 @@
         <v>606</v>
       </c>
       <c r="X24" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="Y24">
         <v>34.275750000000002</v>
@@ -11891,7 +11891,7 @@
         <v>552</v>
       </c>
       <c r="K25" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="L25">
         <v>44.470842554915507</v>
@@ -11924,7 +11924,7 @@
         <v>608</v>
       </c>
       <c r="X25" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="Y25">
         <v>88.0535</v>
@@ -11959,7 +11959,7 @@
         <v>554</v>
       </c>
       <c r="K26" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="L26">
         <v>94.751954680638562</v>
@@ -11992,7 +11992,7 @@
         <v>610</v>
       </c>
       <c r="X26" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="Y26">
         <v>42.073500000000003</v>
@@ -12027,7 +12027,7 @@
         <v>556</v>
       </c>
       <c r="K27" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="L27">
         <v>32.871207794729088</v>
@@ -12060,7 +12060,7 @@
         <v>612</v>
       </c>
       <c r="X27" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="Y27">
         <v>65.507249999999999</v>
@@ -12095,7 +12095,7 @@
         <v>558</v>
       </c>
       <c r="K28" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L28">
         <v>113.99847062392492</v>
@@ -12130,7 +12130,7 @@
         <v>560</v>
       </c>
       <c r="K29" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="L29">
         <v>18.2196769426582</v>
@@ -12165,7 +12165,7 @@
         <v>562</v>
       </c>
       <c r="K30" t="s">
-        <v>451</v>
+        <v>423</v>
       </c>
       <c r="L30">
         <v>53.979644051935594</v>
@@ -12200,7 +12200,7 @@
         <v>564</v>
       </c>
       <c r="K31" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="L31">
         <v>17.215449395412726</v>
@@ -12235,7 +12235,7 @@
         <v>566</v>
       </c>
       <c r="K32" t="s">
-        <v>463</v>
+        <v>420</v>
       </c>
       <c r="L32">
         <v>29.852997664126345</v>
@@ -12270,7 +12270,7 @@
         <v>568</v>
       </c>
       <c r="K33" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="L33">
         <v>33.097235865274165</v>
@@ -12305,7 +12305,7 @@
         <v>570</v>
       </c>
       <c r="K34" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L34">
         <v>50.818330360170975</v>
@@ -12340,7 +12340,7 @@
         <v>572</v>
       </c>
       <c r="K35" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="L35">
         <v>93.018246457332225</v>
@@ -12375,7 +12375,7 @@
         <v>574</v>
       </c>
       <c r="K36" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="L36">
         <v>48.982209359452717</v>
@@ -12410,7 +12410,7 @@
         <v>576</v>
       </c>
       <c r="K37" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="L37">
         <v>22.316533209679985</v>
@@ -12445,7 +12445,7 @@
         <v>578</v>
       </c>
       <c r="K38" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="L38">
         <v>43.496233223332773</v>
@@ -12460,7 +12460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977F3ECF-2390-4CB5-B4CF-297D4A330281}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE03A39-31C8-4171-BBA0-EEB604E09D1E}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
